--- a/backend/catalogues_src/Grade 9 Natural Sciences Catalogue.xlsx
+++ b/backend/catalogues_src/Grade 9 Natural Sciences Catalogue.xlsx
@@ -30,7 +30,7 @@
     <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -190,8 +190,14 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill/>
     </fill>
@@ -388,6 +394,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -1018,7 +1030,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -1222,6 +1234,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="17" fontId="21" fillId="34" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="21" fillId="34" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="21" fillId="34" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1607,7 +1628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:V176"/>
+  <dimension ref="B2:V176"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="8.12844036697248" customWidth="1" style="33" min="1" max="1"/>
@@ -1634,7 +1655,6 @@
     <col width="18" customWidth="1" style="33" min="22" max="22"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="14.95" customHeight="1" s="33">
       <c r="B2" s="69" t="inlineStr">
         <is>
@@ -1648,7 +1668,19 @@
       <c r="G2" s="70" t="n"/>
       <c r="H2" s="70" t="n"/>
       <c r="I2" s="70" t="n"/>
-      <c r="J2" s="71" t="n"/>
+      <c r="J2" s="70" t="n"/>
+      <c r="K2" s="70" t="n"/>
+      <c r="L2" s="70" t="n"/>
+      <c r="M2" s="70" t="n"/>
+      <c r="N2" s="70" t="n"/>
+      <c r="O2" s="70" t="n"/>
+      <c r="P2" s="70" t="n"/>
+      <c r="Q2" s="70" t="n"/>
+      <c r="R2" s="70" t="n"/>
+      <c r="S2" s="70" t="n"/>
+      <c r="T2" s="70" t="n"/>
+      <c r="U2" s="70" t="n"/>
+      <c r="V2" s="71" t="n"/>
     </row>
     <row r="3">
       <c r="B3" s="38" t="n"/>
@@ -2305,8 +2337,20 @@
       <c r="F24" s="70" t="n"/>
       <c r="G24" s="70" t="n"/>
       <c r="H24" s="70" t="n"/>
-      <c r="I24" s="71" t="n"/>
-      <c r="J24" s="58" t="n"/>
+      <c r="I24" s="70" t="n"/>
+      <c r="J24" s="70" t="n"/>
+      <c r="K24" s="70" t="n"/>
+      <c r="L24" s="70" t="n"/>
+      <c r="M24" s="70" t="n"/>
+      <c r="N24" s="70" t="n"/>
+      <c r="O24" s="70" t="n"/>
+      <c r="P24" s="70" t="n"/>
+      <c r="Q24" s="70" t="n"/>
+      <c r="R24" s="70" t="n"/>
+      <c r="S24" s="70" t="n"/>
+      <c r="T24" s="70" t="n"/>
+      <c r="U24" s="70" t="n"/>
+      <c r="V24" s="71" t="n"/>
     </row>
     <row r="25">
       <c r="B25" s="38" t="n"/>
@@ -2987,7 +3031,19 @@
       <c r="G47" s="70" t="n"/>
       <c r="H47" s="70" t="n"/>
       <c r="I47" s="70" t="n"/>
-      <c r="J47" s="71" t="n"/>
+      <c r="J47" s="70" t="n"/>
+      <c r="K47" s="70" t="n"/>
+      <c r="L47" s="70" t="n"/>
+      <c r="M47" s="70" t="n"/>
+      <c r="N47" s="70" t="n"/>
+      <c r="O47" s="70" t="n"/>
+      <c r="P47" s="70" t="n"/>
+      <c r="Q47" s="70" t="n"/>
+      <c r="R47" s="70" t="n"/>
+      <c r="S47" s="70" t="n"/>
+      <c r="T47" s="70" t="n"/>
+      <c r="U47" s="70" t="n"/>
+      <c r="V47" s="71" t="n"/>
     </row>
     <row r="48">
       <c r="B48" s="38" t="n"/>
@@ -3644,8 +3700,20 @@
       <c r="F69" s="70" t="n"/>
       <c r="G69" s="70" t="n"/>
       <c r="H69" s="70" t="n"/>
-      <c r="I69" s="71" t="n"/>
-      <c r="J69" s="58" t="n"/>
+      <c r="I69" s="70" t="n"/>
+      <c r="J69" s="70" t="n"/>
+      <c r="K69" s="70" t="n"/>
+      <c r="L69" s="70" t="n"/>
+      <c r="M69" s="70" t="n"/>
+      <c r="N69" s="70" t="n"/>
+      <c r="O69" s="70" t="n"/>
+      <c r="P69" s="70" t="n"/>
+      <c r="Q69" s="70" t="n"/>
+      <c r="R69" s="70" t="n"/>
+      <c r="S69" s="70" t="n"/>
+      <c r="T69" s="70" t="n"/>
+      <c r="U69" s="70" t="n"/>
+      <c r="V69" s="71" t="n"/>
     </row>
     <row r="70">
       <c r="B70" s="38" t="n"/>
@@ -4326,7 +4394,19 @@
       <c r="G92" s="70" t="n"/>
       <c r="H92" s="70" t="n"/>
       <c r="I92" s="70" t="n"/>
-      <c r="J92" s="71" t="n"/>
+      <c r="J92" s="70" t="n"/>
+      <c r="K92" s="70" t="n"/>
+      <c r="L92" s="70" t="n"/>
+      <c r="M92" s="70" t="n"/>
+      <c r="N92" s="70" t="n"/>
+      <c r="O92" s="70" t="n"/>
+      <c r="P92" s="70" t="n"/>
+      <c r="Q92" s="70" t="n"/>
+      <c r="R92" s="70" t="n"/>
+      <c r="S92" s="70" t="n"/>
+      <c r="T92" s="70" t="n"/>
+      <c r="U92" s="70" t="n"/>
+      <c r="V92" s="71" t="n"/>
     </row>
     <row r="93">
       <c r="B93" s="38" t="n"/>
@@ -4983,8 +5063,20 @@
       <c r="F114" s="70" t="n"/>
       <c r="G114" s="70" t="n"/>
       <c r="H114" s="70" t="n"/>
-      <c r="I114" s="71" t="n"/>
-      <c r="J114" s="58" t="n"/>
+      <c r="I114" s="70" t="n"/>
+      <c r="J114" s="70" t="n"/>
+      <c r="K114" s="70" t="n"/>
+      <c r="L114" s="70" t="n"/>
+      <c r="M114" s="70" t="n"/>
+      <c r="N114" s="70" t="n"/>
+      <c r="O114" s="70" t="n"/>
+      <c r="P114" s="70" t="n"/>
+      <c r="Q114" s="70" t="n"/>
+      <c r="R114" s="70" t="n"/>
+      <c r="S114" s="70" t="n"/>
+      <c r="T114" s="70" t="n"/>
+      <c r="U114" s="70" t="n"/>
+      <c r="V114" s="71" t="n"/>
     </row>
     <row r="115">
       <c r="B115" s="38" t="n"/>
@@ -5642,7 +5734,19 @@
       <c r="G136" s="70" t="n"/>
       <c r="H136" s="70" t="n"/>
       <c r="I136" s="70" t="n"/>
-      <c r="J136" s="71" t="n"/>
+      <c r="J136" s="70" t="n"/>
+      <c r="K136" s="70" t="n"/>
+      <c r="L136" s="70" t="n"/>
+      <c r="M136" s="70" t="n"/>
+      <c r="N136" s="70" t="n"/>
+      <c r="O136" s="70" t="n"/>
+      <c r="P136" s="70" t="n"/>
+      <c r="Q136" s="70" t="n"/>
+      <c r="R136" s="70" t="n"/>
+      <c r="S136" s="70" t="n"/>
+      <c r="T136" s="70" t="n"/>
+      <c r="U136" s="70" t="n"/>
+      <c r="V136" s="71" t="n"/>
     </row>
     <row r="137">
       <c r="B137" s="38" t="n"/>
@@ -6299,8 +6403,20 @@
       <c r="F158" s="70" t="n"/>
       <c r="G158" s="70" t="n"/>
       <c r="H158" s="70" t="n"/>
-      <c r="I158" s="71" t="n"/>
-      <c r="J158" s="58" t="n"/>
+      <c r="I158" s="70" t="n"/>
+      <c r="J158" s="70" t="n"/>
+      <c r="K158" s="70" t="n"/>
+      <c r="L158" s="70" t="n"/>
+      <c r="M158" s="70" t="n"/>
+      <c r="N158" s="70" t="n"/>
+      <c r="O158" s="70" t="n"/>
+      <c r="P158" s="70" t="n"/>
+      <c r="Q158" s="70" t="n"/>
+      <c r="R158" s="70" t="n"/>
+      <c r="S158" s="70" t="n"/>
+      <c r="T158" s="70" t="n"/>
+      <c r="U158" s="70" t="n"/>
+      <c r="V158" s="71" t="n"/>
     </row>
     <row r="159">
       <c r="B159" s="38" t="n"/>
@@ -6878,61 +6994,61 @@
     </row>
   </sheetData>
   <mergeCells count="56">
+    <mergeCell ref="D115:H115"/>
+    <mergeCell ref="B93:B94"/>
+    <mergeCell ref="N70:R70"/>
+    <mergeCell ref="B2:V2"/>
     <mergeCell ref="C137:C138"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="N25:R25"/>
+    <mergeCell ref="B136:V136"/>
+    <mergeCell ref="N159:R159"/>
+    <mergeCell ref="D159:H159"/>
+    <mergeCell ref="C115:C116"/>
     <mergeCell ref="I70:M70"/>
+    <mergeCell ref="B69:V69"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="N3:R3"/>
     <mergeCell ref="S159:V159"/>
+    <mergeCell ref="I25:M25"/>
+    <mergeCell ref="C25:C26"/>
     <mergeCell ref="N115:R115"/>
     <mergeCell ref="C93:C94"/>
     <mergeCell ref="N93:R93"/>
     <mergeCell ref="I159:M159"/>
+    <mergeCell ref="I115:M115"/>
+    <mergeCell ref="S25:V25"/>
+    <mergeCell ref="B137:B138"/>
+    <mergeCell ref="I93:M93"/>
+    <mergeCell ref="S115:V115"/>
+    <mergeCell ref="D48:H48"/>
+    <mergeCell ref="S93:V93"/>
+    <mergeCell ref="D70:H70"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="B158:V158"/>
+    <mergeCell ref="N48:R48"/>
+    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="B92:V92"/>
+    <mergeCell ref="S3:V3"/>
+    <mergeCell ref="B24:V24"/>
+    <mergeCell ref="C159:C160"/>
+    <mergeCell ref="S137:V137"/>
+    <mergeCell ref="S70:V70"/>
+    <mergeCell ref="S48:V48"/>
+    <mergeCell ref="B114:V114"/>
+    <mergeCell ref="D93:H93"/>
+    <mergeCell ref="N137:R137"/>
+    <mergeCell ref="D137:H137"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="I48:M48"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="B47:V47"/>
+    <mergeCell ref="C3:C4"/>
     <mergeCell ref="B25:B26"/>
     <mergeCell ref="I137:M137"/>
     <mergeCell ref="B159:B160"/>
-    <mergeCell ref="B2:J2"/>
-    <mergeCell ref="B93:B94"/>
-    <mergeCell ref="N70:R70"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="N159:R159"/>
-    <mergeCell ref="I115:M115"/>
-    <mergeCell ref="S70:V70"/>
-    <mergeCell ref="S48:V48"/>
-    <mergeCell ref="D93:H93"/>
-    <mergeCell ref="N137:R137"/>
-    <mergeCell ref="D3:H3"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="B114:I114"/>
-    <mergeCell ref="S137:V137"/>
-    <mergeCell ref="D159:H159"/>
-    <mergeCell ref="C115:C116"/>
-    <mergeCell ref="I25:M25"/>
-    <mergeCell ref="B92:J92"/>
-    <mergeCell ref="I93:M93"/>
-    <mergeCell ref="S115:V115"/>
-    <mergeCell ref="S93:V93"/>
-    <mergeCell ref="I3:M3"/>
-    <mergeCell ref="C70:C71"/>
-    <mergeCell ref="S3:V3"/>
-    <mergeCell ref="B69:I69"/>
-    <mergeCell ref="D137:H137"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="B47:J47"/>
-    <mergeCell ref="B158:I158"/>
-    <mergeCell ref="I48:M48"/>
-    <mergeCell ref="B24:I24"/>
-    <mergeCell ref="D115:H115"/>
-    <mergeCell ref="B136:J136"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="N25:R25"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="N3:R3"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="S25:V25"/>
-    <mergeCell ref="B137:B138"/>
-    <mergeCell ref="D48:H48"/>
-    <mergeCell ref="D70:H70"/>
-    <mergeCell ref="N48:R48"/>
-    <mergeCell ref="C159:C160"/>
     <mergeCell ref="B115:B116"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6982,9 +7098,22 @@
       <c r="D2" s="70" t="n"/>
       <c r="E2" s="70" t="n"/>
       <c r="F2" s="70" t="n"/>
-      <c r="G2" s="71" t="n"/>
-      <c r="J2" s="5" t="n"/>
-      <c r="K2" s="5" t="n"/>
+      <c r="G2" s="70" t="n"/>
+      <c r="H2" s="70" t="n"/>
+      <c r="I2" s="70" t="n"/>
+      <c r="J2" s="70" t="n"/>
+      <c r="K2" s="70" t="n"/>
+      <c r="L2" s="70" t="n"/>
+      <c r="M2" s="70" t="n"/>
+      <c r="N2" s="70" t="n"/>
+      <c r="O2" s="70" t="n"/>
+      <c r="P2" s="70" t="n"/>
+      <c r="Q2" s="70" t="n"/>
+      <c r="R2" s="70" t="n"/>
+      <c r="S2" s="70" t="n"/>
+      <c r="T2" s="70" t="n"/>
+      <c r="U2" s="70" t="n"/>
+      <c r="V2" s="71" t="n"/>
     </row>
     <row r="3" ht="14.3" customHeight="1" s="33">
       <c r="B3" s="6" t="n"/>
@@ -7416,9 +7545,22 @@
       <c r="D14" s="70" t="n"/>
       <c r="E14" s="70" t="n"/>
       <c r="F14" s="70" t="n"/>
-      <c r="G14" s="71" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="n"/>
+      <c r="G14" s="70" t="n"/>
+      <c r="H14" s="70" t="n"/>
+      <c r="I14" s="70" t="n"/>
+      <c r="J14" s="70" t="n"/>
+      <c r="K14" s="70" t="n"/>
+      <c r="L14" s="70" t="n"/>
+      <c r="M14" s="70" t="n"/>
+      <c r="N14" s="70" t="n"/>
+      <c r="O14" s="70" t="n"/>
+      <c r="P14" s="70" t="n"/>
+      <c r="Q14" s="70" t="n"/>
+      <c r="R14" s="70" t="n"/>
+      <c r="S14" s="70" t="n"/>
+      <c r="T14" s="70" t="n"/>
+      <c r="U14" s="70" t="n"/>
+      <c r="V14" s="71" t="n"/>
     </row>
     <row r="15" ht="14.3" customHeight="1" s="33">
       <c r="B15" s="6" t="n"/>
@@ -7850,9 +7992,22 @@
       <c r="D26" s="70" t="n"/>
       <c r="E26" s="70" t="n"/>
       <c r="F26" s="70" t="n"/>
-      <c r="G26" s="71" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="n"/>
+      <c r="G26" s="70" t="n"/>
+      <c r="H26" s="70" t="n"/>
+      <c r="I26" s="70" t="n"/>
+      <c r="J26" s="70" t="n"/>
+      <c r="K26" s="70" t="n"/>
+      <c r="L26" s="70" t="n"/>
+      <c r="M26" s="70" t="n"/>
+      <c r="N26" s="70" t="n"/>
+      <c r="O26" s="70" t="n"/>
+      <c r="P26" s="70" t="n"/>
+      <c r="Q26" s="70" t="n"/>
+      <c r="R26" s="70" t="n"/>
+      <c r="S26" s="70" t="n"/>
+      <c r="T26" s="70" t="n"/>
+      <c r="U26" s="70" t="n"/>
+      <c r="V26" s="71" t="n"/>
     </row>
     <row r="27" ht="14.3" customHeight="1" s="33">
       <c r="B27" s="6" t="n"/>
@@ -8284,9 +8439,22 @@
       <c r="D38" s="70" t="n"/>
       <c r="E38" s="70" t="n"/>
       <c r="F38" s="70" t="n"/>
-      <c r="G38" s="71" t="n"/>
-      <c r="J38" s="5" t="n"/>
-      <c r="K38" s="5" t="n"/>
+      <c r="G38" s="70" t="n"/>
+      <c r="H38" s="70" t="n"/>
+      <c r="I38" s="70" t="n"/>
+      <c r="J38" s="70" t="n"/>
+      <c r="K38" s="70" t="n"/>
+      <c r="L38" s="70" t="n"/>
+      <c r="M38" s="70" t="n"/>
+      <c r="N38" s="70" t="n"/>
+      <c r="O38" s="70" t="n"/>
+      <c r="P38" s="70" t="n"/>
+      <c r="Q38" s="70" t="n"/>
+      <c r="R38" s="70" t="n"/>
+      <c r="S38" s="70" t="n"/>
+      <c r="T38" s="70" t="n"/>
+      <c r="U38" s="70" t="n"/>
+      <c r="V38" s="71" t="n"/>
     </row>
     <row r="39" ht="14.3" customHeight="1" s="33">
       <c r="B39" s="6" t="n"/>
@@ -8718,9 +8886,22 @@
       <c r="D50" s="70" t="n"/>
       <c r="E50" s="70" t="n"/>
       <c r="F50" s="70" t="n"/>
-      <c r="G50" s="71" t="n"/>
-      <c r="J50" s="5" t="n"/>
-      <c r="K50" s="5" t="n"/>
+      <c r="G50" s="70" t="n"/>
+      <c r="H50" s="70" t="n"/>
+      <c r="I50" s="70" t="n"/>
+      <c r="J50" s="70" t="n"/>
+      <c r="K50" s="70" t="n"/>
+      <c r="L50" s="70" t="n"/>
+      <c r="M50" s="70" t="n"/>
+      <c r="N50" s="70" t="n"/>
+      <c r="O50" s="70" t="n"/>
+      <c r="P50" s="70" t="n"/>
+      <c r="Q50" s="70" t="n"/>
+      <c r="R50" s="70" t="n"/>
+      <c r="S50" s="70" t="n"/>
+      <c r="T50" s="70" t="n"/>
+      <c r="U50" s="70" t="n"/>
+      <c r="V50" s="71" t="n"/>
     </row>
     <row r="51" ht="14.3" customHeight="1" s="33">
       <c r="B51" s="6" t="n"/>
@@ -9030,31 +9211,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B58" s="20" t="inlineStr">
+      <c r="B58" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C58" s="31" t="n"/>
-      <c r="D58" s="31" t="n"/>
-      <c r="E58" s="31" t="n"/>
-      <c r="F58" s="31" t="n"/>
-      <c r="G58" s="31" t="n"/>
-      <c r="H58" s="31" t="n"/>
-      <c r="I58" s="31" t="n"/>
-      <c r="J58" s="31" t="n"/>
-      <c r="K58" s="31" t="n"/>
-      <c r="L58" s="31" t="n"/>
-      <c r="M58" s="31" t="n"/>
-      <c r="N58" s="31" t="n"/>
-      <c r="O58" s="31" t="n"/>
-      <c r="P58" s="31" t="n"/>
-      <c r="Q58" s="31" t="n"/>
-      <c r="R58" s="31" t="n"/>
-      <c r="S58" s="31" t="n"/>
-      <c r="T58" s="31" t="n"/>
-      <c r="U58" s="31" t="n"/>
-      <c r="V58" s="31" t="n"/>
+      <c r="C58" s="80" t="n"/>
+      <c r="D58" s="80" t="n"/>
+      <c r="E58" s="80" t="n"/>
+      <c r="F58" s="80" t="n"/>
+      <c r="G58" s="80" t="n"/>
+      <c r="H58" s="80" t="n"/>
+      <c r="I58" s="80" t="n"/>
+      <c r="J58" s="80" t="n"/>
+      <c r="K58" s="80" t="n"/>
+      <c r="L58" s="80" t="n"/>
+      <c r="M58" s="80" t="n"/>
+      <c r="N58" s="80" t="n"/>
+      <c r="O58" s="80" t="n"/>
+      <c r="P58" s="80" t="n"/>
+      <c r="Q58" s="80" t="n"/>
+      <c r="R58" s="80" t="n"/>
+      <c r="S58" s="80" t="n"/>
+      <c r="T58" s="80" t="n"/>
+      <c r="U58" s="80" t="n"/>
+      <c r="V58" s="80" t="n"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -9152,9 +9333,22 @@
       <c r="D62" s="70" t="n"/>
       <c r="E62" s="70" t="n"/>
       <c r="F62" s="70" t="n"/>
-      <c r="G62" s="71" t="n"/>
-      <c r="J62" s="5" t="n"/>
-      <c r="K62" s="5" t="n"/>
+      <c r="G62" s="70" t="n"/>
+      <c r="H62" s="70" t="n"/>
+      <c r="I62" s="70" t="n"/>
+      <c r="J62" s="70" t="n"/>
+      <c r="K62" s="70" t="n"/>
+      <c r="L62" s="70" t="n"/>
+      <c r="M62" s="70" t="n"/>
+      <c r="N62" s="70" t="n"/>
+      <c r="O62" s="70" t="n"/>
+      <c r="P62" s="70" t="n"/>
+      <c r="Q62" s="70" t="n"/>
+      <c r="R62" s="70" t="n"/>
+      <c r="S62" s="70" t="n"/>
+      <c r="T62" s="70" t="n"/>
+      <c r="U62" s="70" t="n"/>
+      <c r="V62" s="71" t="n"/>
     </row>
     <row r="63" ht="14.3" customHeight="1" s="33">
       <c r="B63" s="6" t="n"/>
@@ -9464,31 +9658,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B70" s="20" t="inlineStr">
+      <c r="B70" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C70" s="21" t="n"/>
-      <c r="D70" s="21" t="n"/>
-      <c r="E70" s="21" t="n"/>
-      <c r="F70" s="21" t="n"/>
-      <c r="G70" s="21" t="n"/>
-      <c r="H70" s="21" t="n"/>
-      <c r="I70" s="21" t="n"/>
-      <c r="J70" s="21" t="n"/>
-      <c r="K70" s="21" t="n"/>
-      <c r="L70" s="21" t="n"/>
-      <c r="M70" s="21" t="n"/>
-      <c r="N70" s="21" t="n"/>
-      <c r="O70" s="21" t="n"/>
-      <c r="P70" s="21" t="n"/>
-      <c r="Q70" s="21" t="n"/>
-      <c r="R70" s="21" t="n"/>
-      <c r="S70" s="21" t="n"/>
-      <c r="T70" s="21" t="n"/>
-      <c r="U70" s="21" t="n"/>
-      <c r="V70" s="21" t="n"/>
+      <c r="C70" s="82" t="n"/>
+      <c r="D70" s="82" t="n"/>
+      <c r="E70" s="82" t="n"/>
+      <c r="F70" s="82" t="n"/>
+      <c r="G70" s="82" t="n"/>
+      <c r="H70" s="82" t="n"/>
+      <c r="I70" s="82" t="n"/>
+      <c r="J70" s="82" t="n"/>
+      <c r="K70" s="82" t="n"/>
+      <c r="L70" s="82" t="n"/>
+      <c r="M70" s="82" t="n"/>
+      <c r="N70" s="82" t="n"/>
+      <c r="O70" s="82" t="n"/>
+      <c r="P70" s="82" t="n"/>
+      <c r="Q70" s="82" t="n"/>
+      <c r="R70" s="82" t="n"/>
+      <c r="S70" s="82" t="n"/>
+      <c r="T70" s="82" t="n"/>
+      <c r="U70" s="82" t="n"/>
+      <c r="V70" s="82" t="n"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -9586,9 +9780,22 @@
       <c r="D74" s="70" t="n"/>
       <c r="E74" s="70" t="n"/>
       <c r="F74" s="70" t="n"/>
-      <c r="G74" s="71" t="n"/>
-      <c r="J74" s="5" t="n"/>
-      <c r="K74" s="5" t="n"/>
+      <c r="G74" s="70" t="n"/>
+      <c r="H74" s="70" t="n"/>
+      <c r="I74" s="70" t="n"/>
+      <c r="J74" s="70" t="n"/>
+      <c r="K74" s="70" t="n"/>
+      <c r="L74" s="70" t="n"/>
+      <c r="M74" s="70" t="n"/>
+      <c r="N74" s="70" t="n"/>
+      <c r="O74" s="70" t="n"/>
+      <c r="P74" s="70" t="n"/>
+      <c r="Q74" s="70" t="n"/>
+      <c r="R74" s="70" t="n"/>
+      <c r="S74" s="70" t="n"/>
+      <c r="T74" s="70" t="n"/>
+      <c r="U74" s="70" t="n"/>
+      <c r="V74" s="71" t="n"/>
     </row>
     <row r="75" ht="14.3" customHeight="1" s="33">
       <c r="B75" s="6" t="n"/>
@@ -10020,9 +10227,22 @@
       <c r="D86" s="70" t="n"/>
       <c r="E86" s="70" t="n"/>
       <c r="F86" s="70" t="n"/>
-      <c r="G86" s="71" t="n"/>
-      <c r="J86" s="5" t="n"/>
-      <c r="K86" s="5" t="n"/>
+      <c r="G86" s="70" t="n"/>
+      <c r="H86" s="70" t="n"/>
+      <c r="I86" s="70" t="n"/>
+      <c r="J86" s="70" t="n"/>
+      <c r="K86" s="70" t="n"/>
+      <c r="L86" s="70" t="n"/>
+      <c r="M86" s="70" t="n"/>
+      <c r="N86" s="70" t="n"/>
+      <c r="O86" s="70" t="n"/>
+      <c r="P86" s="70" t="n"/>
+      <c r="Q86" s="70" t="n"/>
+      <c r="R86" s="70" t="n"/>
+      <c r="S86" s="70" t="n"/>
+      <c r="T86" s="70" t="n"/>
+      <c r="U86" s="70" t="n"/>
+      <c r="V86" s="71" t="n"/>
     </row>
     <row r="87" ht="14.3" customHeight="1" s="33">
       <c r="B87" s="6" t="n"/>
@@ -10468,62 +10688,62 @@
     </row>
   </sheetData>
   <mergeCells count="56">
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="B86:V86"/>
+    <mergeCell ref="B2:V2"/>
+    <mergeCell ref="I15:M15"/>
+    <mergeCell ref="B3:B4"/>
     <mergeCell ref="N63:R63"/>
+    <mergeCell ref="D63:H63"/>
     <mergeCell ref="C63:C64"/>
     <mergeCell ref="I27:M27"/>
+    <mergeCell ref="B14:V14"/>
     <mergeCell ref="N51:R51"/>
-    <mergeCell ref="B38:G38"/>
-    <mergeCell ref="S51:V51"/>
-    <mergeCell ref="B74:G74"/>
-    <mergeCell ref="I75:M75"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="I87:M87"/>
-    <mergeCell ref="D75:H75"/>
-    <mergeCell ref="I3:M3"/>
-    <mergeCell ref="S3:V3"/>
-    <mergeCell ref="D87:H87"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="B26:G26"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="I39:M39"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="D39:H39"/>
-    <mergeCell ref="B75:B76"/>
-    <mergeCell ref="I63:M63"/>
-    <mergeCell ref="B86:G86"/>
-    <mergeCell ref="N27:R27"/>
-    <mergeCell ref="S15:V15"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="I15:M15"/>
-    <mergeCell ref="B14:G14"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="D63:H63"/>
     <mergeCell ref="N75:R75"/>
     <mergeCell ref="S63:V63"/>
     <mergeCell ref="B39:B40"/>
     <mergeCell ref="C75:C76"/>
+    <mergeCell ref="B38:V38"/>
+    <mergeCell ref="S51:V51"/>
     <mergeCell ref="N3:R3"/>
     <mergeCell ref="S75:V75"/>
     <mergeCell ref="D27:H27"/>
+    <mergeCell ref="I75:M75"/>
+    <mergeCell ref="B15:B16"/>
     <mergeCell ref="N39:R39"/>
+    <mergeCell ref="I87:M87"/>
+    <mergeCell ref="D75:H75"/>
+    <mergeCell ref="B74:V74"/>
     <mergeCell ref="S27:V27"/>
     <mergeCell ref="B87:B88"/>
+    <mergeCell ref="I3:M3"/>
     <mergeCell ref="C51:C52"/>
+    <mergeCell ref="S3:V3"/>
+    <mergeCell ref="D87:H87"/>
     <mergeCell ref="S39:V39"/>
-    <mergeCell ref="B50:G50"/>
-    <mergeCell ref="B62:G62"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="B50:V50"/>
+    <mergeCell ref="I39:M39"/>
+    <mergeCell ref="B26:V26"/>
     <mergeCell ref="D3:H3"/>
+    <mergeCell ref="B63:B64"/>
     <mergeCell ref="N87:R87"/>
+    <mergeCell ref="D39:H39"/>
     <mergeCell ref="B51:B52"/>
     <mergeCell ref="C87:C88"/>
+    <mergeCell ref="B75:B76"/>
+    <mergeCell ref="B62:V62"/>
     <mergeCell ref="I51:M51"/>
+    <mergeCell ref="C3:C4"/>
     <mergeCell ref="D15:H15"/>
-    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="I63:M63"/>
+    <mergeCell ref="S87:V87"/>
     <mergeCell ref="N15:R15"/>
-    <mergeCell ref="S87:V87"/>
     <mergeCell ref="D51:H51"/>
     <mergeCell ref="C15:C16"/>
+    <mergeCell ref="N27:R27"/>
+    <mergeCell ref="S15:V15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10572,9 +10792,22 @@
       <c r="D2" s="70" t="n"/>
       <c r="E2" s="70" t="n"/>
       <c r="F2" s="70" t="n"/>
-      <c r="G2" s="71" t="n"/>
-      <c r="J2" s="5" t="n"/>
-      <c r="K2" s="5" t="n"/>
+      <c r="G2" s="70" t="n"/>
+      <c r="H2" s="70" t="n"/>
+      <c r="I2" s="70" t="n"/>
+      <c r="J2" s="70" t="n"/>
+      <c r="K2" s="70" t="n"/>
+      <c r="L2" s="70" t="n"/>
+      <c r="M2" s="70" t="n"/>
+      <c r="N2" s="70" t="n"/>
+      <c r="O2" s="70" t="n"/>
+      <c r="P2" s="70" t="n"/>
+      <c r="Q2" s="70" t="n"/>
+      <c r="R2" s="70" t="n"/>
+      <c r="S2" s="70" t="n"/>
+      <c r="T2" s="70" t="n"/>
+      <c r="U2" s="70" t="n"/>
+      <c r="V2" s="71" t="n"/>
     </row>
     <row r="3" ht="14.3" customHeight="1" s="33">
       <c r="B3" s="6" t="n"/>
@@ -11006,9 +11239,22 @@
       <c r="D14" s="70" t="n"/>
       <c r="E14" s="70" t="n"/>
       <c r="F14" s="70" t="n"/>
-      <c r="G14" s="71" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="n"/>
+      <c r="G14" s="70" t="n"/>
+      <c r="H14" s="70" t="n"/>
+      <c r="I14" s="70" t="n"/>
+      <c r="J14" s="70" t="n"/>
+      <c r="K14" s="70" t="n"/>
+      <c r="L14" s="70" t="n"/>
+      <c r="M14" s="70" t="n"/>
+      <c r="N14" s="70" t="n"/>
+      <c r="O14" s="70" t="n"/>
+      <c r="P14" s="70" t="n"/>
+      <c r="Q14" s="70" t="n"/>
+      <c r="R14" s="70" t="n"/>
+      <c r="S14" s="70" t="n"/>
+      <c r="T14" s="70" t="n"/>
+      <c r="U14" s="70" t="n"/>
+      <c r="V14" s="71" t="n"/>
     </row>
     <row r="15" ht="14.3" customHeight="1" s="33">
       <c r="B15" s="6" t="n"/>
@@ -11440,9 +11686,22 @@
       <c r="D26" s="70" t="n"/>
       <c r="E26" s="70" t="n"/>
       <c r="F26" s="70" t="n"/>
-      <c r="G26" s="71" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="n"/>
+      <c r="G26" s="70" t="n"/>
+      <c r="H26" s="70" t="n"/>
+      <c r="I26" s="70" t="n"/>
+      <c r="J26" s="70" t="n"/>
+      <c r="K26" s="70" t="n"/>
+      <c r="L26" s="70" t="n"/>
+      <c r="M26" s="70" t="n"/>
+      <c r="N26" s="70" t="n"/>
+      <c r="O26" s="70" t="n"/>
+      <c r="P26" s="70" t="n"/>
+      <c r="Q26" s="70" t="n"/>
+      <c r="R26" s="70" t="n"/>
+      <c r="S26" s="70" t="n"/>
+      <c r="T26" s="70" t="n"/>
+      <c r="U26" s="70" t="n"/>
+      <c r="V26" s="71" t="n"/>
     </row>
     <row r="27" ht="14.3" customHeight="1" s="33">
       <c r="B27" s="6" t="n"/>
@@ -11874,9 +12133,22 @@
       <c r="D38" s="70" t="n"/>
       <c r="E38" s="70" t="n"/>
       <c r="F38" s="70" t="n"/>
-      <c r="G38" s="71" t="n"/>
-      <c r="J38" s="5" t="n"/>
-      <c r="K38" s="5" t="n"/>
+      <c r="G38" s="70" t="n"/>
+      <c r="H38" s="70" t="n"/>
+      <c r="I38" s="70" t="n"/>
+      <c r="J38" s="70" t="n"/>
+      <c r="K38" s="70" t="n"/>
+      <c r="L38" s="70" t="n"/>
+      <c r="M38" s="70" t="n"/>
+      <c r="N38" s="70" t="n"/>
+      <c r="O38" s="70" t="n"/>
+      <c r="P38" s="70" t="n"/>
+      <c r="Q38" s="70" t="n"/>
+      <c r="R38" s="70" t="n"/>
+      <c r="S38" s="70" t="n"/>
+      <c r="T38" s="70" t="n"/>
+      <c r="U38" s="70" t="n"/>
+      <c r="V38" s="71" t="n"/>
     </row>
     <row r="39" ht="14.3" customHeight="1" s="33">
       <c r="B39" s="6" t="n"/>
@@ -12308,9 +12580,22 @@
       <c r="D50" s="70" t="n"/>
       <c r="E50" s="70" t="n"/>
       <c r="F50" s="70" t="n"/>
-      <c r="G50" s="71" t="n"/>
-      <c r="J50" s="5" t="n"/>
-      <c r="K50" s="5" t="n"/>
+      <c r="G50" s="70" t="n"/>
+      <c r="H50" s="70" t="n"/>
+      <c r="I50" s="70" t="n"/>
+      <c r="J50" s="70" t="n"/>
+      <c r="K50" s="70" t="n"/>
+      <c r="L50" s="70" t="n"/>
+      <c r="M50" s="70" t="n"/>
+      <c r="N50" s="70" t="n"/>
+      <c r="O50" s="70" t="n"/>
+      <c r="P50" s="70" t="n"/>
+      <c r="Q50" s="70" t="n"/>
+      <c r="R50" s="70" t="n"/>
+      <c r="S50" s="70" t="n"/>
+      <c r="T50" s="70" t="n"/>
+      <c r="U50" s="70" t="n"/>
+      <c r="V50" s="71" t="n"/>
     </row>
     <row r="51" ht="14.3" customHeight="1" s="33">
       <c r="B51" s="6" t="n"/>
@@ -12620,31 +12905,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B58" s="20" t="inlineStr">
+      <c r="B58" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C58" s="31" t="n"/>
-      <c r="D58" s="31" t="n"/>
-      <c r="E58" s="31" t="n"/>
-      <c r="F58" s="31" t="n"/>
-      <c r="G58" s="31" t="n"/>
-      <c r="H58" s="31" t="n"/>
-      <c r="I58" s="31" t="n"/>
-      <c r="J58" s="31" t="n"/>
-      <c r="K58" s="31" t="n"/>
-      <c r="L58" s="31" t="n"/>
-      <c r="M58" s="31" t="n"/>
-      <c r="N58" s="31" t="n"/>
-      <c r="O58" s="31" t="n"/>
-      <c r="P58" s="31" t="n"/>
-      <c r="Q58" s="31" t="n"/>
-      <c r="R58" s="31" t="n"/>
-      <c r="S58" s="31" t="n"/>
-      <c r="T58" s="31" t="n"/>
-      <c r="U58" s="31" t="n"/>
-      <c r="V58" s="31" t="n"/>
+      <c r="C58" s="80" t="n"/>
+      <c r="D58" s="80" t="n"/>
+      <c r="E58" s="80" t="n"/>
+      <c r="F58" s="80" t="n"/>
+      <c r="G58" s="80" t="n"/>
+      <c r="H58" s="80" t="n"/>
+      <c r="I58" s="80" t="n"/>
+      <c r="J58" s="80" t="n"/>
+      <c r="K58" s="80" t="n"/>
+      <c r="L58" s="80" t="n"/>
+      <c r="M58" s="80" t="n"/>
+      <c r="N58" s="80" t="n"/>
+      <c r="O58" s="80" t="n"/>
+      <c r="P58" s="80" t="n"/>
+      <c r="Q58" s="80" t="n"/>
+      <c r="R58" s="80" t="n"/>
+      <c r="S58" s="80" t="n"/>
+      <c r="T58" s="80" t="n"/>
+      <c r="U58" s="80" t="n"/>
+      <c r="V58" s="80" t="n"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -12742,9 +13027,22 @@
       <c r="D62" s="70" t="n"/>
       <c r="E62" s="70" t="n"/>
       <c r="F62" s="70" t="n"/>
-      <c r="G62" s="71" t="n"/>
-      <c r="J62" s="5" t="n"/>
-      <c r="K62" s="5" t="n"/>
+      <c r="G62" s="70" t="n"/>
+      <c r="H62" s="70" t="n"/>
+      <c r="I62" s="70" t="n"/>
+      <c r="J62" s="70" t="n"/>
+      <c r="K62" s="70" t="n"/>
+      <c r="L62" s="70" t="n"/>
+      <c r="M62" s="70" t="n"/>
+      <c r="N62" s="70" t="n"/>
+      <c r="O62" s="70" t="n"/>
+      <c r="P62" s="70" t="n"/>
+      <c r="Q62" s="70" t="n"/>
+      <c r="R62" s="70" t="n"/>
+      <c r="S62" s="70" t="n"/>
+      <c r="T62" s="70" t="n"/>
+      <c r="U62" s="70" t="n"/>
+      <c r="V62" s="71" t="n"/>
     </row>
     <row r="63" ht="14.3" customHeight="1" s="33">
       <c r="B63" s="6" t="n"/>
@@ -13054,31 +13352,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B70" s="20" t="inlineStr">
+      <c r="B70" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C70" s="21" t="n"/>
-      <c r="D70" s="21" t="n"/>
-      <c r="E70" s="21" t="n"/>
-      <c r="F70" s="21" t="n"/>
-      <c r="G70" s="21" t="n"/>
-      <c r="H70" s="21" t="n"/>
-      <c r="I70" s="21" t="n"/>
-      <c r="J70" s="21" t="n"/>
-      <c r="K70" s="21" t="n"/>
-      <c r="L70" s="21" t="n"/>
-      <c r="M70" s="21" t="n"/>
-      <c r="N70" s="21" t="n"/>
-      <c r="O70" s="21" t="n"/>
-      <c r="P70" s="21" t="n"/>
-      <c r="Q70" s="21" t="n"/>
-      <c r="R70" s="21" t="n"/>
-      <c r="S70" s="21" t="n"/>
-      <c r="T70" s="21" t="n"/>
-      <c r="U70" s="21" t="n"/>
-      <c r="V70" s="21" t="n"/>
+      <c r="C70" s="82" t="n"/>
+      <c r="D70" s="82" t="n"/>
+      <c r="E70" s="82" t="n"/>
+      <c r="F70" s="82" t="n"/>
+      <c r="G70" s="82" t="n"/>
+      <c r="H70" s="82" t="n"/>
+      <c r="I70" s="82" t="n"/>
+      <c r="J70" s="82" t="n"/>
+      <c r="K70" s="82" t="n"/>
+      <c r="L70" s="82" t="n"/>
+      <c r="M70" s="82" t="n"/>
+      <c r="N70" s="82" t="n"/>
+      <c r="O70" s="82" t="n"/>
+      <c r="P70" s="82" t="n"/>
+      <c r="Q70" s="82" t="n"/>
+      <c r="R70" s="82" t="n"/>
+      <c r="S70" s="82" t="n"/>
+      <c r="T70" s="82" t="n"/>
+      <c r="U70" s="82" t="n"/>
+      <c r="V70" s="82" t="n"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -13176,9 +13474,22 @@
       <c r="D74" s="70" t="n"/>
       <c r="E74" s="70" t="n"/>
       <c r="F74" s="70" t="n"/>
-      <c r="G74" s="71" t="n"/>
-      <c r="J74" s="5" t="n"/>
-      <c r="K74" s="5" t="n"/>
+      <c r="G74" s="70" t="n"/>
+      <c r="H74" s="70" t="n"/>
+      <c r="I74" s="70" t="n"/>
+      <c r="J74" s="70" t="n"/>
+      <c r="K74" s="70" t="n"/>
+      <c r="L74" s="70" t="n"/>
+      <c r="M74" s="70" t="n"/>
+      <c r="N74" s="70" t="n"/>
+      <c r="O74" s="70" t="n"/>
+      <c r="P74" s="70" t="n"/>
+      <c r="Q74" s="70" t="n"/>
+      <c r="R74" s="70" t="n"/>
+      <c r="S74" s="70" t="n"/>
+      <c r="T74" s="70" t="n"/>
+      <c r="U74" s="70" t="n"/>
+      <c r="V74" s="71" t="n"/>
     </row>
     <row r="75" ht="14.3" customHeight="1" s="33">
       <c r="B75" s="6" t="n"/>
@@ -13610,9 +13921,22 @@
       <c r="D86" s="70" t="n"/>
       <c r="E86" s="70" t="n"/>
       <c r="F86" s="70" t="n"/>
-      <c r="G86" s="71" t="n"/>
-      <c r="J86" s="5" t="n"/>
-      <c r="K86" s="5" t="n"/>
+      <c r="G86" s="70" t="n"/>
+      <c r="H86" s="70" t="n"/>
+      <c r="I86" s="70" t="n"/>
+      <c r="J86" s="70" t="n"/>
+      <c r="K86" s="70" t="n"/>
+      <c r="L86" s="70" t="n"/>
+      <c r="M86" s="70" t="n"/>
+      <c r="N86" s="70" t="n"/>
+      <c r="O86" s="70" t="n"/>
+      <c r="P86" s="70" t="n"/>
+      <c r="Q86" s="70" t="n"/>
+      <c r="R86" s="70" t="n"/>
+      <c r="S86" s="70" t="n"/>
+      <c r="T86" s="70" t="n"/>
+      <c r="U86" s="70" t="n"/>
+      <c r="V86" s="71" t="n"/>
     </row>
     <row r="87" ht="14.3" customHeight="1" s="33">
       <c r="B87" s="6" t="n"/>
@@ -14036,62 +14360,62 @@
     </row>
   </sheetData>
   <mergeCells count="56">
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="B86:V86"/>
+    <mergeCell ref="B2:V2"/>
+    <mergeCell ref="I15:M15"/>
+    <mergeCell ref="B3:B4"/>
     <mergeCell ref="N63:R63"/>
+    <mergeCell ref="D63:H63"/>
     <mergeCell ref="C63:C64"/>
     <mergeCell ref="I27:M27"/>
+    <mergeCell ref="B14:V14"/>
     <mergeCell ref="N51:R51"/>
-    <mergeCell ref="B38:G38"/>
-    <mergeCell ref="S51:V51"/>
-    <mergeCell ref="B74:G74"/>
-    <mergeCell ref="I75:M75"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="I87:M87"/>
-    <mergeCell ref="D75:H75"/>
-    <mergeCell ref="I3:M3"/>
-    <mergeCell ref="S3:V3"/>
-    <mergeCell ref="D87:H87"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="B26:G26"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="I39:M39"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="D39:H39"/>
-    <mergeCell ref="B75:B76"/>
-    <mergeCell ref="I63:M63"/>
-    <mergeCell ref="B86:G86"/>
-    <mergeCell ref="N27:R27"/>
-    <mergeCell ref="S15:V15"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="I15:M15"/>
-    <mergeCell ref="B14:G14"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="D63:H63"/>
     <mergeCell ref="N75:R75"/>
     <mergeCell ref="S63:V63"/>
     <mergeCell ref="B39:B40"/>
     <mergeCell ref="C75:C76"/>
+    <mergeCell ref="B38:V38"/>
+    <mergeCell ref="S51:V51"/>
     <mergeCell ref="N3:R3"/>
     <mergeCell ref="S75:V75"/>
     <mergeCell ref="D27:H27"/>
+    <mergeCell ref="I75:M75"/>
+    <mergeCell ref="B15:B16"/>
     <mergeCell ref="N39:R39"/>
+    <mergeCell ref="I87:M87"/>
+    <mergeCell ref="D75:H75"/>
+    <mergeCell ref="B74:V74"/>
     <mergeCell ref="S27:V27"/>
     <mergeCell ref="B87:B88"/>
+    <mergeCell ref="I3:M3"/>
     <mergeCell ref="C51:C52"/>
+    <mergeCell ref="S3:V3"/>
+    <mergeCell ref="D87:H87"/>
     <mergeCell ref="S39:V39"/>
-    <mergeCell ref="B50:G50"/>
-    <mergeCell ref="B62:G62"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="B50:V50"/>
+    <mergeCell ref="I39:M39"/>
+    <mergeCell ref="B26:V26"/>
     <mergeCell ref="D3:H3"/>
+    <mergeCell ref="B63:B64"/>
     <mergeCell ref="N87:R87"/>
+    <mergeCell ref="D39:H39"/>
     <mergeCell ref="B51:B52"/>
     <mergeCell ref="C87:C88"/>
+    <mergeCell ref="B75:B76"/>
+    <mergeCell ref="B62:V62"/>
     <mergeCell ref="I51:M51"/>
+    <mergeCell ref="C3:C4"/>
     <mergeCell ref="D15:H15"/>
-    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="I63:M63"/>
+    <mergeCell ref="S87:V87"/>
     <mergeCell ref="N15:R15"/>
-    <mergeCell ref="S87:V87"/>
     <mergeCell ref="D51:H51"/>
     <mergeCell ref="C15:C16"/>
+    <mergeCell ref="N27:R27"/>
+    <mergeCell ref="S15:V15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -14103,7 +14427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:V25"/>
+  <dimension ref="B2:V25"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.12844036697248" defaultRowHeight="14.25"/>
   <cols>
     <col width="16.6238532110092" customWidth="1" style="1" min="2" max="23"/>
@@ -14140,11 +14464,22 @@
       <c r="D2" s="70" t="n"/>
       <c r="E2" s="70" t="n"/>
       <c r="F2" s="70" t="n"/>
-      <c r="G2" s="71" t="n"/>
-      <c r="H2" s="5" t="n"/>
-      <c r="I2" s="5" t="n"/>
-      <c r="J2" s="5" t="n"/>
-      <c r="K2" s="5" t="n"/>
+      <c r="G2" s="70" t="n"/>
+      <c r="H2" s="70" t="n"/>
+      <c r="I2" s="70" t="n"/>
+      <c r="J2" s="70" t="n"/>
+      <c r="K2" s="70" t="n"/>
+      <c r="L2" s="70" t="n"/>
+      <c r="M2" s="70" t="n"/>
+      <c r="N2" s="70" t="n"/>
+      <c r="O2" s="70" t="n"/>
+      <c r="P2" s="70" t="n"/>
+      <c r="Q2" s="70" t="n"/>
+      <c r="R2" s="70" t="n"/>
+      <c r="S2" s="70" t="n"/>
+      <c r="T2" s="70" t="n"/>
+      <c r="U2" s="70" t="n"/>
+      <c r="V2" s="71" t="n"/>
     </row>
     <row r="3">
       <c r="B3" s="6" t="n"/>
@@ -14504,11 +14839,22 @@
       <c r="D14" s="70" t="n"/>
       <c r="E14" s="70" t="n"/>
       <c r="F14" s="70" t="n"/>
-      <c r="G14" s="71" t="n"/>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="n"/>
+      <c r="G14" s="70" t="n"/>
+      <c r="H14" s="70" t="n"/>
+      <c r="I14" s="70" t="n"/>
+      <c r="J14" s="70" t="n"/>
+      <c r="K14" s="70" t="n"/>
+      <c r="L14" s="70" t="n"/>
+      <c r="M14" s="70" t="n"/>
+      <c r="N14" s="70" t="n"/>
+      <c r="O14" s="70" t="n"/>
+      <c r="P14" s="70" t="n"/>
+      <c r="Q14" s="70" t="n"/>
+      <c r="R14" s="70" t="n"/>
+      <c r="S14" s="70" t="n"/>
+      <c r="T14" s="70" t="n"/>
+      <c r="U14" s="70" t="n"/>
+      <c r="V14" s="71" t="n"/>
     </row>
     <row r="15" ht="14.3" customHeight="1" s="33">
       <c r="B15" s="6" t="n"/>
@@ -14861,18 +15207,18 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B2:G2"/>
     <mergeCell ref="I3:M3"/>
+    <mergeCell ref="D15:H15"/>
     <mergeCell ref="S3:V3"/>
+    <mergeCell ref="N3:R3"/>
     <mergeCell ref="I15:M15"/>
-    <mergeCell ref="B14:G14"/>
+    <mergeCell ref="B2:V2"/>
+    <mergeCell ref="C3:C4"/>
     <mergeCell ref="B3:B4"/>
-    <mergeCell ref="D3:H3"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="N3:R3"/>
-    <mergeCell ref="C3:C4"/>
     <mergeCell ref="N15:R15"/>
     <mergeCell ref="C15:C16"/>
+    <mergeCell ref="B14:V14"/>
+    <mergeCell ref="D3:H3"/>
     <mergeCell ref="B15:B16"/>
     <mergeCell ref="S15:V15"/>
   </mergeCells>
@@ -14924,7 +15270,22 @@
       <c r="D2" s="70" t="n"/>
       <c r="E2" s="70" t="n"/>
       <c r="F2" s="70" t="n"/>
-      <c r="G2" s="71" t="n"/>
+      <c r="G2" s="70" t="n"/>
+      <c r="H2" s="70" t="n"/>
+      <c r="I2" s="70" t="n"/>
+      <c r="J2" s="70" t="n"/>
+      <c r="K2" s="70" t="n"/>
+      <c r="L2" s="70" t="n"/>
+      <c r="M2" s="70" t="n"/>
+      <c r="N2" s="70" t="n"/>
+      <c r="O2" s="70" t="n"/>
+      <c r="P2" s="70" t="n"/>
+      <c r="Q2" s="70" t="n"/>
+      <c r="R2" s="70" t="n"/>
+      <c r="S2" s="70" t="n"/>
+      <c r="T2" s="70" t="n"/>
+      <c r="U2" s="70" t="n"/>
+      <c r="V2" s="71" t="n"/>
     </row>
     <row r="3" ht="14.3" customHeight="1" s="33">
       <c r="B3" s="6" t="n"/>
@@ -15081,37 +15442,37 @@
       </c>
       <c r="C5" s="22" t="inlineStr">
         <is>
-          <t>1.8, 10</t>
+          <t>Q1.8, Q10</t>
         </is>
       </c>
       <c r="D5" s="22" t="inlineStr">
         <is>
-          <t>1.10, 11</t>
+          <t>Q1.10, Q11</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
         <is>
-          <t>1.2, 1.3, 2, 3, 4</t>
+          <t>Q1.2, Q1.3, Q2, Q3, Q4</t>
         </is>
       </c>
       <c r="F5" s="22" t="inlineStr">
         <is>
-          <t>1.4, 5</t>
+          <t>Q1.4, Q5</t>
         </is>
       </c>
       <c r="G5" s="22" t="inlineStr">
         <is>
-          <t>1.5, 1.6, 1.7, 6, 7, 8</t>
+          <t>Q1.5, Q1.6, Q1.7, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>Q1.1</t>
         </is>
       </c>
       <c r="I5" s="22" t="inlineStr">
         <is>
-          <t>1.9, 9</t>
+          <t>Q1.9, Q9</t>
         </is>
       </c>
       <c r="J5" s="22" t="n"/>
@@ -15173,37 +15534,37 @@
       </c>
       <c r="C7" s="22" t="inlineStr">
         <is>
-          <t>1.9, 10</t>
+          <t>Q1.9, Q10</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
         <is>
-          <t>1.10, 11</t>
+          <t>Q1.10, Q11</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
         <is>
-          <t>1.2, 1.3, 2, 3, 4</t>
+          <t>Q1.2, Q1.3, Q2, Q3, Q4</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
         <is>
-          <t>1.4, 1.5, 5</t>
+          <t>Q1.4, Q1.5, Q5</t>
         </is>
       </c>
       <c r="G7" s="22" t="inlineStr">
         <is>
-          <t>1.6, 1.7, 6, 7, 8</t>
+          <t>Q1.6, Q1.7, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="H7" s="22" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>Q1.1</t>
         </is>
       </c>
       <c r="I7" s="22" t="inlineStr">
         <is>
-          <t>1.8, 9</t>
+          <t>Q1.8, Q9</t>
         </is>
       </c>
       <c r="J7" s="22" t="n"/>
@@ -15233,32 +15594,34 @@
       </c>
       <c r="C8" s="22" t="inlineStr">
         <is>
-          <t>1.1, 1.7, 10</t>
+          <t>Q1.1, Q1.7, Q10</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
         <is>
-          <t>1.3, 1.6, 11</t>
+          <t>Q1.3, Q1.6, Q11</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
         <is>
-          <t>1.2, 1.4, 1.8, 2, 3, 4</t>
+          <t>Q1.2, Q1.4, Q1.8, Q2, Q3, Q4</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
         <is>
-          <t>1.5, 5</t>
+          <t>Q1.5, Q5</t>
         </is>
       </c>
       <c r="G8" s="22" t="inlineStr">
         <is>
-          <t>1.9, 1.10, 6, 7, 8</t>
+          <t>Q1.9, Q1.10, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="H8" s="22" t="n"/>
-      <c r="I8" s="22" t="n">
-        <v>9</v>
+      <c r="I8" s="22" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
       </c>
       <c r="J8" s="22" t="n"/>
       <c r="K8" s="22" t="n"/>
@@ -15434,7 +15797,22 @@
       <c r="D14" s="70" t="n"/>
       <c r="E14" s="70" t="n"/>
       <c r="F14" s="70" t="n"/>
-      <c r="G14" s="71" t="n"/>
+      <c r="G14" s="70" t="n"/>
+      <c r="H14" s="70" t="n"/>
+      <c r="I14" s="70" t="n"/>
+      <c r="J14" s="70" t="n"/>
+      <c r="K14" s="70" t="n"/>
+      <c r="L14" s="70" t="n"/>
+      <c r="M14" s="70" t="n"/>
+      <c r="N14" s="70" t="n"/>
+      <c r="O14" s="70" t="n"/>
+      <c r="P14" s="70" t="n"/>
+      <c r="Q14" s="70" t="n"/>
+      <c r="R14" s="70" t="n"/>
+      <c r="S14" s="70" t="n"/>
+      <c r="T14" s="70" t="n"/>
+      <c r="U14" s="70" t="n"/>
+      <c r="V14" s="71" t="n"/>
     </row>
     <row r="15" ht="14.3" customHeight="1" s="33">
       <c r="B15" s="6" t="n"/>
@@ -15591,32 +15969,32 @@
       </c>
       <c r="C17" s="22" t="inlineStr">
         <is>
-          <t>1.2, 1.3, 2</t>
+          <t>Q1.2, Q1.3, Q2</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
         <is>
-          <t>1.4, 1.5, 1.6, 1.7,3, 4</t>
+          <t>Q1.4, Q1.5, Q1.6, Q1.7, Q3, Q4</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
         <is>
-          <t>1.8, 7, 8</t>
+          <t>Q1.8, Q7, Q8</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
         <is>
-          <t>1.9, 1.10, 9</t>
+          <t>Q1.9, Q1.10, Q9</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
         <is>
-          <t>5, 6</t>
+          <t>Q5, Q6</t>
         </is>
       </c>
       <c r="H17" s="22" t="inlineStr">
         <is>
-          <t>1.1, 10</t>
+          <t>Q1.1, Q10</t>
         </is>
       </c>
       <c r="I17" s="22" t="n"/>
@@ -15679,32 +16057,32 @@
       </c>
       <c r="C19" s="22" t="inlineStr">
         <is>
-          <t>1.6, 1.8, 2.6, 2.7</t>
+          <t>Q1.6, Q1.8, Q2.6, Q2.7</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
         <is>
-          <t>1.3, 1.4, 1.5, 1.9, 2.1, 3, 4</t>
+          <t>Q1.3, Q1.4, Q1.5, Q1.9, Q2.1, Q3, Q4</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
         <is>
-          <t>5, 7, 8</t>
+          <t>Q5, Q7, Q8</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
         <is>
-          <t>1.7, 6</t>
+          <t>Q1.7, Q6</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>Q1.2</t>
         </is>
       </c>
       <c r="H19" s="22" t="inlineStr">
         <is>
-          <t>1.1, 1.10, 9</t>
+          <t>Q1.1, Q1.10, Q9</t>
         </is>
       </c>
       <c r="I19" s="22" t="n"/>
@@ -15735,30 +16113,32 @@
       </c>
       <c r="C20" s="22" t="inlineStr">
         <is>
-          <t>1.1, 1.6, 2, 3</t>
+          <t>Q1.1, Q1.6, Q2, Q3</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
         <is>
-          <t>1.2, 1.3, 1.5, 1.7, 4, 6</t>
+          <t>Q1.2, Q1.3, Q1.5, Q1.7, Q4, Q6</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
         <is>
-          <t>1.4, 1.9, 7, 8, (9.1-9.2)</t>
+          <t>Q1.4, Q1.9, Q7, Q8, Q9.1-9.2</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
         <is>
-          <t>1.8, 9.3</t>
-        </is>
-      </c>
-      <c r="G20" s="22" t="n">
-        <v>5</v>
+          <t>Q1.8, Q9.3</t>
+        </is>
+      </c>
+      <c r="G20" s="22" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
       </c>
       <c r="H20" s="22" t="inlineStr">
         <is>
-          <t>1.10, 10</t>
+          <t>Q1.10, Q10</t>
         </is>
       </c>
       <c r="I20" s="22" t="n"/>
@@ -15936,7 +16316,22 @@
       <c r="D26" s="70" t="n"/>
       <c r="E26" s="70" t="n"/>
       <c r="F26" s="70" t="n"/>
-      <c r="G26" s="71" t="n"/>
+      <c r="G26" s="70" t="n"/>
+      <c r="H26" s="70" t="n"/>
+      <c r="I26" s="70" t="n"/>
+      <c r="J26" s="70" t="n"/>
+      <c r="K26" s="70" t="n"/>
+      <c r="L26" s="70" t="n"/>
+      <c r="M26" s="70" t="n"/>
+      <c r="N26" s="70" t="n"/>
+      <c r="O26" s="70" t="n"/>
+      <c r="P26" s="70" t="n"/>
+      <c r="Q26" s="70" t="n"/>
+      <c r="R26" s="70" t="n"/>
+      <c r="S26" s="70" t="n"/>
+      <c r="T26" s="70" t="n"/>
+      <c r="U26" s="70" t="n"/>
+      <c r="V26" s="71" t="n"/>
     </row>
     <row r="27" ht="14.3" customHeight="1" s="33">
       <c r="B27" s="6" t="n"/>
@@ -16086,31 +16481,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B29" s="20" t="inlineStr">
+      <c r="B29" s="79" t="inlineStr">
         <is>
           <t>Sept_2015</t>
         </is>
       </c>
-      <c r="C29" s="31" t="n"/>
-      <c r="D29" s="31" t="n"/>
-      <c r="E29" s="31" t="n"/>
-      <c r="F29" s="31" t="n"/>
-      <c r="G29" s="31" t="n"/>
-      <c r="H29" s="31" t="n"/>
-      <c r="I29" s="31" t="n"/>
-      <c r="J29" s="31" t="n"/>
-      <c r="K29" s="31" t="n"/>
-      <c r="L29" s="31" t="n"/>
-      <c r="M29" s="31" t="n"/>
-      <c r="N29" s="31" t="n"/>
-      <c r="O29" s="31" t="n"/>
-      <c r="P29" s="31" t="n"/>
-      <c r="Q29" s="31" t="n"/>
-      <c r="R29" s="31" t="n"/>
-      <c r="S29" s="31" t="n"/>
-      <c r="T29" s="31" t="n"/>
-      <c r="U29" s="31" t="n"/>
-      <c r="V29" s="31" t="n"/>
+      <c r="C29" s="80" t="n"/>
+      <c r="D29" s="80" t="n"/>
+      <c r="E29" s="80" t="n"/>
+      <c r="F29" s="80" t="n"/>
+      <c r="G29" s="80" t="n"/>
+      <c r="H29" s="80" t="n"/>
+      <c r="I29" s="80" t="n"/>
+      <c r="J29" s="80" t="n"/>
+      <c r="K29" s="80" t="n"/>
+      <c r="L29" s="80" t="n"/>
+      <c r="M29" s="80" t="n"/>
+      <c r="N29" s="80" t="n"/>
+      <c r="O29" s="80" t="n"/>
+      <c r="P29" s="80" t="n"/>
+      <c r="Q29" s="80" t="n"/>
+      <c r="R29" s="80" t="n"/>
+      <c r="S29" s="80" t="n"/>
+      <c r="T29" s="80" t="n"/>
+      <c r="U29" s="80" t="n"/>
+      <c r="V29" s="80" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -16125,36 +16520,38 @@
       </c>
       <c r="C30" s="31" t="inlineStr">
         <is>
-          <t>1.9, 10</t>
+          <t>Q1.9, Q10</t>
         </is>
       </c>
       <c r="D30" s="31" t="inlineStr">
         <is>
-          <t>1.10, 11</t>
+          <t>Q1.10, Q11</t>
         </is>
       </c>
       <c r="E30" s="31" t="inlineStr">
         <is>
-          <t>1.2, 1.3, 2, 3, 4</t>
+          <t>Q1.2, Q1.3, Q2, Q3, Q4</t>
         </is>
       </c>
       <c r="F30" s="31" t="inlineStr">
         <is>
-          <t>1.8, 5</t>
+          <t>Q1.8, Q5</t>
         </is>
       </c>
       <c r="G30" s="31" t="inlineStr">
         <is>
-          <t>1.4, 1.5, 1.6, 6, 7, 8</t>
+          <t>Q1.4, Q1.5, Q1.6, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="H30" s="31" t="inlineStr">
         <is>
-          <t>1.1, 1.7</t>
-        </is>
-      </c>
-      <c r="I30" s="31" t="n">
-        <v>9</v>
+          <t>Q1.1, Q1.7</t>
+        </is>
+      </c>
+      <c r="I30" s="31" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
       </c>
       <c r="J30" s="31" t="n"/>
       <c r="K30" s="31" t="n"/>
@@ -16176,31 +16573,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B31" s="20" t="inlineStr">
+      <c r="B31" s="79" t="inlineStr">
         <is>
           <t>Sept_2017</t>
         </is>
       </c>
-      <c r="C31" s="31" t="n"/>
-      <c r="D31" s="31" t="n"/>
-      <c r="E31" s="31" t="n"/>
-      <c r="F31" s="31" t="n"/>
-      <c r="G31" s="31" t="n"/>
-      <c r="H31" s="31" t="n"/>
-      <c r="I31" s="31" t="n"/>
-      <c r="J31" s="31" t="n"/>
-      <c r="K31" s="31" t="n"/>
-      <c r="L31" s="31" t="n"/>
-      <c r="M31" s="31" t="n"/>
-      <c r="N31" s="31" t="n"/>
-      <c r="O31" s="31" t="n"/>
-      <c r="P31" s="31" t="n"/>
-      <c r="Q31" s="31" t="n"/>
-      <c r="R31" s="31" t="n"/>
-      <c r="S31" s="31" t="n"/>
-      <c r="T31" s="31" t="n"/>
-      <c r="U31" s="31" t="n"/>
-      <c r="V31" s="31" t="n"/>
+      <c r="C31" s="80" t="n"/>
+      <c r="D31" s="80" t="n"/>
+      <c r="E31" s="80" t="n"/>
+      <c r="F31" s="80" t="n"/>
+      <c r="G31" s="80" t="n"/>
+      <c r="H31" s="80" t="n"/>
+      <c r="I31" s="80" t="n"/>
+      <c r="J31" s="80" t="n"/>
+      <c r="K31" s="80" t="n"/>
+      <c r="L31" s="80" t="n"/>
+      <c r="M31" s="80" t="n"/>
+      <c r="N31" s="80" t="n"/>
+      <c r="O31" s="80" t="n"/>
+      <c r="P31" s="80" t="n"/>
+      <c r="Q31" s="80" t="n"/>
+      <c r="R31" s="80" t="n"/>
+      <c r="S31" s="80" t="n"/>
+      <c r="T31" s="80" t="n"/>
+      <c r="U31" s="80" t="n"/>
+      <c r="V31" s="80" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -16208,31 +16605,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B32" s="20" t="inlineStr">
+      <c r="B32" s="79" t="inlineStr">
         <is>
           <t>Sept_2018</t>
         </is>
       </c>
-      <c r="C32" s="31" t="n"/>
-      <c r="D32" s="31" t="n"/>
-      <c r="E32" s="31" t="n"/>
-      <c r="F32" s="31" t="n"/>
-      <c r="G32" s="31" t="n"/>
-      <c r="H32" s="31" t="n"/>
-      <c r="I32" s="31" t="n"/>
-      <c r="J32" s="31" t="n"/>
-      <c r="K32" s="31" t="n"/>
-      <c r="L32" s="31" t="n"/>
-      <c r="M32" s="31" t="n"/>
-      <c r="N32" s="31" t="n"/>
-      <c r="O32" s="31" t="n"/>
-      <c r="P32" s="31" t="n"/>
-      <c r="Q32" s="31" t="n"/>
-      <c r="R32" s="31" t="n"/>
-      <c r="S32" s="31" t="n"/>
-      <c r="T32" s="31" t="n"/>
-      <c r="U32" s="31" t="n"/>
-      <c r="V32" s="31" t="n"/>
+      <c r="C32" s="80" t="n"/>
+      <c r="D32" s="80" t="n"/>
+      <c r="E32" s="80" t="n"/>
+      <c r="F32" s="80" t="n"/>
+      <c r="G32" s="80" t="n"/>
+      <c r="H32" s="80" t="n"/>
+      <c r="I32" s="80" t="n"/>
+      <c r="J32" s="80" t="n"/>
+      <c r="K32" s="80" t="n"/>
+      <c r="L32" s="80" t="n"/>
+      <c r="M32" s="80" t="n"/>
+      <c r="N32" s="80" t="n"/>
+      <c r="O32" s="80" t="n"/>
+      <c r="P32" s="80" t="n"/>
+      <c r="Q32" s="80" t="n"/>
+      <c r="R32" s="80" t="n"/>
+      <c r="S32" s="80" t="n"/>
+      <c r="T32" s="80" t="n"/>
+      <c r="U32" s="80" t="n"/>
+      <c r="V32" s="80" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -16240,31 +16637,31 @@
           <t>y</t>
         </is>
       </c>
-      <c r="B33" s="20" t="inlineStr">
+      <c r="B33" s="79" t="inlineStr">
         <is>
           <t>Sept_2019</t>
         </is>
       </c>
-      <c r="C33" s="31" t="n"/>
-      <c r="D33" s="31" t="n"/>
-      <c r="E33" s="31" t="n"/>
-      <c r="F33" s="31" t="n"/>
-      <c r="G33" s="31" t="n"/>
-      <c r="H33" s="31" t="n"/>
-      <c r="I33" s="31" t="n"/>
-      <c r="J33" s="31" t="n"/>
-      <c r="K33" s="31" t="n"/>
-      <c r="L33" s="31" t="n"/>
-      <c r="M33" s="31" t="n"/>
-      <c r="N33" s="31" t="n"/>
-      <c r="O33" s="31" t="n"/>
-      <c r="P33" s="31" t="n"/>
-      <c r="Q33" s="31" t="n"/>
-      <c r="R33" s="31" t="n"/>
-      <c r="S33" s="31" t="n"/>
-      <c r="T33" s="31" t="n"/>
-      <c r="U33" s="31" t="n"/>
-      <c r="V33" s="31" t="n"/>
+      <c r="C33" s="80" t="n"/>
+      <c r="D33" s="80" t="n"/>
+      <c r="E33" s="80" t="n"/>
+      <c r="F33" s="80" t="n"/>
+      <c r="G33" s="80" t="n"/>
+      <c r="H33" s="80" t="n"/>
+      <c r="I33" s="80" t="n"/>
+      <c r="J33" s="80" t="n"/>
+      <c r="K33" s="80" t="n"/>
+      <c r="L33" s="80" t="n"/>
+      <c r="M33" s="80" t="n"/>
+      <c r="N33" s="80" t="n"/>
+      <c r="O33" s="80" t="n"/>
+      <c r="P33" s="80" t="n"/>
+      <c r="Q33" s="80" t="n"/>
+      <c r="R33" s="80" t="n"/>
+      <c r="S33" s="80" t="n"/>
+      <c r="T33" s="80" t="n"/>
+      <c r="U33" s="80" t="n"/>
+      <c r="V33" s="80" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -16272,31 +16669,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B34" s="20" t="inlineStr">
+      <c r="B34" s="79" t="inlineStr">
         <is>
           <t>Sept_2020</t>
         </is>
       </c>
-      <c r="C34" s="31" t="n"/>
-      <c r="D34" s="31" t="n"/>
-      <c r="E34" s="31" t="n"/>
-      <c r="F34" s="31" t="n"/>
-      <c r="G34" s="31" t="n"/>
-      <c r="H34" s="31" t="n"/>
-      <c r="I34" s="31" t="n"/>
-      <c r="J34" s="31" t="n"/>
-      <c r="K34" s="31" t="n"/>
-      <c r="L34" s="31" t="n"/>
-      <c r="M34" s="31" t="n"/>
-      <c r="N34" s="31" t="n"/>
-      <c r="O34" s="31" t="n"/>
-      <c r="P34" s="31" t="n"/>
-      <c r="Q34" s="31" t="n"/>
-      <c r="R34" s="31" t="n"/>
-      <c r="S34" s="31" t="n"/>
-      <c r="T34" s="31" t="n"/>
-      <c r="U34" s="31" t="n"/>
-      <c r="V34" s="31" t="n"/>
+      <c r="C34" s="80" t="n"/>
+      <c r="D34" s="80" t="n"/>
+      <c r="E34" s="80" t="n"/>
+      <c r="F34" s="80" t="n"/>
+      <c r="G34" s="80" t="n"/>
+      <c r="H34" s="80" t="n"/>
+      <c r="I34" s="80" t="n"/>
+      <c r="J34" s="80" t="n"/>
+      <c r="K34" s="80" t="n"/>
+      <c r="L34" s="80" t="n"/>
+      <c r="M34" s="80" t="n"/>
+      <c r="N34" s="80" t="n"/>
+      <c r="O34" s="80" t="n"/>
+      <c r="P34" s="80" t="n"/>
+      <c r="Q34" s="80" t="n"/>
+      <c r="R34" s="80" t="n"/>
+      <c r="S34" s="80" t="n"/>
+      <c r="T34" s="80" t="n"/>
+      <c r="U34" s="80" t="n"/>
+      <c r="V34" s="80" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -16304,31 +16701,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B35" s="20" t="inlineStr">
+      <c r="B35" s="79" t="inlineStr">
         <is>
           <t>Sept_2021</t>
         </is>
       </c>
-      <c r="C35" s="31" t="n"/>
-      <c r="D35" s="31" t="n"/>
-      <c r="E35" s="31" t="n"/>
-      <c r="F35" s="31" t="n"/>
-      <c r="G35" s="31" t="n"/>
-      <c r="H35" s="31" t="n"/>
-      <c r="I35" s="31" t="n"/>
-      <c r="J35" s="31" t="n"/>
-      <c r="K35" s="31" t="n"/>
-      <c r="L35" s="31" t="n"/>
-      <c r="M35" s="31" t="n"/>
-      <c r="N35" s="31" t="n"/>
-      <c r="O35" s="31" t="n"/>
-      <c r="P35" s="31" t="n"/>
-      <c r="Q35" s="31" t="n"/>
-      <c r="R35" s="31" t="n"/>
-      <c r="S35" s="31" t="n"/>
-      <c r="T35" s="31" t="n"/>
-      <c r="U35" s="31" t="n"/>
-      <c r="V35" s="31" t="n"/>
+      <c r="C35" s="80" t="n"/>
+      <c r="D35" s="80" t="n"/>
+      <c r="E35" s="80" t="n"/>
+      <c r="F35" s="80" t="n"/>
+      <c r="G35" s="80" t="n"/>
+      <c r="H35" s="80" t="n"/>
+      <c r="I35" s="80" t="n"/>
+      <c r="J35" s="80" t="n"/>
+      <c r="K35" s="80" t="n"/>
+      <c r="L35" s="80" t="n"/>
+      <c r="M35" s="80" t="n"/>
+      <c r="N35" s="80" t="n"/>
+      <c r="O35" s="80" t="n"/>
+      <c r="P35" s="80" t="n"/>
+      <c r="Q35" s="80" t="n"/>
+      <c r="R35" s="80" t="n"/>
+      <c r="S35" s="80" t="n"/>
+      <c r="T35" s="80" t="n"/>
+      <c r="U35" s="80" t="n"/>
+      <c r="V35" s="80" t="n"/>
     </row>
     <row r="36" ht="15" customHeight="1" s="33">
       <c r="A36" t="inlineStr">
@@ -16336,31 +16733,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B36" s="28" t="inlineStr">
+      <c r="B36" s="81" t="inlineStr">
         <is>
           <t>Sept_2022</t>
         </is>
       </c>
-      <c r="C36" s="31" t="n"/>
-      <c r="D36" s="31" t="n"/>
-      <c r="E36" s="31" t="n"/>
-      <c r="F36" s="31" t="n"/>
-      <c r="G36" s="31" t="n"/>
-      <c r="H36" s="31" t="n"/>
-      <c r="I36" s="31" t="n"/>
-      <c r="J36" s="31" t="n"/>
-      <c r="K36" s="31" t="n"/>
-      <c r="L36" s="31" t="n"/>
-      <c r="M36" s="31" t="n"/>
-      <c r="N36" s="31" t="n"/>
-      <c r="O36" s="31" t="n"/>
-      <c r="P36" s="31" t="n"/>
-      <c r="Q36" s="31" t="n"/>
-      <c r="R36" s="31" t="n"/>
-      <c r="S36" s="31" t="n"/>
-      <c r="T36" s="31" t="n"/>
-      <c r="U36" s="31" t="n"/>
-      <c r="V36" s="31" t="n"/>
+      <c r="C36" s="80" t="n"/>
+      <c r="D36" s="80" t="n"/>
+      <c r="E36" s="80" t="n"/>
+      <c r="F36" s="80" t="n"/>
+      <c r="G36" s="80" t="n"/>
+      <c r="H36" s="80" t="n"/>
+      <c r="I36" s="80" t="n"/>
+      <c r="J36" s="80" t="n"/>
+      <c r="K36" s="80" t="n"/>
+      <c r="L36" s="80" t="n"/>
+      <c r="M36" s="80" t="n"/>
+      <c r="N36" s="80" t="n"/>
+      <c r="O36" s="80" t="n"/>
+      <c r="P36" s="80" t="n"/>
+      <c r="Q36" s="80" t="n"/>
+      <c r="R36" s="80" t="n"/>
+      <c r="S36" s="80" t="n"/>
+      <c r="T36" s="80" t="n"/>
+      <c r="U36" s="80" t="n"/>
+      <c r="V36" s="80" t="n"/>
     </row>
     <row r="37" ht="15" customHeight="1" s="33">
       <c r="C37" s="31" t="n"/>
@@ -16394,7 +16791,22 @@
       <c r="D38" s="70" t="n"/>
       <c r="E38" s="70" t="n"/>
       <c r="F38" s="70" t="n"/>
-      <c r="G38" s="71" t="n"/>
+      <c r="G38" s="70" t="n"/>
+      <c r="H38" s="70" t="n"/>
+      <c r="I38" s="70" t="n"/>
+      <c r="J38" s="70" t="n"/>
+      <c r="K38" s="70" t="n"/>
+      <c r="L38" s="70" t="n"/>
+      <c r="M38" s="70" t="n"/>
+      <c r="N38" s="70" t="n"/>
+      <c r="O38" s="70" t="n"/>
+      <c r="P38" s="70" t="n"/>
+      <c r="Q38" s="70" t="n"/>
+      <c r="R38" s="70" t="n"/>
+      <c r="S38" s="70" t="n"/>
+      <c r="T38" s="70" t="n"/>
+      <c r="U38" s="70" t="n"/>
+      <c r="V38" s="71" t="n"/>
     </row>
     <row r="39" ht="14.3" customHeight="1" s="33">
       <c r="B39" s="6" t="n"/>
@@ -16544,31 +16956,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B41" s="20" t="inlineStr">
+      <c r="B41" s="79" t="inlineStr">
         <is>
           <t>Sept_2015</t>
         </is>
       </c>
-      <c r="C41" s="21" t="n"/>
-      <c r="D41" s="21" t="n"/>
-      <c r="E41" s="21" t="n"/>
-      <c r="F41" s="21" t="n"/>
-      <c r="G41" s="21" t="n"/>
-      <c r="H41" s="21" t="n"/>
-      <c r="I41" s="21" t="n"/>
-      <c r="J41" s="21" t="n"/>
-      <c r="K41" s="21" t="n"/>
-      <c r="L41" s="21" t="n"/>
-      <c r="M41" s="21" t="n"/>
-      <c r="N41" s="21" t="n"/>
-      <c r="O41" s="21" t="n"/>
-      <c r="P41" s="21" t="n"/>
-      <c r="Q41" s="21" t="n"/>
-      <c r="R41" s="21" t="n"/>
-      <c r="S41" s="21" t="n"/>
-      <c r="T41" s="21" t="n"/>
-      <c r="U41" s="21" t="n"/>
-      <c r="V41" s="21" t="n"/>
+      <c r="C41" s="82" t="n"/>
+      <c r="D41" s="82" t="n"/>
+      <c r="E41" s="82" t="n"/>
+      <c r="F41" s="82" t="n"/>
+      <c r="G41" s="82" t="n"/>
+      <c r="H41" s="82" t="n"/>
+      <c r="I41" s="82" t="n"/>
+      <c r="J41" s="82" t="n"/>
+      <c r="K41" s="82" t="n"/>
+      <c r="L41" s="82" t="n"/>
+      <c r="M41" s="82" t="n"/>
+      <c r="N41" s="82" t="n"/>
+      <c r="O41" s="82" t="n"/>
+      <c r="P41" s="82" t="n"/>
+      <c r="Q41" s="82" t="n"/>
+      <c r="R41" s="82" t="n"/>
+      <c r="S41" s="82" t="n"/>
+      <c r="T41" s="82" t="n"/>
+      <c r="U41" s="82" t="n"/>
+      <c r="V41" s="82" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -16583,28 +16995,28 @@
       </c>
       <c r="C42" s="21" t="inlineStr">
         <is>
-          <t>1.2, 1.3, 2, 3</t>
+          <t>Q1.2, Q1.3, Q2, Q3</t>
         </is>
       </c>
       <c r="D42" s="21" t="inlineStr">
         <is>
-          <t>1.1, 1.4, 1.5, 1.6, 1.7, 1.9, 4, 5</t>
+          <t>Q1.1, Q1.4, Q1.5, Q1.6, Q1.7, Q1.9, Q4, Q5</t>
         </is>
       </c>
       <c r="E42" s="21" t="inlineStr">
         <is>
-          <t>7 ,(10.1-10.2)</t>
+          <t>Q7, Q10.1-10.2</t>
         </is>
       </c>
       <c r="F42" s="21" t="inlineStr">
         <is>
-          <t>1.8, 6, 8, 9</t>
+          <t>Q1.8, Q6, Q8, Q9</t>
         </is>
       </c>
       <c r="G42" s="21" t="n"/>
       <c r="H42" s="21" t="inlineStr">
         <is>
-          <t>1.10, (10.3-10.5)</t>
+          <t>Q1.10, Q10.3-10.5</t>
         </is>
       </c>
       <c r="I42" s="21" t="n"/>
@@ -16628,31 +17040,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B43" s="20" t="inlineStr">
+      <c r="B43" s="79" t="inlineStr">
         <is>
           <t>Sept_2017</t>
         </is>
       </c>
-      <c r="C43" s="21" t="n"/>
-      <c r="D43" s="21" t="n"/>
-      <c r="E43" s="21" t="n"/>
-      <c r="F43" s="21" t="n"/>
-      <c r="G43" s="21" t="n"/>
-      <c r="H43" s="21" t="n"/>
-      <c r="I43" s="21" t="n"/>
-      <c r="J43" s="21" t="n"/>
-      <c r="K43" s="21" t="n"/>
-      <c r="L43" s="21" t="n"/>
-      <c r="M43" s="21" t="n"/>
-      <c r="N43" s="21" t="n"/>
-      <c r="O43" s="21" t="n"/>
-      <c r="P43" s="21" t="n"/>
-      <c r="Q43" s="21" t="n"/>
-      <c r="R43" s="21" t="n"/>
-      <c r="S43" s="21" t="n"/>
-      <c r="T43" s="21" t="n"/>
-      <c r="U43" s="21" t="n"/>
-      <c r="V43" s="21" t="n"/>
+      <c r="C43" s="82" t="n"/>
+      <c r="D43" s="82" t="n"/>
+      <c r="E43" s="82" t="n"/>
+      <c r="F43" s="82" t="n"/>
+      <c r="G43" s="82" t="n"/>
+      <c r="H43" s="82" t="n"/>
+      <c r="I43" s="82" t="n"/>
+      <c r="J43" s="82" t="n"/>
+      <c r="K43" s="82" t="n"/>
+      <c r="L43" s="82" t="n"/>
+      <c r="M43" s="82" t="n"/>
+      <c r="N43" s="82" t="n"/>
+      <c r="O43" s="82" t="n"/>
+      <c r="P43" s="82" t="n"/>
+      <c r="Q43" s="82" t="n"/>
+      <c r="R43" s="82" t="n"/>
+      <c r="S43" s="82" t="n"/>
+      <c r="T43" s="82" t="n"/>
+      <c r="U43" s="82" t="n"/>
+      <c r="V43" s="82" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -16660,31 +17072,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B44" s="20" t="inlineStr">
+      <c r="B44" s="79" t="inlineStr">
         <is>
           <t>Sept_2018</t>
         </is>
       </c>
-      <c r="C44" s="21" t="n"/>
-      <c r="D44" s="21" t="n"/>
-      <c r="E44" s="21" t="n"/>
-      <c r="F44" s="21" t="n"/>
-      <c r="G44" s="21" t="n"/>
-      <c r="H44" s="21" t="n"/>
-      <c r="I44" s="21" t="n"/>
-      <c r="J44" s="21" t="n"/>
-      <c r="K44" s="21" t="n"/>
-      <c r="L44" s="21" t="n"/>
-      <c r="M44" s="21" t="n"/>
-      <c r="N44" s="21" t="n"/>
-      <c r="O44" s="21" t="n"/>
-      <c r="P44" s="21" t="n"/>
-      <c r="Q44" s="21" t="n"/>
-      <c r="R44" s="21" t="n"/>
-      <c r="S44" s="21" t="n"/>
-      <c r="T44" s="21" t="n"/>
-      <c r="U44" s="21" t="n"/>
-      <c r="V44" s="21" t="n"/>
+      <c r="C44" s="82" t="n"/>
+      <c r="D44" s="82" t="n"/>
+      <c r="E44" s="82" t="n"/>
+      <c r="F44" s="82" t="n"/>
+      <c r="G44" s="82" t="n"/>
+      <c r="H44" s="82" t="n"/>
+      <c r="I44" s="82" t="n"/>
+      <c r="J44" s="82" t="n"/>
+      <c r="K44" s="82" t="n"/>
+      <c r="L44" s="82" t="n"/>
+      <c r="M44" s="82" t="n"/>
+      <c r="N44" s="82" t="n"/>
+      <c r="O44" s="82" t="n"/>
+      <c r="P44" s="82" t="n"/>
+      <c r="Q44" s="82" t="n"/>
+      <c r="R44" s="82" t="n"/>
+      <c r="S44" s="82" t="n"/>
+      <c r="T44" s="82" t="n"/>
+      <c r="U44" s="82" t="n"/>
+      <c r="V44" s="82" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -16692,31 +17104,31 @@
           <t>y</t>
         </is>
       </c>
-      <c r="B45" s="20" t="inlineStr">
+      <c r="B45" s="79" t="inlineStr">
         <is>
           <t>Sept_2019</t>
         </is>
       </c>
-      <c r="C45" s="21" t="n"/>
-      <c r="D45" s="21" t="n"/>
-      <c r="E45" s="21" t="n"/>
-      <c r="F45" s="21" t="n"/>
-      <c r="G45" s="21" t="n"/>
-      <c r="H45" s="21" t="n"/>
-      <c r="I45" s="21" t="n"/>
-      <c r="J45" s="21" t="n"/>
-      <c r="K45" s="21" t="n"/>
-      <c r="L45" s="21" t="n"/>
-      <c r="M45" s="21" t="n"/>
-      <c r="N45" s="21" t="n"/>
-      <c r="O45" s="21" t="n"/>
-      <c r="P45" s="21" t="n"/>
-      <c r="Q45" s="21" t="n"/>
-      <c r="R45" s="21" t="n"/>
-      <c r="S45" s="21" t="n"/>
-      <c r="T45" s="21" t="n"/>
-      <c r="U45" s="21" t="n"/>
-      <c r="V45" s="21" t="n"/>
+      <c r="C45" s="82" t="n"/>
+      <c r="D45" s="82" t="n"/>
+      <c r="E45" s="82" t="n"/>
+      <c r="F45" s="82" t="n"/>
+      <c r="G45" s="82" t="n"/>
+      <c r="H45" s="82" t="n"/>
+      <c r="I45" s="82" t="n"/>
+      <c r="J45" s="82" t="n"/>
+      <c r="K45" s="82" t="n"/>
+      <c r="L45" s="82" t="n"/>
+      <c r="M45" s="82" t="n"/>
+      <c r="N45" s="82" t="n"/>
+      <c r="O45" s="82" t="n"/>
+      <c r="P45" s="82" t="n"/>
+      <c r="Q45" s="82" t="n"/>
+      <c r="R45" s="82" t="n"/>
+      <c r="S45" s="82" t="n"/>
+      <c r="T45" s="82" t="n"/>
+      <c r="U45" s="82" t="n"/>
+      <c r="V45" s="82" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -16724,31 +17136,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B46" s="20" t="inlineStr">
+      <c r="B46" s="79" t="inlineStr">
         <is>
           <t>Sept_2020</t>
         </is>
       </c>
-      <c r="C46" s="21" t="n"/>
-      <c r="D46" s="21" t="n"/>
-      <c r="E46" s="21" t="n"/>
-      <c r="F46" s="21" t="n"/>
-      <c r="G46" s="21" t="n"/>
-      <c r="H46" s="21" t="n"/>
-      <c r="I46" s="21" t="n"/>
-      <c r="J46" s="21" t="n"/>
-      <c r="K46" s="21" t="n"/>
-      <c r="L46" s="21" t="n"/>
-      <c r="M46" s="21" t="n"/>
-      <c r="N46" s="21" t="n"/>
-      <c r="O46" s="21" t="n"/>
-      <c r="P46" s="21" t="n"/>
-      <c r="Q46" s="21" t="n"/>
-      <c r="R46" s="21" t="n"/>
-      <c r="S46" s="21" t="n"/>
-      <c r="T46" s="21" t="n"/>
-      <c r="U46" s="21" t="n"/>
-      <c r="V46" s="21" t="n"/>
+      <c r="C46" s="82" t="n"/>
+      <c r="D46" s="82" t="n"/>
+      <c r="E46" s="82" t="n"/>
+      <c r="F46" s="82" t="n"/>
+      <c r="G46" s="82" t="n"/>
+      <c r="H46" s="82" t="n"/>
+      <c r="I46" s="82" t="n"/>
+      <c r="J46" s="82" t="n"/>
+      <c r="K46" s="82" t="n"/>
+      <c r="L46" s="82" t="n"/>
+      <c r="M46" s="82" t="n"/>
+      <c r="N46" s="82" t="n"/>
+      <c r="O46" s="82" t="n"/>
+      <c r="P46" s="82" t="n"/>
+      <c r="Q46" s="82" t="n"/>
+      <c r="R46" s="82" t="n"/>
+      <c r="S46" s="82" t="n"/>
+      <c r="T46" s="82" t="n"/>
+      <c r="U46" s="82" t="n"/>
+      <c r="V46" s="82" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -16756,31 +17168,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B47" s="20" t="inlineStr">
+      <c r="B47" s="79" t="inlineStr">
         <is>
           <t>Sept_2021</t>
         </is>
       </c>
-      <c r="C47" s="21" t="n"/>
-      <c r="D47" s="21" t="n"/>
-      <c r="E47" s="21" t="n"/>
-      <c r="F47" s="21" t="n"/>
-      <c r="G47" s="21" t="n"/>
-      <c r="H47" s="21" t="n"/>
-      <c r="I47" s="21" t="n"/>
-      <c r="J47" s="21" t="n"/>
-      <c r="K47" s="21" t="n"/>
-      <c r="L47" s="21" t="n"/>
-      <c r="M47" s="21" t="n"/>
-      <c r="N47" s="21" t="n"/>
-      <c r="O47" s="21" t="n"/>
-      <c r="P47" s="21" t="n"/>
-      <c r="Q47" s="21" t="n"/>
-      <c r="R47" s="21" t="n"/>
-      <c r="S47" s="21" t="n"/>
-      <c r="T47" s="21" t="n"/>
-      <c r="U47" s="21" t="n"/>
-      <c r="V47" s="21" t="n"/>
+      <c r="C47" s="82" t="n"/>
+      <c r="D47" s="82" t="n"/>
+      <c r="E47" s="82" t="n"/>
+      <c r="F47" s="82" t="n"/>
+      <c r="G47" s="82" t="n"/>
+      <c r="H47" s="82" t="n"/>
+      <c r="I47" s="82" t="n"/>
+      <c r="J47" s="82" t="n"/>
+      <c r="K47" s="82" t="n"/>
+      <c r="L47" s="82" t="n"/>
+      <c r="M47" s="82" t="n"/>
+      <c r="N47" s="82" t="n"/>
+      <c r="O47" s="82" t="n"/>
+      <c r="P47" s="82" t="n"/>
+      <c r="Q47" s="82" t="n"/>
+      <c r="R47" s="82" t="n"/>
+      <c r="S47" s="82" t="n"/>
+      <c r="T47" s="82" t="n"/>
+      <c r="U47" s="82" t="n"/>
+      <c r="V47" s="82" t="n"/>
     </row>
     <row r="48" ht="15" customHeight="1" s="33">
       <c r="A48" t="inlineStr">
@@ -16788,31 +17200,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B48" s="28" t="inlineStr">
+      <c r="B48" s="81" t="inlineStr">
         <is>
           <t>Sept_2022</t>
         </is>
       </c>
-      <c r="C48" s="21" t="n"/>
-      <c r="D48" s="21" t="n"/>
-      <c r="E48" s="21" t="n"/>
-      <c r="F48" s="21" t="n"/>
-      <c r="G48" s="21" t="n"/>
-      <c r="H48" s="21" t="n"/>
-      <c r="I48" s="21" t="n"/>
-      <c r="J48" s="21" t="n"/>
-      <c r="K48" s="21" t="n"/>
-      <c r="L48" s="21" t="n"/>
-      <c r="M48" s="21" t="n"/>
-      <c r="N48" s="21" t="n"/>
-      <c r="O48" s="21" t="n"/>
-      <c r="P48" s="21" t="n"/>
-      <c r="Q48" s="21" t="n"/>
-      <c r="R48" s="21" t="n"/>
-      <c r="S48" s="21" t="n"/>
-      <c r="T48" s="21" t="n"/>
-      <c r="U48" s="21" t="n"/>
-      <c r="V48" s="21" t="n"/>
+      <c r="C48" s="82" t="n"/>
+      <c r="D48" s="82" t="n"/>
+      <c r="E48" s="82" t="n"/>
+      <c r="F48" s="82" t="n"/>
+      <c r="G48" s="82" t="n"/>
+      <c r="H48" s="82" t="n"/>
+      <c r="I48" s="82" t="n"/>
+      <c r="J48" s="82" t="n"/>
+      <c r="K48" s="82" t="n"/>
+      <c r="L48" s="82" t="n"/>
+      <c r="M48" s="82" t="n"/>
+      <c r="N48" s="82" t="n"/>
+      <c r="O48" s="82" t="n"/>
+      <c r="P48" s="82" t="n"/>
+      <c r="Q48" s="82" t="n"/>
+      <c r="R48" s="82" t="n"/>
+      <c r="S48" s="82" t="n"/>
+      <c r="T48" s="82" t="n"/>
+      <c r="U48" s="82" t="n"/>
+      <c r="V48" s="82" t="n"/>
     </row>
     <row r="49" ht="15" customHeight="1" s="33">
       <c r="C49" s="21" t="n"/>
@@ -16846,7 +17258,22 @@
       <c r="D50" s="70" t="n"/>
       <c r="E50" s="70" t="n"/>
       <c r="F50" s="70" t="n"/>
-      <c r="G50" s="71" t="n"/>
+      <c r="G50" s="70" t="n"/>
+      <c r="H50" s="70" t="n"/>
+      <c r="I50" s="70" t="n"/>
+      <c r="J50" s="70" t="n"/>
+      <c r="K50" s="70" t="n"/>
+      <c r="L50" s="70" t="n"/>
+      <c r="M50" s="70" t="n"/>
+      <c r="N50" s="70" t="n"/>
+      <c r="O50" s="70" t="n"/>
+      <c r="P50" s="70" t="n"/>
+      <c r="Q50" s="70" t="n"/>
+      <c r="R50" s="70" t="n"/>
+      <c r="S50" s="70" t="n"/>
+      <c r="T50" s="70" t="n"/>
+      <c r="U50" s="70" t="n"/>
+      <c r="V50" s="71" t="n"/>
     </row>
     <row r="51" ht="14.3" customHeight="1" s="33">
       <c r="B51" s="6" t="n"/>
@@ -16996,31 +17423,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B53" s="20" t="inlineStr">
+      <c r="B53" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2015</t>
         </is>
       </c>
-      <c r="C53" s="31" t="n"/>
-      <c r="D53" s="31" t="n"/>
-      <c r="E53" s="31" t="n"/>
-      <c r="F53" s="31" t="n"/>
-      <c r="G53" s="31" t="n"/>
-      <c r="H53" s="31" t="n"/>
-      <c r="I53" s="31" t="n"/>
-      <c r="J53" s="31" t="n"/>
-      <c r="K53" s="31" t="n"/>
-      <c r="L53" s="31" t="n"/>
-      <c r="M53" s="31" t="n"/>
-      <c r="N53" s="31" t="n"/>
-      <c r="O53" s="31" t="n"/>
-      <c r="P53" s="31" t="n"/>
-      <c r="Q53" s="31" t="n"/>
-      <c r="R53" s="31" t="n"/>
-      <c r="S53" s="31" t="n"/>
-      <c r="T53" s="31" t="n"/>
-      <c r="U53" s="31" t="n"/>
-      <c r="V53" s="31" t="n"/>
+      <c r="C53" s="80" t="n"/>
+      <c r="D53" s="80" t="n"/>
+      <c r="E53" s="80" t="n"/>
+      <c r="F53" s="80" t="n"/>
+      <c r="G53" s="80" t="n"/>
+      <c r="H53" s="80" t="n"/>
+      <c r="I53" s="80" t="n"/>
+      <c r="J53" s="80" t="n"/>
+      <c r="K53" s="80" t="n"/>
+      <c r="L53" s="80" t="n"/>
+      <c r="M53" s="80" t="n"/>
+      <c r="N53" s="80" t="n"/>
+      <c r="O53" s="80" t="n"/>
+      <c r="P53" s="80" t="n"/>
+      <c r="Q53" s="80" t="n"/>
+      <c r="R53" s="80" t="n"/>
+      <c r="S53" s="80" t="n"/>
+      <c r="T53" s="80" t="n"/>
+      <c r="U53" s="80" t="n"/>
+      <c r="V53" s="80" t="n"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -17028,31 +17455,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B54" s="20" t="inlineStr">
+      <c r="B54" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2016</t>
         </is>
       </c>
-      <c r="C54" s="31" t="n"/>
-      <c r="D54" s="31" t="n"/>
-      <c r="E54" s="31" t="n"/>
-      <c r="F54" s="31" t="n"/>
-      <c r="G54" s="31" t="n"/>
-      <c r="H54" s="31" t="n"/>
-      <c r="I54" s="31" t="n"/>
-      <c r="J54" s="31" t="n"/>
-      <c r="K54" s="31" t="n"/>
-      <c r="L54" s="31" t="n"/>
-      <c r="M54" s="31" t="n"/>
-      <c r="N54" s="31" t="n"/>
-      <c r="O54" s="31" t="n"/>
-      <c r="P54" s="31" t="n"/>
-      <c r="Q54" s="31" t="n"/>
-      <c r="R54" s="31" t="n"/>
-      <c r="S54" s="31" t="n"/>
-      <c r="T54" s="31" t="n"/>
-      <c r="U54" s="31" t="n"/>
-      <c r="V54" s="31" t="n"/>
+      <c r="C54" s="80" t="n"/>
+      <c r="D54" s="80" t="n"/>
+      <c r="E54" s="80" t="n"/>
+      <c r="F54" s="80" t="n"/>
+      <c r="G54" s="80" t="n"/>
+      <c r="H54" s="80" t="n"/>
+      <c r="I54" s="80" t="n"/>
+      <c r="J54" s="80" t="n"/>
+      <c r="K54" s="80" t="n"/>
+      <c r="L54" s="80" t="n"/>
+      <c r="M54" s="80" t="n"/>
+      <c r="N54" s="80" t="n"/>
+      <c r="O54" s="80" t="n"/>
+      <c r="P54" s="80" t="n"/>
+      <c r="Q54" s="80" t="n"/>
+      <c r="R54" s="80" t="n"/>
+      <c r="S54" s="80" t="n"/>
+      <c r="T54" s="80" t="n"/>
+      <c r="U54" s="80" t="n"/>
+      <c r="V54" s="80" t="n"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -17060,31 +17487,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B55" s="20" t="inlineStr">
+      <c r="B55" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2017</t>
         </is>
       </c>
-      <c r="C55" s="31" t="n"/>
-      <c r="D55" s="31" t="n"/>
-      <c r="E55" s="31" t="n"/>
-      <c r="F55" s="31" t="n"/>
-      <c r="G55" s="31" t="n"/>
-      <c r="H55" s="31" t="n"/>
-      <c r="I55" s="31" t="n"/>
-      <c r="J55" s="31" t="n"/>
-      <c r="K55" s="31" t="n"/>
-      <c r="L55" s="31" t="n"/>
-      <c r="M55" s="31" t="n"/>
-      <c r="N55" s="31" t="n"/>
-      <c r="O55" s="31" t="n"/>
-      <c r="P55" s="31" t="n"/>
-      <c r="Q55" s="31" t="n"/>
-      <c r="R55" s="31" t="n"/>
-      <c r="S55" s="31" t="n"/>
-      <c r="T55" s="31" t="n"/>
-      <c r="U55" s="31" t="n"/>
-      <c r="V55" s="31" t="n"/>
+      <c r="C55" s="80" t="n"/>
+      <c r="D55" s="80" t="n"/>
+      <c r="E55" s="80" t="n"/>
+      <c r="F55" s="80" t="n"/>
+      <c r="G55" s="80" t="n"/>
+      <c r="H55" s="80" t="n"/>
+      <c r="I55" s="80" t="n"/>
+      <c r="J55" s="80" t="n"/>
+      <c r="K55" s="80" t="n"/>
+      <c r="L55" s="80" t="n"/>
+      <c r="M55" s="80" t="n"/>
+      <c r="N55" s="80" t="n"/>
+      <c r="O55" s="80" t="n"/>
+      <c r="P55" s="80" t="n"/>
+      <c r="Q55" s="80" t="n"/>
+      <c r="R55" s="80" t="n"/>
+      <c r="S55" s="80" t="n"/>
+      <c r="T55" s="80" t="n"/>
+      <c r="U55" s="80" t="n"/>
+      <c r="V55" s="80" t="n"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -17092,31 +17519,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B56" s="20" t="inlineStr">
+      <c r="B56" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2018</t>
         </is>
       </c>
-      <c r="C56" s="31" t="n"/>
-      <c r="D56" s="31" t="n"/>
-      <c r="E56" s="31" t="n"/>
-      <c r="F56" s="31" t="n"/>
-      <c r="G56" s="31" t="n"/>
-      <c r="H56" s="31" t="n"/>
-      <c r="I56" s="31" t="n"/>
-      <c r="J56" s="31" t="n"/>
-      <c r="K56" s="31" t="n"/>
-      <c r="L56" s="31" t="n"/>
-      <c r="M56" s="31" t="n"/>
-      <c r="N56" s="31" t="n"/>
-      <c r="O56" s="31" t="n"/>
-      <c r="P56" s="31" t="n"/>
-      <c r="Q56" s="31" t="n"/>
-      <c r="R56" s="31" t="n"/>
-      <c r="S56" s="31" t="n"/>
-      <c r="T56" s="31" t="n"/>
-      <c r="U56" s="31" t="n"/>
-      <c r="V56" s="31" t="n"/>
+      <c r="C56" s="80" t="n"/>
+      <c r="D56" s="80" t="n"/>
+      <c r="E56" s="80" t="n"/>
+      <c r="F56" s="80" t="n"/>
+      <c r="G56" s="80" t="n"/>
+      <c r="H56" s="80" t="n"/>
+      <c r="I56" s="80" t="n"/>
+      <c r="J56" s="80" t="n"/>
+      <c r="K56" s="80" t="n"/>
+      <c r="L56" s="80" t="n"/>
+      <c r="M56" s="80" t="n"/>
+      <c r="N56" s="80" t="n"/>
+      <c r="O56" s="80" t="n"/>
+      <c r="P56" s="80" t="n"/>
+      <c r="Q56" s="80" t="n"/>
+      <c r="R56" s="80" t="n"/>
+      <c r="S56" s="80" t="n"/>
+      <c r="T56" s="80" t="n"/>
+      <c r="U56" s="80" t="n"/>
+      <c r="V56" s="80" t="n"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -17124,31 +17551,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B57" s="20" t="inlineStr">
+      <c r="B57" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2019</t>
         </is>
       </c>
-      <c r="C57" s="31" t="n"/>
-      <c r="D57" s="31" t="n"/>
-      <c r="E57" s="31" t="n"/>
-      <c r="F57" s="31" t="n"/>
-      <c r="G57" s="31" t="n"/>
-      <c r="H57" s="31" t="n"/>
-      <c r="I57" s="31" t="n"/>
-      <c r="J57" s="31" t="n"/>
-      <c r="K57" s="31" t="n"/>
-      <c r="L57" s="31" t="n"/>
-      <c r="M57" s="31" t="n"/>
-      <c r="N57" s="31" t="n"/>
-      <c r="O57" s="31" t="n"/>
-      <c r="P57" s="31" t="n"/>
-      <c r="Q57" s="31" t="n"/>
-      <c r="R57" s="31" t="n"/>
-      <c r="S57" s="31" t="n"/>
-      <c r="T57" s="31" t="n"/>
-      <c r="U57" s="31" t="n"/>
-      <c r="V57" s="31" t="n"/>
+      <c r="C57" s="80" t="n"/>
+      <c r="D57" s="80" t="n"/>
+      <c r="E57" s="80" t="n"/>
+      <c r="F57" s="80" t="n"/>
+      <c r="G57" s="80" t="n"/>
+      <c r="H57" s="80" t="n"/>
+      <c r="I57" s="80" t="n"/>
+      <c r="J57" s="80" t="n"/>
+      <c r="K57" s="80" t="n"/>
+      <c r="L57" s="80" t="n"/>
+      <c r="M57" s="80" t="n"/>
+      <c r="N57" s="80" t="n"/>
+      <c r="O57" s="80" t="n"/>
+      <c r="P57" s="80" t="n"/>
+      <c r="Q57" s="80" t="n"/>
+      <c r="R57" s="80" t="n"/>
+      <c r="S57" s="80" t="n"/>
+      <c r="T57" s="80" t="n"/>
+      <c r="U57" s="80" t="n"/>
+      <c r="V57" s="80" t="n"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -17156,31 +17583,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B58" s="20" t="inlineStr">
+      <c r="B58" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C58" s="31" t="n"/>
-      <c r="D58" s="31" t="n"/>
-      <c r="E58" s="31" t="n"/>
-      <c r="F58" s="31" t="n"/>
-      <c r="G58" s="31" t="n"/>
-      <c r="H58" s="31" t="n"/>
-      <c r="I58" s="31" t="n"/>
-      <c r="J58" s="31" t="n"/>
-      <c r="K58" s="31" t="n"/>
-      <c r="L58" s="31" t="n"/>
-      <c r="M58" s="31" t="n"/>
-      <c r="N58" s="31" t="n"/>
-      <c r="O58" s="31" t="n"/>
-      <c r="P58" s="31" t="n"/>
-      <c r="Q58" s="31" t="n"/>
-      <c r="R58" s="31" t="n"/>
-      <c r="S58" s="31" t="n"/>
-      <c r="T58" s="31" t="n"/>
-      <c r="U58" s="31" t="n"/>
-      <c r="V58" s="31" t="n"/>
+      <c r="C58" s="80" t="n"/>
+      <c r="D58" s="80" t="n"/>
+      <c r="E58" s="80" t="n"/>
+      <c r="F58" s="80" t="n"/>
+      <c r="G58" s="80" t="n"/>
+      <c r="H58" s="80" t="n"/>
+      <c r="I58" s="80" t="n"/>
+      <c r="J58" s="80" t="n"/>
+      <c r="K58" s="80" t="n"/>
+      <c r="L58" s="80" t="n"/>
+      <c r="M58" s="80" t="n"/>
+      <c r="N58" s="80" t="n"/>
+      <c r="O58" s="80" t="n"/>
+      <c r="P58" s="80" t="n"/>
+      <c r="Q58" s="80" t="n"/>
+      <c r="R58" s="80" t="n"/>
+      <c r="S58" s="80" t="n"/>
+      <c r="T58" s="80" t="n"/>
+      <c r="U58" s="80" t="n"/>
+      <c r="V58" s="80" t="n"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -17188,31 +17615,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B59" s="20" t="inlineStr">
+      <c r="B59" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2021</t>
         </is>
       </c>
-      <c r="C59" s="31" t="n"/>
-      <c r="D59" s="31" t="n"/>
-      <c r="E59" s="31" t="n"/>
-      <c r="F59" s="31" t="n"/>
-      <c r="G59" s="31" t="n"/>
-      <c r="H59" s="31" t="n"/>
-      <c r="I59" s="31" t="n"/>
-      <c r="J59" s="31" t="n"/>
-      <c r="K59" s="31" t="n"/>
-      <c r="L59" s="31" t="n"/>
-      <c r="M59" s="31" t="n"/>
-      <c r="N59" s="31" t="n"/>
-      <c r="O59" s="31" t="n"/>
-      <c r="P59" s="31" t="n"/>
-      <c r="Q59" s="31" t="n"/>
-      <c r="R59" s="31" t="n"/>
-      <c r="S59" s="31" t="n"/>
-      <c r="T59" s="31" t="n"/>
-      <c r="U59" s="31" t="n"/>
-      <c r="V59" s="31" t="n"/>
+      <c r="C59" s="80" t="n"/>
+      <c r="D59" s="80" t="n"/>
+      <c r="E59" s="80" t="n"/>
+      <c r="F59" s="80" t="n"/>
+      <c r="G59" s="80" t="n"/>
+      <c r="H59" s="80" t="n"/>
+      <c r="I59" s="80" t="n"/>
+      <c r="J59" s="80" t="n"/>
+      <c r="K59" s="80" t="n"/>
+      <c r="L59" s="80" t="n"/>
+      <c r="M59" s="80" t="n"/>
+      <c r="N59" s="80" t="n"/>
+      <c r="O59" s="80" t="n"/>
+      <c r="P59" s="80" t="n"/>
+      <c r="Q59" s="80" t="n"/>
+      <c r="R59" s="80" t="n"/>
+      <c r="S59" s="80" t="n"/>
+      <c r="T59" s="80" t="n"/>
+      <c r="U59" s="80" t="n"/>
+      <c r="V59" s="80" t="n"/>
     </row>
     <row r="60" ht="15" customHeight="1" s="33">
       <c r="A60" t="inlineStr">
@@ -17220,31 +17647,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B60" s="28" t="inlineStr">
+      <c r="B60" s="81" t="inlineStr">
         <is>
           <t>May/Jun_2022</t>
         </is>
       </c>
-      <c r="C60" s="31" t="n"/>
-      <c r="D60" s="31" t="n"/>
-      <c r="E60" s="31" t="n"/>
-      <c r="F60" s="31" t="n"/>
-      <c r="G60" s="31" t="n"/>
-      <c r="H60" s="31" t="n"/>
-      <c r="I60" s="31" t="n"/>
-      <c r="J60" s="31" t="n"/>
-      <c r="K60" s="31" t="n"/>
-      <c r="L60" s="31" t="n"/>
-      <c r="M60" s="31" t="n"/>
-      <c r="N60" s="31" t="n"/>
-      <c r="O60" s="31" t="n"/>
-      <c r="P60" s="31" t="n"/>
-      <c r="Q60" s="31" t="n"/>
-      <c r="R60" s="31" t="n"/>
-      <c r="S60" s="31" t="n"/>
-      <c r="T60" s="31" t="n"/>
-      <c r="U60" s="31" t="n"/>
-      <c r="V60" s="31" t="n"/>
+      <c r="C60" s="80" t="n"/>
+      <c r="D60" s="80" t="n"/>
+      <c r="E60" s="80" t="n"/>
+      <c r="F60" s="80" t="n"/>
+      <c r="G60" s="80" t="n"/>
+      <c r="H60" s="80" t="n"/>
+      <c r="I60" s="80" t="n"/>
+      <c r="J60" s="80" t="n"/>
+      <c r="K60" s="80" t="n"/>
+      <c r="L60" s="80" t="n"/>
+      <c r="M60" s="80" t="n"/>
+      <c r="N60" s="80" t="n"/>
+      <c r="O60" s="80" t="n"/>
+      <c r="P60" s="80" t="n"/>
+      <c r="Q60" s="80" t="n"/>
+      <c r="R60" s="80" t="n"/>
+      <c r="S60" s="80" t="n"/>
+      <c r="T60" s="80" t="n"/>
+      <c r="U60" s="80" t="n"/>
+      <c r="V60" s="80" t="n"/>
     </row>
     <row r="61" ht="15" customHeight="1" s="33">
       <c r="C61" s="31" t="n"/>
@@ -17278,7 +17705,22 @@
       <c r="D62" s="70" t="n"/>
       <c r="E62" s="70" t="n"/>
       <c r="F62" s="70" t="n"/>
-      <c r="G62" s="71" t="n"/>
+      <c r="G62" s="70" t="n"/>
+      <c r="H62" s="70" t="n"/>
+      <c r="I62" s="70" t="n"/>
+      <c r="J62" s="70" t="n"/>
+      <c r="K62" s="70" t="n"/>
+      <c r="L62" s="70" t="n"/>
+      <c r="M62" s="70" t="n"/>
+      <c r="N62" s="70" t="n"/>
+      <c r="O62" s="70" t="n"/>
+      <c r="P62" s="70" t="n"/>
+      <c r="Q62" s="70" t="n"/>
+      <c r="R62" s="70" t="n"/>
+      <c r="S62" s="70" t="n"/>
+      <c r="T62" s="70" t="n"/>
+      <c r="U62" s="70" t="n"/>
+      <c r="V62" s="71" t="n"/>
     </row>
     <row r="63" ht="14.3" customHeight="1" s="33">
       <c r="B63" s="6" t="n"/>
@@ -17428,31 +17870,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B65" s="20" t="inlineStr">
+      <c r="B65" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2015</t>
         </is>
       </c>
-      <c r="C65" s="21" t="n"/>
-      <c r="D65" s="21" t="n"/>
-      <c r="E65" s="21" t="n"/>
-      <c r="F65" s="21" t="n"/>
-      <c r="G65" s="21" t="n"/>
-      <c r="H65" s="21" t="n"/>
-      <c r="I65" s="21" t="n"/>
-      <c r="J65" s="21" t="n"/>
-      <c r="K65" s="21" t="n"/>
-      <c r="L65" s="21" t="n"/>
-      <c r="M65" s="21" t="n"/>
-      <c r="N65" s="21" t="n"/>
-      <c r="O65" s="21" t="n"/>
-      <c r="P65" s="21" t="n"/>
-      <c r="Q65" s="21" t="n"/>
-      <c r="R65" s="21" t="n"/>
-      <c r="S65" s="21" t="n"/>
-      <c r="T65" s="21" t="n"/>
-      <c r="U65" s="21" t="n"/>
-      <c r="V65" s="21" t="n"/>
+      <c r="C65" s="82" t="n"/>
+      <c r="D65" s="82" t="n"/>
+      <c r="E65" s="82" t="n"/>
+      <c r="F65" s="82" t="n"/>
+      <c r="G65" s="82" t="n"/>
+      <c r="H65" s="82" t="n"/>
+      <c r="I65" s="82" t="n"/>
+      <c r="J65" s="82" t="n"/>
+      <c r="K65" s="82" t="n"/>
+      <c r="L65" s="82" t="n"/>
+      <c r="M65" s="82" t="n"/>
+      <c r="N65" s="82" t="n"/>
+      <c r="O65" s="82" t="n"/>
+      <c r="P65" s="82" t="n"/>
+      <c r="Q65" s="82" t="n"/>
+      <c r="R65" s="82" t="n"/>
+      <c r="S65" s="82" t="n"/>
+      <c r="T65" s="82" t="n"/>
+      <c r="U65" s="82" t="n"/>
+      <c r="V65" s="82" t="n"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -17460,31 +17902,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B66" s="20" t="inlineStr">
+      <c r="B66" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2016</t>
         </is>
       </c>
-      <c r="C66" s="21" t="n"/>
-      <c r="D66" s="21" t="n"/>
-      <c r="E66" s="21" t="n"/>
-      <c r="F66" s="21" t="n"/>
-      <c r="G66" s="21" t="n"/>
-      <c r="H66" s="21" t="n"/>
-      <c r="I66" s="21" t="n"/>
-      <c r="J66" s="21" t="n"/>
-      <c r="K66" s="21" t="n"/>
-      <c r="L66" s="21" t="n"/>
-      <c r="M66" s="21" t="n"/>
-      <c r="N66" s="21" t="n"/>
-      <c r="O66" s="21" t="n"/>
-      <c r="P66" s="21" t="n"/>
-      <c r="Q66" s="21" t="n"/>
-      <c r="R66" s="21" t="n"/>
-      <c r="S66" s="21" t="n"/>
-      <c r="T66" s="21" t="n"/>
-      <c r="U66" s="21" t="n"/>
-      <c r="V66" s="21" t="n"/>
+      <c r="C66" s="82" t="n"/>
+      <c r="D66" s="82" t="n"/>
+      <c r="E66" s="82" t="n"/>
+      <c r="F66" s="82" t="n"/>
+      <c r="G66" s="82" t="n"/>
+      <c r="H66" s="82" t="n"/>
+      <c r="I66" s="82" t="n"/>
+      <c r="J66" s="82" t="n"/>
+      <c r="K66" s="82" t="n"/>
+      <c r="L66" s="82" t="n"/>
+      <c r="M66" s="82" t="n"/>
+      <c r="N66" s="82" t="n"/>
+      <c r="O66" s="82" t="n"/>
+      <c r="P66" s="82" t="n"/>
+      <c r="Q66" s="82" t="n"/>
+      <c r="R66" s="82" t="n"/>
+      <c r="S66" s="82" t="n"/>
+      <c r="T66" s="82" t="n"/>
+      <c r="U66" s="82" t="n"/>
+      <c r="V66" s="82" t="n"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -17492,31 +17934,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B67" s="20" t="inlineStr">
+      <c r="B67" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2017</t>
         </is>
       </c>
-      <c r="C67" s="21" t="n"/>
-      <c r="D67" s="21" t="n"/>
-      <c r="E67" s="21" t="n"/>
-      <c r="F67" s="21" t="n"/>
-      <c r="G67" s="21" t="n"/>
-      <c r="H67" s="21" t="n"/>
-      <c r="I67" s="21" t="n"/>
-      <c r="J67" s="21" t="n"/>
-      <c r="K67" s="21" t="n"/>
-      <c r="L67" s="21" t="n"/>
-      <c r="M67" s="21" t="n"/>
-      <c r="N67" s="21" t="n"/>
-      <c r="O67" s="21" t="n"/>
-      <c r="P67" s="21" t="n"/>
-      <c r="Q67" s="21" t="n"/>
-      <c r="R67" s="21" t="n"/>
-      <c r="S67" s="21" t="n"/>
-      <c r="T67" s="21" t="n"/>
-      <c r="U67" s="21" t="n"/>
-      <c r="V67" s="21" t="n"/>
+      <c r="C67" s="82" t="n"/>
+      <c r="D67" s="82" t="n"/>
+      <c r="E67" s="82" t="n"/>
+      <c r="F67" s="82" t="n"/>
+      <c r="G67" s="82" t="n"/>
+      <c r="H67" s="82" t="n"/>
+      <c r="I67" s="82" t="n"/>
+      <c r="J67" s="82" t="n"/>
+      <c r="K67" s="82" t="n"/>
+      <c r="L67" s="82" t="n"/>
+      <c r="M67" s="82" t="n"/>
+      <c r="N67" s="82" t="n"/>
+      <c r="O67" s="82" t="n"/>
+      <c r="P67" s="82" t="n"/>
+      <c r="Q67" s="82" t="n"/>
+      <c r="R67" s="82" t="n"/>
+      <c r="S67" s="82" t="n"/>
+      <c r="T67" s="82" t="n"/>
+      <c r="U67" s="82" t="n"/>
+      <c r="V67" s="82" t="n"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -17524,31 +17966,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B68" s="20" t="inlineStr">
+      <c r="B68" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2018</t>
         </is>
       </c>
-      <c r="C68" s="21" t="n"/>
-      <c r="D68" s="21" t="n"/>
-      <c r="E68" s="21" t="n"/>
-      <c r="F68" s="21" t="n"/>
-      <c r="G68" s="21" t="n"/>
-      <c r="H68" s="21" t="n"/>
-      <c r="I68" s="21" t="n"/>
-      <c r="J68" s="21" t="n"/>
-      <c r="K68" s="21" t="n"/>
-      <c r="L68" s="21" t="n"/>
-      <c r="M68" s="21" t="n"/>
-      <c r="N68" s="21" t="n"/>
-      <c r="O68" s="21" t="n"/>
-      <c r="P68" s="21" t="n"/>
-      <c r="Q68" s="21" t="n"/>
-      <c r="R68" s="21" t="n"/>
-      <c r="S68" s="21" t="n"/>
-      <c r="T68" s="21" t="n"/>
-      <c r="U68" s="21" t="n"/>
-      <c r="V68" s="21" t="n"/>
+      <c r="C68" s="82" t="n"/>
+      <c r="D68" s="82" t="n"/>
+      <c r="E68" s="82" t="n"/>
+      <c r="F68" s="82" t="n"/>
+      <c r="G68" s="82" t="n"/>
+      <c r="H68" s="82" t="n"/>
+      <c r="I68" s="82" t="n"/>
+      <c r="J68" s="82" t="n"/>
+      <c r="K68" s="82" t="n"/>
+      <c r="L68" s="82" t="n"/>
+      <c r="M68" s="82" t="n"/>
+      <c r="N68" s="82" t="n"/>
+      <c r="O68" s="82" t="n"/>
+      <c r="P68" s="82" t="n"/>
+      <c r="Q68" s="82" t="n"/>
+      <c r="R68" s="82" t="n"/>
+      <c r="S68" s="82" t="n"/>
+      <c r="T68" s="82" t="n"/>
+      <c r="U68" s="82" t="n"/>
+      <c r="V68" s="82" t="n"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -17556,31 +17998,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B69" s="20" t="inlineStr">
+      <c r="B69" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2019</t>
         </is>
       </c>
-      <c r="C69" s="21" t="n"/>
-      <c r="D69" s="21" t="n"/>
-      <c r="E69" s="21" t="n"/>
-      <c r="F69" s="21" t="n"/>
-      <c r="G69" s="21" t="n"/>
-      <c r="H69" s="21" t="n"/>
-      <c r="I69" s="21" t="n"/>
-      <c r="J69" s="21" t="n"/>
-      <c r="K69" s="21" t="n"/>
-      <c r="L69" s="21" t="n"/>
-      <c r="M69" s="21" t="n"/>
-      <c r="N69" s="21" t="n"/>
-      <c r="O69" s="21" t="n"/>
-      <c r="P69" s="21" t="n"/>
-      <c r="Q69" s="21" t="n"/>
-      <c r="R69" s="21" t="n"/>
-      <c r="S69" s="21" t="n"/>
-      <c r="T69" s="21" t="n"/>
-      <c r="U69" s="21" t="n"/>
-      <c r="V69" s="21" t="n"/>
+      <c r="C69" s="82" t="n"/>
+      <c r="D69" s="82" t="n"/>
+      <c r="E69" s="82" t="n"/>
+      <c r="F69" s="82" t="n"/>
+      <c r="G69" s="82" t="n"/>
+      <c r="H69" s="82" t="n"/>
+      <c r="I69" s="82" t="n"/>
+      <c r="J69" s="82" t="n"/>
+      <c r="K69" s="82" t="n"/>
+      <c r="L69" s="82" t="n"/>
+      <c r="M69" s="82" t="n"/>
+      <c r="N69" s="82" t="n"/>
+      <c r="O69" s="82" t="n"/>
+      <c r="P69" s="82" t="n"/>
+      <c r="Q69" s="82" t="n"/>
+      <c r="R69" s="82" t="n"/>
+      <c r="S69" s="82" t="n"/>
+      <c r="T69" s="82" t="n"/>
+      <c r="U69" s="82" t="n"/>
+      <c r="V69" s="82" t="n"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -17588,31 +18030,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B70" s="20" t="inlineStr">
+      <c r="B70" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C70" s="21" t="n"/>
-      <c r="D70" s="21" t="n"/>
-      <c r="E70" s="21" t="n"/>
-      <c r="F70" s="21" t="n"/>
-      <c r="G70" s="21" t="n"/>
-      <c r="H70" s="21" t="n"/>
-      <c r="I70" s="21" t="n"/>
-      <c r="J70" s="21" t="n"/>
-      <c r="K70" s="21" t="n"/>
-      <c r="L70" s="21" t="n"/>
-      <c r="M70" s="21" t="n"/>
-      <c r="N70" s="21" t="n"/>
-      <c r="O70" s="21" t="n"/>
-      <c r="P70" s="21" t="n"/>
-      <c r="Q70" s="21" t="n"/>
-      <c r="R70" s="21" t="n"/>
-      <c r="S70" s="21" t="n"/>
-      <c r="T70" s="21" t="n"/>
-      <c r="U70" s="21" t="n"/>
-      <c r="V70" s="21" t="n"/>
+      <c r="C70" s="82" t="n"/>
+      <c r="D70" s="82" t="n"/>
+      <c r="E70" s="82" t="n"/>
+      <c r="F70" s="82" t="n"/>
+      <c r="G70" s="82" t="n"/>
+      <c r="H70" s="82" t="n"/>
+      <c r="I70" s="82" t="n"/>
+      <c r="J70" s="82" t="n"/>
+      <c r="K70" s="82" t="n"/>
+      <c r="L70" s="82" t="n"/>
+      <c r="M70" s="82" t="n"/>
+      <c r="N70" s="82" t="n"/>
+      <c r="O70" s="82" t="n"/>
+      <c r="P70" s="82" t="n"/>
+      <c r="Q70" s="82" t="n"/>
+      <c r="R70" s="82" t="n"/>
+      <c r="S70" s="82" t="n"/>
+      <c r="T70" s="82" t="n"/>
+      <c r="U70" s="82" t="n"/>
+      <c r="V70" s="82" t="n"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -17620,31 +18062,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B71" s="20" t="inlineStr">
+      <c r="B71" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2021</t>
         </is>
       </c>
-      <c r="C71" s="21" t="n"/>
-      <c r="D71" s="21" t="n"/>
-      <c r="E71" s="21" t="n"/>
-      <c r="F71" s="21" t="n"/>
-      <c r="G71" s="21" t="n"/>
-      <c r="H71" s="21" t="n"/>
-      <c r="I71" s="21" t="n"/>
-      <c r="J71" s="21" t="n"/>
-      <c r="K71" s="21" t="n"/>
-      <c r="L71" s="21" t="n"/>
-      <c r="M71" s="21" t="n"/>
-      <c r="N71" s="21" t="n"/>
-      <c r="O71" s="21" t="n"/>
-      <c r="P71" s="21" t="n"/>
-      <c r="Q71" s="21" t="n"/>
-      <c r="R71" s="21" t="n"/>
-      <c r="S71" s="21" t="n"/>
-      <c r="T71" s="21" t="n"/>
-      <c r="U71" s="21" t="n"/>
-      <c r="V71" s="21" t="n"/>
+      <c r="C71" s="82" t="n"/>
+      <c r="D71" s="82" t="n"/>
+      <c r="E71" s="82" t="n"/>
+      <c r="F71" s="82" t="n"/>
+      <c r="G71" s="82" t="n"/>
+      <c r="H71" s="82" t="n"/>
+      <c r="I71" s="82" t="n"/>
+      <c r="J71" s="82" t="n"/>
+      <c r="K71" s="82" t="n"/>
+      <c r="L71" s="82" t="n"/>
+      <c r="M71" s="82" t="n"/>
+      <c r="N71" s="82" t="n"/>
+      <c r="O71" s="82" t="n"/>
+      <c r="P71" s="82" t="n"/>
+      <c r="Q71" s="82" t="n"/>
+      <c r="R71" s="82" t="n"/>
+      <c r="S71" s="82" t="n"/>
+      <c r="T71" s="82" t="n"/>
+      <c r="U71" s="82" t="n"/>
+      <c r="V71" s="82" t="n"/>
     </row>
     <row r="72" ht="15" customHeight="1" s="33">
       <c r="A72" t="inlineStr">
@@ -17652,31 +18094,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B72" s="28" t="inlineStr">
+      <c r="B72" s="81" t="inlineStr">
         <is>
           <t>May/Jun_2022</t>
         </is>
       </c>
-      <c r="C72" s="21" t="n"/>
-      <c r="D72" s="21" t="n"/>
-      <c r="E72" s="21" t="n"/>
-      <c r="F72" s="21" t="n"/>
-      <c r="G72" s="21" t="n"/>
-      <c r="H72" s="21" t="n"/>
-      <c r="I72" s="21" t="n"/>
-      <c r="J72" s="21" t="n"/>
-      <c r="K72" s="21" t="n"/>
-      <c r="L72" s="21" t="n"/>
-      <c r="M72" s="21" t="n"/>
-      <c r="N72" s="21" t="n"/>
-      <c r="O72" s="21" t="n"/>
-      <c r="P72" s="21" t="n"/>
-      <c r="Q72" s="21" t="n"/>
-      <c r="R72" s="21" t="n"/>
-      <c r="S72" s="21" t="n"/>
-      <c r="T72" s="21" t="n"/>
-      <c r="U72" s="21" t="n"/>
-      <c r="V72" s="21" t="n"/>
+      <c r="C72" s="82" t="n"/>
+      <c r="D72" s="82" t="n"/>
+      <c r="E72" s="82" t="n"/>
+      <c r="F72" s="82" t="n"/>
+      <c r="G72" s="82" t="n"/>
+      <c r="H72" s="82" t="n"/>
+      <c r="I72" s="82" t="n"/>
+      <c r="J72" s="82" t="n"/>
+      <c r="K72" s="82" t="n"/>
+      <c r="L72" s="82" t="n"/>
+      <c r="M72" s="82" t="n"/>
+      <c r="N72" s="82" t="n"/>
+      <c r="O72" s="82" t="n"/>
+      <c r="P72" s="82" t="n"/>
+      <c r="Q72" s="82" t="n"/>
+      <c r="R72" s="82" t="n"/>
+      <c r="S72" s="82" t="n"/>
+      <c r="T72" s="82" t="n"/>
+      <c r="U72" s="82" t="n"/>
+      <c r="V72" s="82" t="n"/>
     </row>
     <row r="73" ht="15" customHeight="1" s="33">
       <c r="C73" s="21" t="n"/>
@@ -17710,7 +18152,22 @@
       <c r="D74" s="70" t="n"/>
       <c r="E74" s="70" t="n"/>
       <c r="F74" s="70" t="n"/>
-      <c r="G74" s="71" t="n"/>
+      <c r="G74" s="70" t="n"/>
+      <c r="H74" s="70" t="n"/>
+      <c r="I74" s="70" t="n"/>
+      <c r="J74" s="70" t="n"/>
+      <c r="K74" s="70" t="n"/>
+      <c r="L74" s="70" t="n"/>
+      <c r="M74" s="70" t="n"/>
+      <c r="N74" s="70" t="n"/>
+      <c r="O74" s="70" t="n"/>
+      <c r="P74" s="70" t="n"/>
+      <c r="Q74" s="70" t="n"/>
+      <c r="R74" s="70" t="n"/>
+      <c r="S74" s="70" t="n"/>
+      <c r="T74" s="70" t="n"/>
+      <c r="U74" s="70" t="n"/>
+      <c r="V74" s="71" t="n"/>
     </row>
     <row r="75" ht="14.3" customHeight="1" s="33">
       <c r="B75" s="6" t="n"/>
@@ -17860,31 +18317,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B77" s="20" t="inlineStr">
+      <c r="B77" s="79" t="inlineStr">
         <is>
           <t>Feb/Mar_2015</t>
         </is>
       </c>
-      <c r="C77" s="31" t="n"/>
-      <c r="D77" s="31" t="n"/>
-      <c r="E77" s="31" t="n"/>
-      <c r="F77" s="31" t="n"/>
-      <c r="G77" s="31" t="n"/>
-      <c r="H77" s="31" t="n"/>
-      <c r="I77" s="31" t="n"/>
-      <c r="J77" s="31" t="n"/>
-      <c r="K77" s="31" t="n"/>
-      <c r="L77" s="31" t="n"/>
-      <c r="M77" s="31" t="n"/>
-      <c r="N77" s="31" t="n"/>
-      <c r="O77" s="31" t="n"/>
-      <c r="P77" s="31" t="n"/>
-      <c r="Q77" s="31" t="n"/>
-      <c r="R77" s="31" t="n"/>
-      <c r="S77" s="31" t="n"/>
-      <c r="T77" s="31" t="n"/>
-      <c r="U77" s="31" t="n"/>
-      <c r="V77" s="31" t="n"/>
+      <c r="C77" s="80" t="n"/>
+      <c r="D77" s="80" t="n"/>
+      <c r="E77" s="80" t="n"/>
+      <c r="F77" s="80" t="n"/>
+      <c r="G77" s="80" t="n"/>
+      <c r="H77" s="80" t="n"/>
+      <c r="I77" s="80" t="n"/>
+      <c r="J77" s="80" t="n"/>
+      <c r="K77" s="80" t="n"/>
+      <c r="L77" s="80" t="n"/>
+      <c r="M77" s="80" t="n"/>
+      <c r="N77" s="80" t="n"/>
+      <c r="O77" s="80" t="n"/>
+      <c r="P77" s="80" t="n"/>
+      <c r="Q77" s="80" t="n"/>
+      <c r="R77" s="80" t="n"/>
+      <c r="S77" s="80" t="n"/>
+      <c r="T77" s="80" t="n"/>
+      <c r="U77" s="80" t="n"/>
+      <c r="V77" s="80" t="n"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -17892,31 +18349,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B78" s="20" t="inlineStr">
+      <c r="B78" s="79" t="inlineStr">
         <is>
           <t>Feb/Mar_2016</t>
         </is>
       </c>
-      <c r="C78" s="31" t="n"/>
-      <c r="D78" s="31" t="n"/>
-      <c r="E78" s="31" t="n"/>
-      <c r="F78" s="31" t="n"/>
-      <c r="G78" s="31" t="n"/>
-      <c r="H78" s="31" t="n"/>
-      <c r="I78" s="31" t="n"/>
-      <c r="J78" s="31" t="n"/>
-      <c r="K78" s="31" t="n"/>
-      <c r="L78" s="31" t="n"/>
-      <c r="M78" s="31" t="n"/>
-      <c r="N78" s="31" t="n"/>
-      <c r="O78" s="31" t="n"/>
-      <c r="P78" s="31" t="n"/>
-      <c r="Q78" s="31" t="n"/>
-      <c r="R78" s="31" t="n"/>
-      <c r="S78" s="31" t="n"/>
-      <c r="T78" s="31" t="n"/>
-      <c r="U78" s="31" t="n"/>
-      <c r="V78" s="31" t="n"/>
+      <c r="C78" s="80" t="n"/>
+      <c r="D78" s="80" t="n"/>
+      <c r="E78" s="80" t="n"/>
+      <c r="F78" s="80" t="n"/>
+      <c r="G78" s="80" t="n"/>
+      <c r="H78" s="80" t="n"/>
+      <c r="I78" s="80" t="n"/>
+      <c r="J78" s="80" t="n"/>
+      <c r="K78" s="80" t="n"/>
+      <c r="L78" s="80" t="n"/>
+      <c r="M78" s="80" t="n"/>
+      <c r="N78" s="80" t="n"/>
+      <c r="O78" s="80" t="n"/>
+      <c r="P78" s="80" t="n"/>
+      <c r="Q78" s="80" t="n"/>
+      <c r="R78" s="80" t="n"/>
+      <c r="S78" s="80" t="n"/>
+      <c r="T78" s="80" t="n"/>
+      <c r="U78" s="80" t="n"/>
+      <c r="V78" s="80" t="n"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -17924,31 +18381,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B79" s="20" t="inlineStr">
+      <c r="B79" s="79" t="inlineStr">
         <is>
           <t>Feb/Mar_2017</t>
         </is>
       </c>
-      <c r="C79" s="31" t="n"/>
-      <c r="D79" s="31" t="n"/>
-      <c r="E79" s="31" t="n"/>
-      <c r="F79" s="31" t="n"/>
-      <c r="G79" s="31" t="n"/>
-      <c r="H79" s="31" t="n"/>
-      <c r="I79" s="31" t="n"/>
-      <c r="J79" s="31" t="n"/>
-      <c r="K79" s="31" t="n"/>
-      <c r="L79" s="31" t="n"/>
-      <c r="M79" s="31" t="n"/>
-      <c r="N79" s="31" t="n"/>
-      <c r="O79" s="31" t="n"/>
-      <c r="P79" s="31" t="n"/>
-      <c r="Q79" s="31" t="n"/>
-      <c r="R79" s="31" t="n"/>
-      <c r="S79" s="31" t="n"/>
-      <c r="T79" s="31" t="n"/>
-      <c r="U79" s="31" t="n"/>
-      <c r="V79" s="31" t="n"/>
+      <c r="C79" s="80" t="n"/>
+      <c r="D79" s="80" t="n"/>
+      <c r="E79" s="80" t="n"/>
+      <c r="F79" s="80" t="n"/>
+      <c r="G79" s="80" t="n"/>
+      <c r="H79" s="80" t="n"/>
+      <c r="I79" s="80" t="n"/>
+      <c r="J79" s="80" t="n"/>
+      <c r="K79" s="80" t="n"/>
+      <c r="L79" s="80" t="n"/>
+      <c r="M79" s="80" t="n"/>
+      <c r="N79" s="80" t="n"/>
+      <c r="O79" s="80" t="n"/>
+      <c r="P79" s="80" t="n"/>
+      <c r="Q79" s="80" t="n"/>
+      <c r="R79" s="80" t="n"/>
+      <c r="S79" s="80" t="n"/>
+      <c r="T79" s="80" t="n"/>
+      <c r="U79" s="80" t="n"/>
+      <c r="V79" s="80" t="n"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -17956,31 +18413,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B80" s="20" t="inlineStr">
+      <c r="B80" s="79" t="inlineStr">
         <is>
           <t>Feb/Mar_2018</t>
         </is>
       </c>
-      <c r="C80" s="31" t="n"/>
-      <c r="D80" s="31" t="n"/>
-      <c r="E80" s="31" t="n"/>
-      <c r="F80" s="31" t="n"/>
-      <c r="G80" s="31" t="n"/>
-      <c r="H80" s="31" t="n"/>
-      <c r="I80" s="31" t="n"/>
-      <c r="J80" s="31" t="n"/>
-      <c r="K80" s="31" t="n"/>
-      <c r="L80" s="31" t="n"/>
-      <c r="M80" s="31" t="n"/>
-      <c r="N80" s="31" t="n"/>
-      <c r="O80" s="31" t="n"/>
-      <c r="P80" s="31" t="n"/>
-      <c r="Q80" s="31" t="n"/>
-      <c r="R80" s="31" t="n"/>
-      <c r="S80" s="31" t="n"/>
-      <c r="T80" s="31" t="n"/>
-      <c r="U80" s="31" t="n"/>
-      <c r="V80" s="31" t="n"/>
+      <c r="C80" s="80" t="n"/>
+      <c r="D80" s="80" t="n"/>
+      <c r="E80" s="80" t="n"/>
+      <c r="F80" s="80" t="n"/>
+      <c r="G80" s="80" t="n"/>
+      <c r="H80" s="80" t="n"/>
+      <c r="I80" s="80" t="n"/>
+      <c r="J80" s="80" t="n"/>
+      <c r="K80" s="80" t="n"/>
+      <c r="L80" s="80" t="n"/>
+      <c r="M80" s="80" t="n"/>
+      <c r="N80" s="80" t="n"/>
+      <c r="O80" s="80" t="n"/>
+      <c r="P80" s="80" t="n"/>
+      <c r="Q80" s="80" t="n"/>
+      <c r="R80" s="80" t="n"/>
+      <c r="S80" s="80" t="n"/>
+      <c r="T80" s="80" t="n"/>
+      <c r="U80" s="80" t="n"/>
+      <c r="V80" s="80" t="n"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -17988,31 +18445,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B81" s="20" t="inlineStr">
+      <c r="B81" s="79" t="inlineStr">
         <is>
           <t>Feb/Mar_2019</t>
         </is>
       </c>
-      <c r="C81" s="31" t="n"/>
-      <c r="D81" s="31" t="n"/>
-      <c r="E81" s="31" t="n"/>
-      <c r="F81" s="31" t="n"/>
-      <c r="G81" s="31" t="n"/>
-      <c r="H81" s="31" t="n"/>
-      <c r="I81" s="31" t="n"/>
-      <c r="J81" s="31" t="n"/>
-      <c r="K81" s="31" t="n"/>
-      <c r="L81" s="31" t="n"/>
-      <c r="M81" s="31" t="n"/>
-      <c r="N81" s="31" t="n"/>
-      <c r="O81" s="31" t="n"/>
-      <c r="P81" s="31" t="n"/>
-      <c r="Q81" s="31" t="n"/>
-      <c r="R81" s="31" t="n"/>
-      <c r="S81" s="31" t="n"/>
-      <c r="T81" s="31" t="n"/>
-      <c r="U81" s="31" t="n"/>
-      <c r="V81" s="31" t="n"/>
+      <c r="C81" s="80" t="n"/>
+      <c r="D81" s="80" t="n"/>
+      <c r="E81" s="80" t="n"/>
+      <c r="F81" s="80" t="n"/>
+      <c r="G81" s="80" t="n"/>
+      <c r="H81" s="80" t="n"/>
+      <c r="I81" s="80" t="n"/>
+      <c r="J81" s="80" t="n"/>
+      <c r="K81" s="80" t="n"/>
+      <c r="L81" s="80" t="n"/>
+      <c r="M81" s="80" t="n"/>
+      <c r="N81" s="80" t="n"/>
+      <c r="O81" s="80" t="n"/>
+      <c r="P81" s="80" t="n"/>
+      <c r="Q81" s="80" t="n"/>
+      <c r="R81" s="80" t="n"/>
+      <c r="S81" s="80" t="n"/>
+      <c r="T81" s="80" t="n"/>
+      <c r="U81" s="80" t="n"/>
+      <c r="V81" s="80" t="n"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -18020,31 +18477,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B82" s="20" t="inlineStr">
+      <c r="B82" s="79" t="inlineStr">
         <is>
           <t>Feb/Mar_2020</t>
         </is>
       </c>
-      <c r="C82" s="31" t="n"/>
-      <c r="D82" s="31" t="n"/>
-      <c r="E82" s="31" t="n"/>
-      <c r="F82" s="31" t="n"/>
-      <c r="G82" s="31" t="n"/>
-      <c r="H82" s="31" t="n"/>
-      <c r="I82" s="31" t="n"/>
-      <c r="J82" s="31" t="n"/>
-      <c r="K82" s="31" t="n"/>
-      <c r="L82" s="31" t="n"/>
-      <c r="M82" s="31" t="n"/>
-      <c r="N82" s="31" t="n"/>
-      <c r="O82" s="31" t="n"/>
-      <c r="P82" s="31" t="n"/>
-      <c r="Q82" s="31" t="n"/>
-      <c r="R82" s="31" t="n"/>
-      <c r="S82" s="31" t="n"/>
-      <c r="T82" s="31" t="n"/>
-      <c r="U82" s="31" t="n"/>
-      <c r="V82" s="31" t="n"/>
+      <c r="C82" s="80" t="n"/>
+      <c r="D82" s="80" t="n"/>
+      <c r="E82" s="80" t="n"/>
+      <c r="F82" s="80" t="n"/>
+      <c r="G82" s="80" t="n"/>
+      <c r="H82" s="80" t="n"/>
+      <c r="I82" s="80" t="n"/>
+      <c r="J82" s="80" t="n"/>
+      <c r="K82" s="80" t="n"/>
+      <c r="L82" s="80" t="n"/>
+      <c r="M82" s="80" t="n"/>
+      <c r="N82" s="80" t="n"/>
+      <c r="O82" s="80" t="n"/>
+      <c r="P82" s="80" t="n"/>
+      <c r="Q82" s="80" t="n"/>
+      <c r="R82" s="80" t="n"/>
+      <c r="S82" s="80" t="n"/>
+      <c r="T82" s="80" t="n"/>
+      <c r="U82" s="80" t="n"/>
+      <c r="V82" s="80" t="n"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -18052,31 +18509,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B83" s="20" t="inlineStr">
+      <c r="B83" s="79" t="inlineStr">
         <is>
           <t>Feb/Mar_2021</t>
         </is>
       </c>
-      <c r="C83" s="31" t="n"/>
-      <c r="D83" s="31" t="n"/>
-      <c r="E83" s="31" t="n"/>
-      <c r="F83" s="31" t="n"/>
-      <c r="G83" s="31" t="n"/>
-      <c r="H83" s="31" t="n"/>
-      <c r="I83" s="31" t="n"/>
-      <c r="J83" s="31" t="n"/>
-      <c r="K83" s="31" t="n"/>
-      <c r="L83" s="31" t="n"/>
-      <c r="M83" s="31" t="n"/>
-      <c r="N83" s="31" t="n"/>
-      <c r="O83" s="31" t="n"/>
-      <c r="P83" s="31" t="n"/>
-      <c r="Q83" s="31" t="n"/>
-      <c r="R83" s="31" t="n"/>
-      <c r="S83" s="31" t="n"/>
-      <c r="T83" s="31" t="n"/>
-      <c r="U83" s="31" t="n"/>
-      <c r="V83" s="31" t="n"/>
+      <c r="C83" s="80" t="n"/>
+      <c r="D83" s="80" t="n"/>
+      <c r="E83" s="80" t="n"/>
+      <c r="F83" s="80" t="n"/>
+      <c r="G83" s="80" t="n"/>
+      <c r="H83" s="80" t="n"/>
+      <c r="I83" s="80" t="n"/>
+      <c r="J83" s="80" t="n"/>
+      <c r="K83" s="80" t="n"/>
+      <c r="L83" s="80" t="n"/>
+      <c r="M83" s="80" t="n"/>
+      <c r="N83" s="80" t="n"/>
+      <c r="O83" s="80" t="n"/>
+      <c r="P83" s="80" t="n"/>
+      <c r="Q83" s="80" t="n"/>
+      <c r="R83" s="80" t="n"/>
+      <c r="S83" s="80" t="n"/>
+      <c r="T83" s="80" t="n"/>
+      <c r="U83" s="80" t="n"/>
+      <c r="V83" s="80" t="n"/>
     </row>
     <row r="84" ht="15" customHeight="1" s="33">
       <c r="A84" t="inlineStr">
@@ -18084,31 +18541,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B84" s="28" t="inlineStr">
+      <c r="B84" s="81" t="inlineStr">
         <is>
           <t>Feb/Mar_2022</t>
         </is>
       </c>
-      <c r="C84" s="31" t="n"/>
-      <c r="D84" s="31" t="n"/>
-      <c r="E84" s="31" t="n"/>
-      <c r="F84" s="31" t="n"/>
-      <c r="G84" s="31" t="n"/>
-      <c r="H84" s="31" t="n"/>
-      <c r="I84" s="31" t="n"/>
-      <c r="J84" s="31" t="n"/>
-      <c r="K84" s="31" t="n"/>
-      <c r="L84" s="31" t="n"/>
-      <c r="M84" s="31" t="n"/>
-      <c r="N84" s="31" t="n"/>
-      <c r="O84" s="31" t="n"/>
-      <c r="P84" s="31" t="n"/>
-      <c r="Q84" s="31" t="n"/>
-      <c r="R84" s="31" t="n"/>
-      <c r="S84" s="31" t="n"/>
-      <c r="T84" s="31" t="n"/>
-      <c r="U84" s="31" t="n"/>
-      <c r="V84" s="31" t="n"/>
+      <c r="C84" s="80" t="n"/>
+      <c r="D84" s="80" t="n"/>
+      <c r="E84" s="80" t="n"/>
+      <c r="F84" s="80" t="n"/>
+      <c r="G84" s="80" t="n"/>
+      <c r="H84" s="80" t="n"/>
+      <c r="I84" s="80" t="n"/>
+      <c r="J84" s="80" t="n"/>
+      <c r="K84" s="80" t="n"/>
+      <c r="L84" s="80" t="n"/>
+      <c r="M84" s="80" t="n"/>
+      <c r="N84" s="80" t="n"/>
+      <c r="O84" s="80" t="n"/>
+      <c r="P84" s="80" t="n"/>
+      <c r="Q84" s="80" t="n"/>
+      <c r="R84" s="80" t="n"/>
+      <c r="S84" s="80" t="n"/>
+      <c r="T84" s="80" t="n"/>
+      <c r="U84" s="80" t="n"/>
+      <c r="V84" s="80" t="n"/>
     </row>
     <row r="85" ht="15" customHeight="1" s="33">
       <c r="C85" s="31" t="n"/>
@@ -18142,7 +18599,22 @@
       <c r="D86" s="70" t="n"/>
       <c r="E86" s="70" t="n"/>
       <c r="F86" s="70" t="n"/>
-      <c r="G86" s="71" t="n"/>
+      <c r="G86" s="70" t="n"/>
+      <c r="H86" s="70" t="n"/>
+      <c r="I86" s="70" t="n"/>
+      <c r="J86" s="70" t="n"/>
+      <c r="K86" s="70" t="n"/>
+      <c r="L86" s="70" t="n"/>
+      <c r="M86" s="70" t="n"/>
+      <c r="N86" s="70" t="n"/>
+      <c r="O86" s="70" t="n"/>
+      <c r="P86" s="70" t="n"/>
+      <c r="Q86" s="70" t="n"/>
+      <c r="R86" s="70" t="n"/>
+      <c r="S86" s="70" t="n"/>
+      <c r="T86" s="70" t="n"/>
+      <c r="U86" s="70" t="n"/>
+      <c r="V86" s="71" t="n"/>
     </row>
     <row r="87" ht="14.3" customHeight="1" s="33">
       <c r="B87" s="6" t="n"/>
@@ -18292,31 +18764,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B89" s="20" t="inlineStr">
+      <c r="B89" s="79" t="inlineStr">
         <is>
           <t>Feb/Mar_2015</t>
         </is>
       </c>
-      <c r="C89" s="21" t="n"/>
-      <c r="D89" s="21" t="n"/>
-      <c r="E89" s="21" t="n"/>
-      <c r="F89" s="21" t="n"/>
-      <c r="G89" s="21" t="n"/>
-      <c r="H89" s="21" t="n"/>
-      <c r="I89" s="21" t="n"/>
-      <c r="J89" s="21" t="n"/>
-      <c r="K89" s="21" t="n"/>
-      <c r="L89" s="21" t="n"/>
-      <c r="M89" s="21" t="n"/>
-      <c r="N89" s="21" t="n"/>
-      <c r="O89" s="21" t="n"/>
-      <c r="P89" s="21" t="n"/>
-      <c r="Q89" s="21" t="n"/>
-      <c r="R89" s="21" t="n"/>
-      <c r="S89" s="21" t="n"/>
-      <c r="T89" s="21" t="n"/>
-      <c r="U89" s="21" t="n"/>
-      <c r="V89" s="21" t="n"/>
+      <c r="C89" s="82" t="n"/>
+      <c r="D89" s="82" t="n"/>
+      <c r="E89" s="82" t="n"/>
+      <c r="F89" s="82" t="n"/>
+      <c r="G89" s="82" t="n"/>
+      <c r="H89" s="82" t="n"/>
+      <c r="I89" s="82" t="n"/>
+      <c r="J89" s="82" t="n"/>
+      <c r="K89" s="82" t="n"/>
+      <c r="L89" s="82" t="n"/>
+      <c r="M89" s="82" t="n"/>
+      <c r="N89" s="82" t="n"/>
+      <c r="O89" s="82" t="n"/>
+      <c r="P89" s="82" t="n"/>
+      <c r="Q89" s="82" t="n"/>
+      <c r="R89" s="82" t="n"/>
+      <c r="S89" s="82" t="n"/>
+      <c r="T89" s="82" t="n"/>
+      <c r="U89" s="82" t="n"/>
+      <c r="V89" s="82" t="n"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -18324,31 +18796,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B90" s="20" t="inlineStr">
+      <c r="B90" s="79" t="inlineStr">
         <is>
           <t>Feb/Mar_2016</t>
         </is>
       </c>
-      <c r="C90" s="21" t="n"/>
-      <c r="D90" s="21" t="n"/>
-      <c r="E90" s="21" t="n"/>
-      <c r="F90" s="21" t="n"/>
-      <c r="G90" s="21" t="n"/>
-      <c r="H90" s="21" t="n"/>
-      <c r="I90" s="21" t="n"/>
-      <c r="J90" s="21" t="n"/>
-      <c r="K90" s="21" t="n"/>
-      <c r="L90" s="21" t="n"/>
-      <c r="M90" s="21" t="n"/>
-      <c r="N90" s="21" t="n"/>
-      <c r="O90" s="21" t="n"/>
-      <c r="P90" s="21" t="n"/>
-      <c r="Q90" s="21" t="n"/>
-      <c r="R90" s="21" t="n"/>
-      <c r="S90" s="21" t="n"/>
-      <c r="T90" s="21" t="n"/>
-      <c r="U90" s="21" t="n"/>
-      <c r="V90" s="21" t="n"/>
+      <c r="C90" s="82" t="n"/>
+      <c r="D90" s="82" t="n"/>
+      <c r="E90" s="82" t="n"/>
+      <c r="F90" s="82" t="n"/>
+      <c r="G90" s="82" t="n"/>
+      <c r="H90" s="82" t="n"/>
+      <c r="I90" s="82" t="n"/>
+      <c r="J90" s="82" t="n"/>
+      <c r="K90" s="82" t="n"/>
+      <c r="L90" s="82" t="n"/>
+      <c r="M90" s="82" t="n"/>
+      <c r="N90" s="82" t="n"/>
+      <c r="O90" s="82" t="n"/>
+      <c r="P90" s="82" t="n"/>
+      <c r="Q90" s="82" t="n"/>
+      <c r="R90" s="82" t="n"/>
+      <c r="S90" s="82" t="n"/>
+      <c r="T90" s="82" t="n"/>
+      <c r="U90" s="82" t="n"/>
+      <c r="V90" s="82" t="n"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -18356,31 +18828,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B91" s="20" t="inlineStr">
+      <c r="B91" s="79" t="inlineStr">
         <is>
           <t>Feb/Mar_2017</t>
         </is>
       </c>
-      <c r="C91" s="21" t="n"/>
-      <c r="D91" s="21" t="n"/>
-      <c r="E91" s="21" t="n"/>
-      <c r="F91" s="21" t="n"/>
-      <c r="G91" s="21" t="n"/>
-      <c r="H91" s="21" t="n"/>
-      <c r="I91" s="21" t="n"/>
-      <c r="J91" s="21" t="n"/>
-      <c r="K91" s="21" t="n"/>
-      <c r="L91" s="21" t="n"/>
-      <c r="M91" s="21" t="n"/>
-      <c r="N91" s="21" t="n"/>
-      <c r="O91" s="21" t="n"/>
-      <c r="P91" s="21" t="n"/>
-      <c r="Q91" s="21" t="n"/>
-      <c r="R91" s="21" t="n"/>
-      <c r="S91" s="21" t="n"/>
-      <c r="T91" s="21" t="n"/>
-      <c r="U91" s="21" t="n"/>
-      <c r="V91" s="21" t="n"/>
+      <c r="C91" s="82" t="n"/>
+      <c r="D91" s="82" t="n"/>
+      <c r="E91" s="82" t="n"/>
+      <c r="F91" s="82" t="n"/>
+      <c r="G91" s="82" t="n"/>
+      <c r="H91" s="82" t="n"/>
+      <c r="I91" s="82" t="n"/>
+      <c r="J91" s="82" t="n"/>
+      <c r="K91" s="82" t="n"/>
+      <c r="L91" s="82" t="n"/>
+      <c r="M91" s="82" t="n"/>
+      <c r="N91" s="82" t="n"/>
+      <c r="O91" s="82" t="n"/>
+      <c r="P91" s="82" t="n"/>
+      <c r="Q91" s="82" t="n"/>
+      <c r="R91" s="82" t="n"/>
+      <c r="S91" s="82" t="n"/>
+      <c r="T91" s="82" t="n"/>
+      <c r="U91" s="82" t="n"/>
+      <c r="V91" s="82" t="n"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -18388,31 +18860,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B92" s="20" t="inlineStr">
+      <c r="B92" s="79" t="inlineStr">
         <is>
           <t>Feb/Mar_2018</t>
         </is>
       </c>
-      <c r="C92" s="21" t="n"/>
-      <c r="D92" s="21" t="n"/>
-      <c r="E92" s="21" t="n"/>
-      <c r="F92" s="21" t="n"/>
-      <c r="G92" s="21" t="n"/>
-      <c r="H92" s="21" t="n"/>
-      <c r="I92" s="21" t="n"/>
-      <c r="J92" s="21" t="n"/>
-      <c r="K92" s="21" t="n"/>
-      <c r="L92" s="21" t="n"/>
-      <c r="M92" s="21" t="n"/>
-      <c r="N92" s="21" t="n"/>
-      <c r="O92" s="21" t="n"/>
-      <c r="P92" s="21" t="n"/>
-      <c r="Q92" s="21" t="n"/>
-      <c r="R92" s="21" t="n"/>
-      <c r="S92" s="21" t="n"/>
-      <c r="T92" s="21" t="n"/>
-      <c r="U92" s="21" t="n"/>
-      <c r="V92" s="21" t="n"/>
+      <c r="C92" s="82" t="n"/>
+      <c r="D92" s="82" t="n"/>
+      <c r="E92" s="82" t="n"/>
+      <c r="F92" s="82" t="n"/>
+      <c r="G92" s="82" t="n"/>
+      <c r="H92" s="82" t="n"/>
+      <c r="I92" s="82" t="n"/>
+      <c r="J92" s="82" t="n"/>
+      <c r="K92" s="82" t="n"/>
+      <c r="L92" s="82" t="n"/>
+      <c r="M92" s="82" t="n"/>
+      <c r="N92" s="82" t="n"/>
+      <c r="O92" s="82" t="n"/>
+      <c r="P92" s="82" t="n"/>
+      <c r="Q92" s="82" t="n"/>
+      <c r="R92" s="82" t="n"/>
+      <c r="S92" s="82" t="n"/>
+      <c r="T92" s="82" t="n"/>
+      <c r="U92" s="82" t="n"/>
+      <c r="V92" s="82" t="n"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -18420,31 +18892,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B93" s="20" t="inlineStr">
+      <c r="B93" s="79" t="inlineStr">
         <is>
           <t>Feb/Mar_2019</t>
         </is>
       </c>
-      <c r="C93" s="21" t="n"/>
-      <c r="D93" s="21" t="n"/>
-      <c r="E93" s="21" t="n"/>
-      <c r="F93" s="21" t="n"/>
-      <c r="G93" s="21" t="n"/>
-      <c r="H93" s="21" t="n"/>
-      <c r="I93" s="21" t="n"/>
-      <c r="J93" s="21" t="n"/>
-      <c r="K93" s="21" t="n"/>
-      <c r="L93" s="21" t="n"/>
-      <c r="M93" s="21" t="n"/>
-      <c r="N93" s="21" t="n"/>
-      <c r="O93" s="21" t="n"/>
-      <c r="P93" s="21" t="n"/>
-      <c r="Q93" s="21" t="n"/>
-      <c r="R93" s="21" t="n"/>
-      <c r="S93" s="21" t="n"/>
-      <c r="T93" s="21" t="n"/>
-      <c r="U93" s="21" t="n"/>
-      <c r="V93" s="21" t="n"/>
+      <c r="C93" s="82" t="n"/>
+      <c r="D93" s="82" t="n"/>
+      <c r="E93" s="82" t="n"/>
+      <c r="F93" s="82" t="n"/>
+      <c r="G93" s="82" t="n"/>
+      <c r="H93" s="82" t="n"/>
+      <c r="I93" s="82" t="n"/>
+      <c r="J93" s="82" t="n"/>
+      <c r="K93" s="82" t="n"/>
+      <c r="L93" s="82" t="n"/>
+      <c r="M93" s="82" t="n"/>
+      <c r="N93" s="82" t="n"/>
+      <c r="O93" s="82" t="n"/>
+      <c r="P93" s="82" t="n"/>
+      <c r="Q93" s="82" t="n"/>
+      <c r="R93" s="82" t="n"/>
+      <c r="S93" s="82" t="n"/>
+      <c r="T93" s="82" t="n"/>
+      <c r="U93" s="82" t="n"/>
+      <c r="V93" s="82" t="n"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -18452,31 +18924,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B94" s="20" t="inlineStr">
+      <c r="B94" s="79" t="inlineStr">
         <is>
           <t>Feb/Mar_2020</t>
         </is>
       </c>
-      <c r="C94" s="21" t="n"/>
-      <c r="D94" s="21" t="n"/>
-      <c r="E94" s="21" t="n"/>
-      <c r="F94" s="21" t="n"/>
-      <c r="G94" s="21" t="n"/>
-      <c r="H94" s="21" t="n"/>
-      <c r="I94" s="21" t="n"/>
-      <c r="J94" s="21" t="n"/>
-      <c r="K94" s="21" t="n"/>
-      <c r="L94" s="21" t="n"/>
-      <c r="M94" s="21" t="n"/>
-      <c r="N94" s="21" t="n"/>
-      <c r="O94" s="21" t="n"/>
-      <c r="P94" s="21" t="n"/>
-      <c r="Q94" s="21" t="n"/>
-      <c r="R94" s="21" t="n"/>
-      <c r="S94" s="21" t="n"/>
-      <c r="T94" s="21" t="n"/>
-      <c r="U94" s="21" t="n"/>
-      <c r="V94" s="21" t="n"/>
+      <c r="C94" s="82" t="n"/>
+      <c r="D94" s="82" t="n"/>
+      <c r="E94" s="82" t="n"/>
+      <c r="F94" s="82" t="n"/>
+      <c r="G94" s="82" t="n"/>
+      <c r="H94" s="82" t="n"/>
+      <c r="I94" s="82" t="n"/>
+      <c r="J94" s="82" t="n"/>
+      <c r="K94" s="82" t="n"/>
+      <c r="L94" s="82" t="n"/>
+      <c r="M94" s="82" t="n"/>
+      <c r="N94" s="82" t="n"/>
+      <c r="O94" s="82" t="n"/>
+      <c r="P94" s="82" t="n"/>
+      <c r="Q94" s="82" t="n"/>
+      <c r="R94" s="82" t="n"/>
+      <c r="S94" s="82" t="n"/>
+      <c r="T94" s="82" t="n"/>
+      <c r="U94" s="82" t="n"/>
+      <c r="V94" s="82" t="n"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -18484,31 +18956,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B95" s="20" t="inlineStr">
+      <c r="B95" s="79" t="inlineStr">
         <is>
           <t>Feb/Mar_2021</t>
         </is>
       </c>
-      <c r="C95" s="21" t="n"/>
-      <c r="D95" s="21" t="n"/>
-      <c r="E95" s="21" t="n"/>
-      <c r="F95" s="21" t="n"/>
-      <c r="G95" s="21" t="n"/>
-      <c r="H95" s="21" t="n"/>
-      <c r="I95" s="21" t="n"/>
-      <c r="J95" s="21" t="n"/>
-      <c r="K95" s="21" t="n"/>
-      <c r="L95" s="21" t="n"/>
-      <c r="M95" s="21" t="n"/>
-      <c r="N95" s="21" t="n"/>
-      <c r="O95" s="21" t="n"/>
-      <c r="P95" s="21" t="n"/>
-      <c r="Q95" s="21" t="n"/>
-      <c r="R95" s="21" t="n"/>
-      <c r="S95" s="21" t="n"/>
-      <c r="T95" s="21" t="n"/>
-      <c r="U95" s="21" t="n"/>
-      <c r="V95" s="21" t="n"/>
+      <c r="C95" s="82" t="n"/>
+      <c r="D95" s="82" t="n"/>
+      <c r="E95" s="82" t="n"/>
+      <c r="F95" s="82" t="n"/>
+      <c r="G95" s="82" t="n"/>
+      <c r="H95" s="82" t="n"/>
+      <c r="I95" s="82" t="n"/>
+      <c r="J95" s="82" t="n"/>
+      <c r="K95" s="82" t="n"/>
+      <c r="L95" s="82" t="n"/>
+      <c r="M95" s="82" t="n"/>
+      <c r="N95" s="82" t="n"/>
+      <c r="O95" s="82" t="n"/>
+      <c r="P95" s="82" t="n"/>
+      <c r="Q95" s="82" t="n"/>
+      <c r="R95" s="82" t="n"/>
+      <c r="S95" s="82" t="n"/>
+      <c r="T95" s="82" t="n"/>
+      <c r="U95" s="82" t="n"/>
+      <c r="V95" s="82" t="n"/>
     </row>
     <row r="96" ht="15" customHeight="1" s="33">
       <c r="A96" t="inlineStr">
@@ -18516,90 +18988,90 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B96" s="28" t="inlineStr">
+      <c r="B96" s="81" t="inlineStr">
         <is>
           <t>Feb/Mar_2022</t>
         </is>
       </c>
-      <c r="C96" s="21" t="n"/>
-      <c r="D96" s="21" t="n"/>
-      <c r="E96" s="21" t="n"/>
-      <c r="F96" s="21" t="n"/>
-      <c r="G96" s="21" t="n"/>
-      <c r="H96" s="21" t="n"/>
-      <c r="I96" s="21" t="n"/>
-      <c r="J96" s="21" t="n"/>
-      <c r="K96" s="21" t="n"/>
-      <c r="L96" s="21" t="n"/>
-      <c r="M96" s="21" t="n"/>
-      <c r="N96" s="21" t="n"/>
-      <c r="O96" s="21" t="n"/>
-      <c r="P96" s="21" t="n"/>
-      <c r="Q96" s="21" t="n"/>
-      <c r="R96" s="21" t="n"/>
-      <c r="S96" s="21" t="n"/>
-      <c r="T96" s="21" t="n"/>
-      <c r="U96" s="21" t="n"/>
-      <c r="V96" s="21" t="n"/>
+      <c r="C96" s="82" t="n"/>
+      <c r="D96" s="82" t="n"/>
+      <c r="E96" s="82" t="n"/>
+      <c r="F96" s="82" t="n"/>
+      <c r="G96" s="82" t="n"/>
+      <c r="H96" s="82" t="n"/>
+      <c r="I96" s="82" t="n"/>
+      <c r="J96" s="82" t="n"/>
+      <c r="K96" s="82" t="n"/>
+      <c r="L96" s="82" t="n"/>
+      <c r="M96" s="82" t="n"/>
+      <c r="N96" s="82" t="n"/>
+      <c r="O96" s="82" t="n"/>
+      <c r="P96" s="82" t="n"/>
+      <c r="Q96" s="82" t="n"/>
+      <c r="R96" s="82" t="n"/>
+      <c r="S96" s="82" t="n"/>
+      <c r="T96" s="82" t="n"/>
+      <c r="U96" s="82" t="n"/>
+      <c r="V96" s="82" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="56">
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="B86:V86"/>
+    <mergeCell ref="B2:V2"/>
+    <mergeCell ref="I15:M15"/>
+    <mergeCell ref="B3:B4"/>
     <mergeCell ref="N63:R63"/>
+    <mergeCell ref="D63:H63"/>
     <mergeCell ref="C63:C64"/>
     <mergeCell ref="I27:M27"/>
+    <mergeCell ref="B14:V14"/>
     <mergeCell ref="N51:R51"/>
-    <mergeCell ref="B38:G38"/>
-    <mergeCell ref="S51:V51"/>
-    <mergeCell ref="B74:G74"/>
-    <mergeCell ref="I75:M75"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="I87:M87"/>
-    <mergeCell ref="D75:H75"/>
-    <mergeCell ref="I3:M3"/>
-    <mergeCell ref="S3:V3"/>
-    <mergeCell ref="D87:H87"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="B26:G26"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="I39:M39"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="D39:H39"/>
-    <mergeCell ref="B75:B76"/>
-    <mergeCell ref="I63:M63"/>
-    <mergeCell ref="B86:G86"/>
-    <mergeCell ref="N27:R27"/>
-    <mergeCell ref="S15:V15"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="I15:M15"/>
-    <mergeCell ref="B14:G14"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="D63:H63"/>
     <mergeCell ref="N75:R75"/>
     <mergeCell ref="S63:V63"/>
     <mergeCell ref="B39:B40"/>
     <mergeCell ref="C75:C76"/>
+    <mergeCell ref="B38:V38"/>
+    <mergeCell ref="S51:V51"/>
     <mergeCell ref="N3:R3"/>
     <mergeCell ref="S75:V75"/>
     <mergeCell ref="D27:H27"/>
+    <mergeCell ref="I75:M75"/>
+    <mergeCell ref="B15:B16"/>
     <mergeCell ref="N39:R39"/>
+    <mergeCell ref="I87:M87"/>
+    <mergeCell ref="D75:H75"/>
+    <mergeCell ref="B74:V74"/>
     <mergeCell ref="S27:V27"/>
     <mergeCell ref="B87:B88"/>
+    <mergeCell ref="I3:M3"/>
     <mergeCell ref="C51:C52"/>
+    <mergeCell ref="S3:V3"/>
+    <mergeCell ref="D87:H87"/>
     <mergeCell ref="S39:V39"/>
-    <mergeCell ref="B50:G50"/>
-    <mergeCell ref="B62:G62"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="B50:V50"/>
+    <mergeCell ref="I39:M39"/>
+    <mergeCell ref="B26:V26"/>
     <mergeCell ref="D3:H3"/>
+    <mergeCell ref="B63:B64"/>
     <mergeCell ref="N87:R87"/>
+    <mergeCell ref="D39:H39"/>
     <mergeCell ref="B51:B52"/>
     <mergeCell ref="C87:C88"/>
+    <mergeCell ref="B75:B76"/>
+    <mergeCell ref="B62:V62"/>
     <mergeCell ref="I51:M51"/>
+    <mergeCell ref="C3:C4"/>
     <mergeCell ref="D15:H15"/>
-    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="I63:M63"/>
+    <mergeCell ref="S87:V87"/>
     <mergeCell ref="N15:R15"/>
-    <mergeCell ref="S87:V87"/>
     <mergeCell ref="D51:H51"/>
     <mergeCell ref="C15:C16"/>
+    <mergeCell ref="N27:R27"/>
+    <mergeCell ref="S15:V15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -18648,9 +19120,22 @@
       <c r="D2" s="70" t="n"/>
       <c r="E2" s="70" t="n"/>
       <c r="F2" s="70" t="n"/>
-      <c r="G2" s="71" t="n"/>
-      <c r="J2" s="5" t="n"/>
-      <c r="K2" s="5" t="n"/>
+      <c r="G2" s="70" t="n"/>
+      <c r="H2" s="70" t="n"/>
+      <c r="I2" s="70" t="n"/>
+      <c r="J2" s="70" t="n"/>
+      <c r="K2" s="70" t="n"/>
+      <c r="L2" s="70" t="n"/>
+      <c r="M2" s="70" t="n"/>
+      <c r="N2" s="70" t="n"/>
+      <c r="O2" s="70" t="n"/>
+      <c r="P2" s="70" t="n"/>
+      <c r="Q2" s="70" t="n"/>
+      <c r="R2" s="70" t="n"/>
+      <c r="S2" s="70" t="n"/>
+      <c r="T2" s="70" t="n"/>
+      <c r="U2" s="70" t="n"/>
+      <c r="V2" s="71" t="n"/>
     </row>
     <row r="3">
       <c r="B3" s="6" t="n"/>
@@ -19082,9 +19567,22 @@
       <c r="D14" s="70" t="n"/>
       <c r="E14" s="70" t="n"/>
       <c r="F14" s="70" t="n"/>
-      <c r="G14" s="71" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="n"/>
+      <c r="G14" s="70" t="n"/>
+      <c r="H14" s="70" t="n"/>
+      <c r="I14" s="70" t="n"/>
+      <c r="J14" s="70" t="n"/>
+      <c r="K14" s="70" t="n"/>
+      <c r="L14" s="70" t="n"/>
+      <c r="M14" s="70" t="n"/>
+      <c r="N14" s="70" t="n"/>
+      <c r="O14" s="70" t="n"/>
+      <c r="P14" s="70" t="n"/>
+      <c r="Q14" s="70" t="n"/>
+      <c r="R14" s="70" t="n"/>
+      <c r="S14" s="70" t="n"/>
+      <c r="T14" s="70" t="n"/>
+      <c r="U14" s="70" t="n"/>
+      <c r="V14" s="71" t="n"/>
     </row>
     <row r="15" ht="14.3" customHeight="1" s="33">
       <c r="B15" s="6" t="n"/>
@@ -19516,9 +20014,22 @@
       <c r="D26" s="70" t="n"/>
       <c r="E26" s="70" t="n"/>
       <c r="F26" s="70" t="n"/>
-      <c r="G26" s="71" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="n"/>
+      <c r="G26" s="70" t="n"/>
+      <c r="H26" s="70" t="n"/>
+      <c r="I26" s="70" t="n"/>
+      <c r="J26" s="70" t="n"/>
+      <c r="K26" s="70" t="n"/>
+      <c r="L26" s="70" t="n"/>
+      <c r="M26" s="70" t="n"/>
+      <c r="N26" s="70" t="n"/>
+      <c r="O26" s="70" t="n"/>
+      <c r="P26" s="70" t="n"/>
+      <c r="Q26" s="70" t="n"/>
+      <c r="R26" s="70" t="n"/>
+      <c r="S26" s="70" t="n"/>
+      <c r="T26" s="70" t="n"/>
+      <c r="U26" s="70" t="n"/>
+      <c r="V26" s="71" t="n"/>
     </row>
     <row r="27">
       <c r="B27" s="6" t="n"/>
@@ -19769,37 +20280,39 @@
           <t>Sept_2018</t>
         </is>
       </c>
-      <c r="C32" s="31" t="n">
-        <v>9</v>
+      <c r="C32" s="31" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
       </c>
       <c r="D32" s="31" t="inlineStr">
         <is>
-          <t>1.8, 1.9, 1.10, 10, 11</t>
+          <t>Q1.8, Q1.9, Q1.10, Q10, Q11</t>
         </is>
       </c>
       <c r="E32" s="31" t="inlineStr">
         <is>
-          <t>1.3, 2, 3, 4</t>
+          <t>Q1.3, Q2, Q3, Q4</t>
         </is>
       </c>
       <c r="F32" s="31" t="inlineStr">
         <is>
-          <t>1.2, 5</t>
+          <t>Q1.2, Q5</t>
         </is>
       </c>
       <c r="G32" s="31" t="inlineStr">
         <is>
-          <t>1.5, 1.6, 1.7, 6, 7, 8</t>
+          <t>Q1.5, Q1.6, Q1.7, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="H32" s="31" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>Q1.1</t>
         </is>
       </c>
       <c r="I32" s="31" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>Q1.4</t>
         </is>
       </c>
       <c r="J32" s="31" t="n"/>
@@ -19976,9 +20489,22 @@
       <c r="D38" s="70" t="n"/>
       <c r="E38" s="70" t="n"/>
       <c r="F38" s="70" t="n"/>
-      <c r="G38" s="71" t="n"/>
-      <c r="J38" s="5" t="n"/>
-      <c r="K38" s="5" t="n"/>
+      <c r="G38" s="70" t="n"/>
+      <c r="H38" s="70" t="n"/>
+      <c r="I38" s="70" t="n"/>
+      <c r="J38" s="70" t="n"/>
+      <c r="K38" s="70" t="n"/>
+      <c r="L38" s="70" t="n"/>
+      <c r="M38" s="70" t="n"/>
+      <c r="N38" s="70" t="n"/>
+      <c r="O38" s="70" t="n"/>
+      <c r="P38" s="70" t="n"/>
+      <c r="Q38" s="70" t="n"/>
+      <c r="R38" s="70" t="n"/>
+      <c r="S38" s="70" t="n"/>
+      <c r="T38" s="70" t="n"/>
+      <c r="U38" s="70" t="n"/>
+      <c r="V38" s="71" t="n"/>
     </row>
     <row r="39" ht="14.3" customHeight="1" s="33">
       <c r="B39" s="6" t="n"/>
@@ -20410,9 +20936,22 @@
       <c r="D50" s="70" t="n"/>
       <c r="E50" s="70" t="n"/>
       <c r="F50" s="70" t="n"/>
-      <c r="G50" s="71" t="n"/>
-      <c r="J50" s="5" t="n"/>
-      <c r="K50" s="5" t="n"/>
+      <c r="G50" s="70" t="n"/>
+      <c r="H50" s="70" t="n"/>
+      <c r="I50" s="70" t="n"/>
+      <c r="J50" s="70" t="n"/>
+      <c r="K50" s="70" t="n"/>
+      <c r="L50" s="70" t="n"/>
+      <c r="M50" s="70" t="n"/>
+      <c r="N50" s="70" t="n"/>
+      <c r="O50" s="70" t="n"/>
+      <c r="P50" s="70" t="n"/>
+      <c r="Q50" s="70" t="n"/>
+      <c r="R50" s="70" t="n"/>
+      <c r="S50" s="70" t="n"/>
+      <c r="T50" s="70" t="n"/>
+      <c r="U50" s="70" t="n"/>
+      <c r="V50" s="71" t="n"/>
     </row>
     <row r="51">
       <c r="B51" s="6" t="n"/>
@@ -20633,24 +21172,26 @@
       </c>
       <c r="C55" s="31" t="inlineStr">
         <is>
-          <t>1.4, 5</t>
+          <t>Q1.4, Q5</t>
         </is>
       </c>
       <c r="D55" s="31" t="inlineStr">
         <is>
-          <t>1.5, 1.6, 6</t>
+          <t>Q1.5, Q1.6, Q6</t>
         </is>
       </c>
       <c r="E55" s="31" t="n"/>
       <c r="F55" s="31" t="n"/>
       <c r="G55" s="31" t="inlineStr">
         <is>
-          <t>1.1, 1.2, 1.3, 2, 3</t>
+          <t>Q1.1, Q1.2, Q1.3, Q2, Q3</t>
         </is>
       </c>
       <c r="H55" s="31" t="n"/>
-      <c r="I55" s="31" t="n">
-        <v>4</v>
+      <c r="I55" s="31" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
       </c>
       <c r="J55" s="31" t="n"/>
       <c r="K55" s="31" t="n"/>
@@ -20711,25 +21252,25 @@
       </c>
       <c r="C57" s="31" t="inlineStr">
         <is>
-          <t>1.5, 5</t>
+          <t>Q1.5, Q5</t>
         </is>
       </c>
       <c r="D57" s="31" t="inlineStr">
         <is>
-          <t>1.6, 1.7, 6, 7</t>
+          <t>Q1.6, Q1.7, Q6, Q7</t>
         </is>
       </c>
       <c r="E57" s="31" t="n"/>
       <c r="F57" s="31" t="n"/>
       <c r="G57" s="31" t="inlineStr">
         <is>
-          <t>1.1, 1.2, 1.3, 2, 3</t>
+          <t>Q1.1, Q1.2, Q1.3, Q2, Q3</t>
         </is>
       </c>
       <c r="H57" s="31" t="n"/>
       <c r="I57" s="31" t="inlineStr">
         <is>
-          <t>1.4, 4</t>
+          <t>Q1.4, Q4</t>
         </is>
       </c>
       <c r="J57" s="31" t="n"/>
@@ -20752,31 +21293,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B58" s="20" t="inlineStr">
+      <c r="B58" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C58" s="31" t="n"/>
-      <c r="D58" s="31" t="n"/>
-      <c r="E58" s="31" t="n"/>
-      <c r="F58" s="31" t="n"/>
-      <c r="G58" s="31" t="n"/>
-      <c r="H58" s="31" t="n"/>
-      <c r="I58" s="31" t="n"/>
-      <c r="J58" s="31" t="n"/>
-      <c r="K58" s="31" t="n"/>
-      <c r="L58" s="31" t="n"/>
-      <c r="M58" s="31" t="n"/>
-      <c r="N58" s="31" t="n"/>
-      <c r="O58" s="31" t="n"/>
-      <c r="P58" s="31" t="n"/>
-      <c r="Q58" s="31" t="n"/>
-      <c r="R58" s="31" t="n"/>
-      <c r="S58" s="31" t="n"/>
-      <c r="T58" s="31" t="n"/>
-      <c r="U58" s="31" t="n"/>
-      <c r="V58" s="31" t="n"/>
+      <c r="C58" s="80" t="n"/>
+      <c r="D58" s="80" t="n"/>
+      <c r="E58" s="80" t="n"/>
+      <c r="F58" s="80" t="n"/>
+      <c r="G58" s="80" t="n"/>
+      <c r="H58" s="80" t="n"/>
+      <c r="I58" s="80" t="n"/>
+      <c r="J58" s="80" t="n"/>
+      <c r="K58" s="80" t="n"/>
+      <c r="L58" s="80" t="n"/>
+      <c r="M58" s="80" t="n"/>
+      <c r="N58" s="80" t="n"/>
+      <c r="O58" s="80" t="n"/>
+      <c r="P58" s="80" t="n"/>
+      <c r="Q58" s="80" t="n"/>
+      <c r="R58" s="80" t="n"/>
+      <c r="S58" s="80" t="n"/>
+      <c r="T58" s="80" t="n"/>
+      <c r="U58" s="80" t="n"/>
+      <c r="V58" s="80" t="n"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -20874,9 +21415,22 @@
       <c r="D62" s="70" t="n"/>
       <c r="E62" s="70" t="n"/>
       <c r="F62" s="70" t="n"/>
-      <c r="G62" s="71" t="n"/>
-      <c r="J62" s="5" t="n"/>
-      <c r="K62" s="5" t="n"/>
+      <c r="G62" s="70" t="n"/>
+      <c r="H62" s="70" t="n"/>
+      <c r="I62" s="70" t="n"/>
+      <c r="J62" s="70" t="n"/>
+      <c r="K62" s="70" t="n"/>
+      <c r="L62" s="70" t="n"/>
+      <c r="M62" s="70" t="n"/>
+      <c r="N62" s="70" t="n"/>
+      <c r="O62" s="70" t="n"/>
+      <c r="P62" s="70" t="n"/>
+      <c r="Q62" s="70" t="n"/>
+      <c r="R62" s="70" t="n"/>
+      <c r="S62" s="70" t="n"/>
+      <c r="T62" s="70" t="n"/>
+      <c r="U62" s="70" t="n"/>
+      <c r="V62" s="71" t="n"/>
     </row>
     <row r="63" ht="14.3" customHeight="1" s="33">
       <c r="B63" s="6" t="n"/>
@@ -21097,23 +21651,23 @@
       </c>
       <c r="C67" s="21" t="inlineStr">
         <is>
-          <t>1.1, 1.2, 2, 5.1</t>
+          <t>Q1.1, Q1.2, Q2, Q5.1</t>
         </is>
       </c>
       <c r="D67" s="21" t="inlineStr">
         <is>
-          <t>1.3, 1.4, 1.5, 3, 4, 6</t>
+          <t>Q1.3, Q1.4, Q1.5, Q3, Q4, Q6</t>
         </is>
       </c>
       <c r="E67" s="21" t="inlineStr">
         <is>
-          <t>1.6, 1.7, 7</t>
+          <t>Q1.6, Q1.7, Q7</t>
         </is>
       </c>
       <c r="F67" s="21" t="n"/>
       <c r="G67" s="21" t="inlineStr">
         <is>
-          <t>(5.2-5.4)</t>
+          <t>Q5.2-5.4</t>
         </is>
       </c>
       <c r="H67" s="21" t="n"/>
@@ -21145,23 +21699,23 @@
       </c>
       <c r="C68" s="21" t="inlineStr">
         <is>
-          <t>1.1, 1.2, 1.3, 1.7, 2</t>
+          <t>Q1.1, Q1.2, Q1.3, Q1.7, Q2</t>
         </is>
       </c>
       <c r="D68" s="21" t="inlineStr">
         <is>
-          <t>1.4, 1.6, 4, 5, 8</t>
+          <t>Q1.4, Q1.6, Q4, Q5, Q8</t>
         </is>
       </c>
       <c r="E68" s="21" t="inlineStr">
         <is>
-          <t>6, 7</t>
+          <t>Q6, Q7</t>
         </is>
       </c>
       <c r="F68" s="21" t="n"/>
       <c r="G68" s="21" t="inlineStr">
         <is>
-          <t>1.5, 3</t>
+          <t>Q1.5, Q3</t>
         </is>
       </c>
       <c r="H68" s="21" t="n"/>
@@ -21218,31 +21772,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B70" s="20" t="inlineStr">
+      <c r="B70" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C70" s="21" t="n"/>
-      <c r="D70" s="21" t="n"/>
-      <c r="E70" s="21" t="n"/>
-      <c r="F70" s="21" t="n"/>
-      <c r="G70" s="21" t="n"/>
-      <c r="H70" s="21" t="n"/>
-      <c r="I70" s="21" t="n"/>
-      <c r="J70" s="21" t="n"/>
-      <c r="K70" s="21" t="n"/>
-      <c r="L70" s="21" t="n"/>
-      <c r="M70" s="21" t="n"/>
-      <c r="N70" s="21" t="n"/>
-      <c r="O70" s="21" t="n"/>
-      <c r="P70" s="21" t="n"/>
-      <c r="Q70" s="21" t="n"/>
-      <c r="R70" s="21" t="n"/>
-      <c r="S70" s="21" t="n"/>
-      <c r="T70" s="21" t="n"/>
-      <c r="U70" s="21" t="n"/>
-      <c r="V70" s="21" t="n"/>
+      <c r="C70" s="82" t="n"/>
+      <c r="D70" s="82" t="n"/>
+      <c r="E70" s="82" t="n"/>
+      <c r="F70" s="82" t="n"/>
+      <c r="G70" s="82" t="n"/>
+      <c r="H70" s="82" t="n"/>
+      <c r="I70" s="82" t="n"/>
+      <c r="J70" s="82" t="n"/>
+      <c r="K70" s="82" t="n"/>
+      <c r="L70" s="82" t="n"/>
+      <c r="M70" s="82" t="n"/>
+      <c r="N70" s="82" t="n"/>
+      <c r="O70" s="82" t="n"/>
+      <c r="P70" s="82" t="n"/>
+      <c r="Q70" s="82" t="n"/>
+      <c r="R70" s="82" t="n"/>
+      <c r="S70" s="82" t="n"/>
+      <c r="T70" s="82" t="n"/>
+      <c r="U70" s="82" t="n"/>
+      <c r="V70" s="82" t="n"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -21340,9 +21894,22 @@
       <c r="D74" s="70" t="n"/>
       <c r="E74" s="70" t="n"/>
       <c r="F74" s="70" t="n"/>
-      <c r="G74" s="71" t="n"/>
-      <c r="J74" s="5" t="n"/>
-      <c r="K74" s="5" t="n"/>
+      <c r="G74" s="70" t="n"/>
+      <c r="H74" s="70" t="n"/>
+      <c r="I74" s="70" t="n"/>
+      <c r="J74" s="70" t="n"/>
+      <c r="K74" s="70" t="n"/>
+      <c r="L74" s="70" t="n"/>
+      <c r="M74" s="70" t="n"/>
+      <c r="N74" s="70" t="n"/>
+      <c r="O74" s="70" t="n"/>
+      <c r="P74" s="70" t="n"/>
+      <c r="Q74" s="70" t="n"/>
+      <c r="R74" s="70" t="n"/>
+      <c r="S74" s="70" t="n"/>
+      <c r="T74" s="70" t="n"/>
+      <c r="U74" s="70" t="n"/>
+      <c r="V74" s="71" t="n"/>
     </row>
     <row r="75">
       <c r="B75" s="6" t="n"/>
@@ -21631,7 +22198,7 @@
       <c r="F81" s="31" t="n"/>
       <c r="G81" s="31" t="inlineStr">
         <is>
-          <t>1.1, 1.2, 1.3, 1.4, 2, 3, 4, 5</t>
+          <t>Q1.1, Q1.2, Q1.3, Q1.4, Q2, Q3, Q4, Q5</t>
         </is>
       </c>
       <c r="H81" s="31" t="n"/>
@@ -21667,7 +22234,7 @@
       <c r="F82" s="31" t="n"/>
       <c r="G82" s="31" t="inlineStr">
         <is>
-          <t>1.1, 1.2, 1.3, 1.4, 2, 3, 4, 5</t>
+          <t>Q1.1, Q1.2, Q1.3, Q1.4, Q2, Q3, Q4, Q5</t>
         </is>
       </c>
       <c r="H82" s="31" t="n"/>
@@ -21782,9 +22349,22 @@
       <c r="D86" s="70" t="n"/>
       <c r="E86" s="70" t="n"/>
       <c r="F86" s="70" t="n"/>
-      <c r="G86" s="71" t="n"/>
-      <c r="J86" s="5" t="n"/>
-      <c r="K86" s="5" t="n"/>
+      <c r="G86" s="70" t="n"/>
+      <c r="H86" s="70" t="n"/>
+      <c r="I86" s="70" t="n"/>
+      <c r="J86" s="70" t="n"/>
+      <c r="K86" s="70" t="n"/>
+      <c r="L86" s="70" t="n"/>
+      <c r="M86" s="70" t="n"/>
+      <c r="N86" s="70" t="n"/>
+      <c r="O86" s="70" t="n"/>
+      <c r="P86" s="70" t="n"/>
+      <c r="Q86" s="70" t="n"/>
+      <c r="R86" s="70" t="n"/>
+      <c r="S86" s="70" t="n"/>
+      <c r="T86" s="70" t="n"/>
+      <c r="U86" s="70" t="n"/>
+      <c r="V86" s="71" t="n"/>
     </row>
     <row r="87" ht="14.3" customHeight="1" s="33">
       <c r="B87" s="6" t="n"/>
@@ -22069,12 +22649,12 @@
       </c>
       <c r="C93" s="21" t="inlineStr">
         <is>
-          <t>1.1, 2, 3</t>
+          <t>Q1.1, Q2, Q3</t>
         </is>
       </c>
       <c r="D93" s="21" t="inlineStr">
         <is>
-          <t>1.2, 1.3, 4, 5</t>
+          <t>Q1.2, Q1.3, Q4, Q5</t>
         </is>
       </c>
       <c r="E93" s="21" t="n"/>
@@ -22109,12 +22689,12 @@
       </c>
       <c r="C94" s="21" t="inlineStr">
         <is>
-          <t>1.1, 1.2, 2.2, 3</t>
+          <t>Q1.1, Q1.2, Q2.2, Q3</t>
         </is>
       </c>
       <c r="D94" s="21" t="inlineStr">
         <is>
-          <t>1.3, 2.1, 4, 5</t>
+          <t>Q1.3, Q2.1, Q4, Q5</t>
         </is>
       </c>
       <c r="E94" s="21" t="n"/>
@@ -22202,62 +22782,62 @@
     </row>
   </sheetData>
   <mergeCells count="56">
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="B86:V86"/>
+    <mergeCell ref="B2:V2"/>
+    <mergeCell ref="I15:M15"/>
+    <mergeCell ref="B3:B4"/>
     <mergeCell ref="N63:R63"/>
+    <mergeCell ref="D63:H63"/>
     <mergeCell ref="C63:C64"/>
     <mergeCell ref="I27:M27"/>
+    <mergeCell ref="B14:V14"/>
     <mergeCell ref="N51:R51"/>
-    <mergeCell ref="B38:G38"/>
-    <mergeCell ref="S51:V51"/>
-    <mergeCell ref="B74:G74"/>
-    <mergeCell ref="I75:M75"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="I87:M87"/>
-    <mergeCell ref="D75:H75"/>
-    <mergeCell ref="I3:M3"/>
-    <mergeCell ref="S3:V3"/>
-    <mergeCell ref="D87:H87"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="B26:G26"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="I39:M39"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="D39:H39"/>
-    <mergeCell ref="B75:B76"/>
-    <mergeCell ref="I63:M63"/>
-    <mergeCell ref="B86:G86"/>
-    <mergeCell ref="N27:R27"/>
-    <mergeCell ref="S15:V15"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="I15:M15"/>
-    <mergeCell ref="B14:G14"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="D63:H63"/>
     <mergeCell ref="N75:R75"/>
     <mergeCell ref="S63:V63"/>
     <mergeCell ref="B39:B40"/>
     <mergeCell ref="C75:C76"/>
+    <mergeCell ref="B38:V38"/>
+    <mergeCell ref="S51:V51"/>
     <mergeCell ref="N3:R3"/>
     <mergeCell ref="S75:V75"/>
     <mergeCell ref="D27:H27"/>
+    <mergeCell ref="I75:M75"/>
+    <mergeCell ref="B15:B16"/>
     <mergeCell ref="N39:R39"/>
+    <mergeCell ref="I87:M87"/>
+    <mergeCell ref="D75:H75"/>
+    <mergeCell ref="B74:V74"/>
     <mergeCell ref="S27:V27"/>
     <mergeCell ref="B87:B88"/>
+    <mergeCell ref="I3:M3"/>
     <mergeCell ref="C51:C52"/>
+    <mergeCell ref="S3:V3"/>
+    <mergeCell ref="D87:H87"/>
     <mergeCell ref="S39:V39"/>
-    <mergeCell ref="B50:G50"/>
-    <mergeCell ref="B62:G62"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="B50:V50"/>
+    <mergeCell ref="I39:M39"/>
+    <mergeCell ref="B26:V26"/>
     <mergeCell ref="D3:H3"/>
+    <mergeCell ref="B63:B64"/>
     <mergeCell ref="N87:R87"/>
+    <mergeCell ref="D39:H39"/>
     <mergeCell ref="B51:B52"/>
     <mergeCell ref="C87:C88"/>
+    <mergeCell ref="B75:B76"/>
+    <mergeCell ref="B62:V62"/>
     <mergeCell ref="I51:M51"/>
+    <mergeCell ref="C3:C4"/>
     <mergeCell ref="D15:H15"/>
-    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="I63:M63"/>
+    <mergeCell ref="S87:V87"/>
     <mergeCell ref="N15:R15"/>
-    <mergeCell ref="S87:V87"/>
     <mergeCell ref="D51:H51"/>
     <mergeCell ref="C15:C16"/>
+    <mergeCell ref="N27:R27"/>
+    <mergeCell ref="S15:V15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22306,9 +22886,22 @@
       <c r="D2" s="70" t="n"/>
       <c r="E2" s="70" t="n"/>
       <c r="F2" s="70" t="n"/>
-      <c r="G2" s="71" t="n"/>
-      <c r="J2" s="5" t="n"/>
-      <c r="K2" s="5" t="n"/>
+      <c r="G2" s="70" t="n"/>
+      <c r="H2" s="70" t="n"/>
+      <c r="I2" s="70" t="n"/>
+      <c r="J2" s="70" t="n"/>
+      <c r="K2" s="70" t="n"/>
+      <c r="L2" s="70" t="n"/>
+      <c r="M2" s="70" t="n"/>
+      <c r="N2" s="70" t="n"/>
+      <c r="O2" s="70" t="n"/>
+      <c r="P2" s="70" t="n"/>
+      <c r="Q2" s="70" t="n"/>
+      <c r="R2" s="70" t="n"/>
+      <c r="S2" s="70" t="n"/>
+      <c r="T2" s="70" t="n"/>
+      <c r="U2" s="70" t="n"/>
+      <c r="V2" s="71" t="n"/>
     </row>
     <row r="3" ht="14.3" customHeight="1" s="33">
       <c r="B3" s="6" t="n"/>
@@ -22740,9 +23333,22 @@
       <c r="D14" s="70" t="n"/>
       <c r="E14" s="70" t="n"/>
       <c r="F14" s="70" t="n"/>
-      <c r="G14" s="71" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="n"/>
+      <c r="G14" s="70" t="n"/>
+      <c r="H14" s="70" t="n"/>
+      <c r="I14" s="70" t="n"/>
+      <c r="J14" s="70" t="n"/>
+      <c r="K14" s="70" t="n"/>
+      <c r="L14" s="70" t="n"/>
+      <c r="M14" s="70" t="n"/>
+      <c r="N14" s="70" t="n"/>
+      <c r="O14" s="70" t="n"/>
+      <c r="P14" s="70" t="n"/>
+      <c r="Q14" s="70" t="n"/>
+      <c r="R14" s="70" t="n"/>
+      <c r="S14" s="70" t="n"/>
+      <c r="T14" s="70" t="n"/>
+      <c r="U14" s="70" t="n"/>
+      <c r="V14" s="71" t="n"/>
     </row>
     <row r="15" ht="14.3" customHeight="1" s="33">
       <c r="B15" s="6" t="n"/>
@@ -23174,9 +23780,22 @@
       <c r="D26" s="70" t="n"/>
       <c r="E26" s="70" t="n"/>
       <c r="F26" s="70" t="n"/>
-      <c r="G26" s="71" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="n"/>
+      <c r="G26" s="70" t="n"/>
+      <c r="H26" s="70" t="n"/>
+      <c r="I26" s="70" t="n"/>
+      <c r="J26" s="70" t="n"/>
+      <c r="K26" s="70" t="n"/>
+      <c r="L26" s="70" t="n"/>
+      <c r="M26" s="70" t="n"/>
+      <c r="N26" s="70" t="n"/>
+      <c r="O26" s="70" t="n"/>
+      <c r="P26" s="70" t="n"/>
+      <c r="Q26" s="70" t="n"/>
+      <c r="R26" s="70" t="n"/>
+      <c r="S26" s="70" t="n"/>
+      <c r="T26" s="70" t="n"/>
+      <c r="U26" s="70" t="n"/>
+      <c r="V26" s="71" t="n"/>
     </row>
     <row r="27" ht="14.3" customHeight="1" s="33">
       <c r="B27" s="6" t="n"/>
@@ -23608,9 +24227,22 @@
       <c r="D38" s="70" t="n"/>
       <c r="E38" s="70" t="n"/>
       <c r="F38" s="70" t="n"/>
-      <c r="G38" s="71" t="n"/>
-      <c r="J38" s="5" t="n"/>
-      <c r="K38" s="5" t="n"/>
+      <c r="G38" s="70" t="n"/>
+      <c r="H38" s="70" t="n"/>
+      <c r="I38" s="70" t="n"/>
+      <c r="J38" s="70" t="n"/>
+      <c r="K38" s="70" t="n"/>
+      <c r="L38" s="70" t="n"/>
+      <c r="M38" s="70" t="n"/>
+      <c r="N38" s="70" t="n"/>
+      <c r="O38" s="70" t="n"/>
+      <c r="P38" s="70" t="n"/>
+      <c r="Q38" s="70" t="n"/>
+      <c r="R38" s="70" t="n"/>
+      <c r="S38" s="70" t="n"/>
+      <c r="T38" s="70" t="n"/>
+      <c r="U38" s="70" t="n"/>
+      <c r="V38" s="71" t="n"/>
     </row>
     <row r="39" ht="14.3" customHeight="1" s="33">
       <c r="B39" s="6" t="n"/>
@@ -24042,9 +24674,22 @@
       <c r="D50" s="70" t="n"/>
       <c r="E50" s="70" t="n"/>
       <c r="F50" s="70" t="n"/>
-      <c r="G50" s="71" t="n"/>
-      <c r="J50" s="5" t="n"/>
-      <c r="K50" s="5" t="n"/>
+      <c r="G50" s="70" t="n"/>
+      <c r="H50" s="70" t="n"/>
+      <c r="I50" s="70" t="n"/>
+      <c r="J50" s="70" t="n"/>
+      <c r="K50" s="70" t="n"/>
+      <c r="L50" s="70" t="n"/>
+      <c r="M50" s="70" t="n"/>
+      <c r="N50" s="70" t="n"/>
+      <c r="O50" s="70" t="n"/>
+      <c r="P50" s="70" t="n"/>
+      <c r="Q50" s="70" t="n"/>
+      <c r="R50" s="70" t="n"/>
+      <c r="S50" s="70" t="n"/>
+      <c r="T50" s="70" t="n"/>
+      <c r="U50" s="70" t="n"/>
+      <c r="V50" s="71" t="n"/>
     </row>
     <row r="51" ht="14.3" customHeight="1" s="33">
       <c r="B51" s="6" t="n"/>
@@ -24265,25 +24910,25 @@
       </c>
       <c r="C55" s="31" t="inlineStr">
         <is>
-          <t>1.7, 5</t>
+          <t>Q1.7, Q5</t>
         </is>
       </c>
       <c r="D55" s="31" t="inlineStr">
         <is>
-          <t>1.8, 1.9, 1.10, 6</t>
+          <t>Q1.8, Q1.9, Q1.10, Q6</t>
         </is>
       </c>
       <c r="E55" s="31" t="n"/>
       <c r="F55" s="31" t="n"/>
       <c r="G55" s="31" t="inlineStr">
         <is>
-          <t>1.1, 1.2, 1.3, 1.4, 1.5, 2, 3</t>
+          <t>Q1.1, Q1.2, Q1.3, Q1.4, Q1.5, Q2, Q3</t>
         </is>
       </c>
       <c r="H55" s="31" t="n"/>
       <c r="I55" s="31" t="inlineStr">
         <is>
-          <t>1.6, 4</t>
+          <t>Q1.6, Q4</t>
         </is>
       </c>
       <c r="J55" s="31" t="n"/>
@@ -24313,25 +24958,25 @@
       </c>
       <c r="C56" s="31" t="inlineStr">
         <is>
-          <t>1.4, 5</t>
+          <t>Q1.4, Q5</t>
         </is>
       </c>
       <c r="D56" s="31" t="inlineStr">
         <is>
-          <t>1.2, 1.8, 1.9, 1.10, 7</t>
+          <t>Q1.2, Q1.8, Q1.9, Q1.10, Q7</t>
         </is>
       </c>
       <c r="E56" s="31" t="n"/>
       <c r="F56" s="31" t="n"/>
       <c r="G56" s="31" t="inlineStr">
         <is>
-          <t>1.1, 1.3, 1.5, 1.6, 2, 3, 6</t>
+          <t>Q1.1, Q1.3, Q1.5, Q1.6, Q2, Q3, Q6</t>
         </is>
       </c>
       <c r="H56" s="31" t="n"/>
       <c r="I56" s="31" t="inlineStr">
         <is>
-          <t>1.7, 4</t>
+          <t>Q1.7, Q4</t>
         </is>
       </c>
       <c r="J56" s="31" t="n"/>
@@ -24361,25 +25006,25 @@
       </c>
       <c r="C57" s="31" t="inlineStr">
         <is>
-          <t>1.4, 5</t>
+          <t>Q1.4, Q5</t>
         </is>
       </c>
       <c r="D57" s="31" t="inlineStr">
         <is>
-          <t>1.6, 1.7, 6</t>
+          <t>Q1.6, Q1.7, Q6</t>
         </is>
       </c>
       <c r="E57" s="31" t="n"/>
       <c r="F57" s="31" t="n"/>
       <c r="G57" s="31" t="inlineStr">
         <is>
-          <t>1.1, 1.2, 1.3, 1.8, 1.9, 1.10, 2, 3, 4</t>
+          <t>Q1.1, Q1.2, Q1.3, Q1.8, Q1.9, Q1.10, Q2, Q3, Q4</t>
         </is>
       </c>
       <c r="H57" s="31" t="n"/>
       <c r="I57" s="31" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>Q1.5</t>
         </is>
       </c>
       <c r="J57" s="31" t="n"/>
@@ -24402,31 +25047,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B58" s="20" t="inlineStr">
+      <c r="B58" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C58" s="31" t="n"/>
-      <c r="D58" s="31" t="n"/>
-      <c r="E58" s="31" t="n"/>
-      <c r="F58" s="31" t="n"/>
-      <c r="G58" s="31" t="n"/>
-      <c r="H58" s="31" t="n"/>
-      <c r="I58" s="31" t="n"/>
-      <c r="J58" s="31" t="n"/>
-      <c r="K58" s="31" t="n"/>
-      <c r="L58" s="31" t="n"/>
-      <c r="M58" s="31" t="n"/>
-      <c r="N58" s="31" t="n"/>
-      <c r="O58" s="31" t="n"/>
-      <c r="P58" s="31" t="n"/>
-      <c r="Q58" s="31" t="n"/>
-      <c r="R58" s="31" t="n"/>
-      <c r="S58" s="31" t="n"/>
-      <c r="T58" s="31" t="n"/>
-      <c r="U58" s="31" t="n"/>
-      <c r="V58" s="31" t="n"/>
+      <c r="C58" s="80" t="n"/>
+      <c r="D58" s="80" t="n"/>
+      <c r="E58" s="80" t="n"/>
+      <c r="F58" s="80" t="n"/>
+      <c r="G58" s="80" t="n"/>
+      <c r="H58" s="80" t="n"/>
+      <c r="I58" s="80" t="n"/>
+      <c r="J58" s="80" t="n"/>
+      <c r="K58" s="80" t="n"/>
+      <c r="L58" s="80" t="n"/>
+      <c r="M58" s="80" t="n"/>
+      <c r="N58" s="80" t="n"/>
+      <c r="O58" s="80" t="n"/>
+      <c r="P58" s="80" t="n"/>
+      <c r="Q58" s="80" t="n"/>
+      <c r="R58" s="80" t="n"/>
+      <c r="S58" s="80" t="n"/>
+      <c r="T58" s="80" t="n"/>
+      <c r="U58" s="80" t="n"/>
+      <c r="V58" s="80" t="n"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -24524,9 +25169,22 @@
       <c r="D62" s="70" t="n"/>
       <c r="E62" s="70" t="n"/>
       <c r="F62" s="70" t="n"/>
-      <c r="G62" s="71" t="n"/>
-      <c r="J62" s="5" t="n"/>
-      <c r="K62" s="5" t="n"/>
+      <c r="G62" s="70" t="n"/>
+      <c r="H62" s="70" t="n"/>
+      <c r="I62" s="70" t="n"/>
+      <c r="J62" s="70" t="n"/>
+      <c r="K62" s="70" t="n"/>
+      <c r="L62" s="70" t="n"/>
+      <c r="M62" s="70" t="n"/>
+      <c r="N62" s="70" t="n"/>
+      <c r="O62" s="70" t="n"/>
+      <c r="P62" s="70" t="n"/>
+      <c r="Q62" s="70" t="n"/>
+      <c r="R62" s="70" t="n"/>
+      <c r="S62" s="70" t="n"/>
+      <c r="T62" s="70" t="n"/>
+      <c r="U62" s="70" t="n"/>
+      <c r="V62" s="71" t="n"/>
     </row>
     <row r="63" ht="14.3" customHeight="1" s="33">
       <c r="B63" s="6" t="n"/>
@@ -24747,19 +25405,19 @@
       </c>
       <c r="C67" s="21" t="inlineStr">
         <is>
-          <t>1.3, 1.4, 1.5, 1.9, 2</t>
+          <t>Q1.3, Q1.4, Q1.5, Q1.9, Q2</t>
         </is>
       </c>
       <c r="D67" s="21" t="inlineStr">
         <is>
-          <t>1.1, 1.2, 1.6, 1.7, 1.8, 3, 4, 5</t>
+          <t>Q1.1, Q1.2, Q1.6, Q1.7, Q1.8, Q3, Q4, Q5</t>
         </is>
       </c>
       <c r="E67" s="21" t="n"/>
       <c r="F67" s="21" t="n"/>
       <c r="G67" s="21" t="inlineStr">
         <is>
-          <t>1.10, 6</t>
+          <t>Q1.10, Q6</t>
         </is>
       </c>
       <c r="H67" s="21" t="n"/>
@@ -24791,18 +25449,20 @@
       </c>
       <c r="C68" s="21" t="inlineStr">
         <is>
-          <t>1.1, 1.4, 2, 3</t>
+          <t>Q1.1, Q1.4, Q2, Q3</t>
         </is>
       </c>
       <c r="D68" s="21" t="inlineStr">
         <is>
-          <t>1.2, 1.3, 1.5, 1.6, 1.7, 1.9, 1.10, 4, 5, 6, 8</t>
+          <t>Q1.2, Q1.3, Q1.5, Q1.6, Q1.7, Q1.9, Q1.10, Q4, Q5, Q6, Q8</t>
         </is>
       </c>
       <c r="E68" s="21" t="n"/>
       <c r="F68" s="21" t="n"/>
-      <c r="G68" s="21" t="n">
-        <v>7</v>
+      <c r="G68" s="21" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
       </c>
       <c r="H68" s="21" t="n"/>
       <c r="I68" s="21" t="n"/>
@@ -24858,31 +25518,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B70" s="20" t="inlineStr">
+      <c r="B70" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C70" s="21" t="n"/>
-      <c r="D70" s="21" t="n"/>
-      <c r="E70" s="21" t="n"/>
-      <c r="F70" s="21" t="n"/>
-      <c r="G70" s="21" t="n"/>
-      <c r="H70" s="21" t="n"/>
-      <c r="I70" s="21" t="n"/>
-      <c r="J70" s="21" t="n"/>
-      <c r="K70" s="21" t="n"/>
-      <c r="L70" s="21" t="n"/>
-      <c r="M70" s="21" t="n"/>
-      <c r="N70" s="21" t="n"/>
-      <c r="O70" s="21" t="n"/>
-      <c r="P70" s="21" t="n"/>
-      <c r="Q70" s="21" t="n"/>
-      <c r="R70" s="21" t="n"/>
-      <c r="S70" s="21" t="n"/>
-      <c r="T70" s="21" t="n"/>
-      <c r="U70" s="21" t="n"/>
-      <c r="V70" s="21" t="n"/>
+      <c r="C70" s="82" t="n"/>
+      <c r="D70" s="82" t="n"/>
+      <c r="E70" s="82" t="n"/>
+      <c r="F70" s="82" t="n"/>
+      <c r="G70" s="82" t="n"/>
+      <c r="H70" s="82" t="n"/>
+      <c r="I70" s="82" t="n"/>
+      <c r="J70" s="82" t="n"/>
+      <c r="K70" s="82" t="n"/>
+      <c r="L70" s="82" t="n"/>
+      <c r="M70" s="82" t="n"/>
+      <c r="N70" s="82" t="n"/>
+      <c r="O70" s="82" t="n"/>
+      <c r="P70" s="82" t="n"/>
+      <c r="Q70" s="82" t="n"/>
+      <c r="R70" s="82" t="n"/>
+      <c r="S70" s="82" t="n"/>
+      <c r="T70" s="82" t="n"/>
+      <c r="U70" s="82" t="n"/>
+      <c r="V70" s="82" t="n"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -24980,9 +25640,22 @@
       <c r="D74" s="70" t="n"/>
       <c r="E74" s="70" t="n"/>
       <c r="F74" s="70" t="n"/>
-      <c r="G74" s="71" t="n"/>
-      <c r="J74" s="5" t="n"/>
-      <c r="K74" s="5" t="n"/>
+      <c r="G74" s="70" t="n"/>
+      <c r="H74" s="70" t="n"/>
+      <c r="I74" s="70" t="n"/>
+      <c r="J74" s="70" t="n"/>
+      <c r="K74" s="70" t="n"/>
+      <c r="L74" s="70" t="n"/>
+      <c r="M74" s="70" t="n"/>
+      <c r="N74" s="70" t="n"/>
+      <c r="O74" s="70" t="n"/>
+      <c r="P74" s="70" t="n"/>
+      <c r="Q74" s="70" t="n"/>
+      <c r="R74" s="70" t="n"/>
+      <c r="S74" s="70" t="n"/>
+      <c r="T74" s="70" t="n"/>
+      <c r="U74" s="70" t="n"/>
+      <c r="V74" s="71" t="n"/>
     </row>
     <row r="75" ht="14.3" customHeight="1" s="33">
       <c r="B75" s="6" t="n"/>
@@ -25414,9 +26087,22 @@
       <c r="D86" s="70" t="n"/>
       <c r="E86" s="70" t="n"/>
       <c r="F86" s="70" t="n"/>
-      <c r="G86" s="71" t="n"/>
-      <c r="J86" s="5" t="n"/>
-      <c r="K86" s="5" t="n"/>
+      <c r="G86" s="70" t="n"/>
+      <c r="H86" s="70" t="n"/>
+      <c r="I86" s="70" t="n"/>
+      <c r="J86" s="70" t="n"/>
+      <c r="K86" s="70" t="n"/>
+      <c r="L86" s="70" t="n"/>
+      <c r="M86" s="70" t="n"/>
+      <c r="N86" s="70" t="n"/>
+      <c r="O86" s="70" t="n"/>
+      <c r="P86" s="70" t="n"/>
+      <c r="Q86" s="70" t="n"/>
+      <c r="R86" s="70" t="n"/>
+      <c r="S86" s="70" t="n"/>
+      <c r="T86" s="70" t="n"/>
+      <c r="U86" s="70" t="n"/>
+      <c r="V86" s="71" t="n"/>
     </row>
     <row r="87" ht="14.3" customHeight="1" s="33">
       <c r="B87" s="6" t="n"/>
@@ -25885,62 +26571,62 @@
     </row>
   </sheetData>
   <mergeCells count="56">
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="B86:V86"/>
+    <mergeCell ref="B2:V2"/>
+    <mergeCell ref="I15:M15"/>
+    <mergeCell ref="B3:B4"/>
     <mergeCell ref="N63:R63"/>
+    <mergeCell ref="D63:H63"/>
     <mergeCell ref="C63:C64"/>
     <mergeCell ref="I27:M27"/>
+    <mergeCell ref="B14:V14"/>
     <mergeCell ref="N51:R51"/>
-    <mergeCell ref="B38:G38"/>
-    <mergeCell ref="S51:V51"/>
-    <mergeCell ref="B74:G74"/>
-    <mergeCell ref="I75:M75"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="I87:M87"/>
-    <mergeCell ref="D75:H75"/>
-    <mergeCell ref="I3:M3"/>
-    <mergeCell ref="S3:V3"/>
-    <mergeCell ref="D87:H87"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="B26:G26"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="I39:M39"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="D39:H39"/>
-    <mergeCell ref="B75:B76"/>
-    <mergeCell ref="I63:M63"/>
-    <mergeCell ref="B86:G86"/>
-    <mergeCell ref="N27:R27"/>
-    <mergeCell ref="S15:V15"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="I15:M15"/>
-    <mergeCell ref="B14:G14"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="D63:H63"/>
     <mergeCell ref="N75:R75"/>
     <mergeCell ref="S63:V63"/>
     <mergeCell ref="B39:B40"/>
     <mergeCell ref="C75:C76"/>
+    <mergeCell ref="B38:V38"/>
+    <mergeCell ref="S51:V51"/>
     <mergeCell ref="N3:R3"/>
     <mergeCell ref="S75:V75"/>
     <mergeCell ref="D27:H27"/>
+    <mergeCell ref="I75:M75"/>
+    <mergeCell ref="B15:B16"/>
     <mergeCell ref="N39:R39"/>
+    <mergeCell ref="I87:M87"/>
+    <mergeCell ref="D75:H75"/>
+    <mergeCell ref="B74:V74"/>
     <mergeCell ref="S27:V27"/>
     <mergeCell ref="B87:B88"/>
+    <mergeCell ref="I3:M3"/>
     <mergeCell ref="C51:C52"/>
+    <mergeCell ref="S3:V3"/>
+    <mergeCell ref="D87:H87"/>
     <mergeCell ref="S39:V39"/>
-    <mergeCell ref="B50:G50"/>
-    <mergeCell ref="B62:G62"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="B50:V50"/>
+    <mergeCell ref="I39:M39"/>
+    <mergeCell ref="B26:V26"/>
     <mergeCell ref="D3:H3"/>
+    <mergeCell ref="B63:B64"/>
     <mergeCell ref="N87:R87"/>
+    <mergeCell ref="D39:H39"/>
     <mergeCell ref="B51:B52"/>
     <mergeCell ref="C87:C88"/>
+    <mergeCell ref="B75:B76"/>
+    <mergeCell ref="B62:V62"/>
     <mergeCell ref="I51:M51"/>
+    <mergeCell ref="C3:C4"/>
     <mergeCell ref="D15:H15"/>
-    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="I63:M63"/>
+    <mergeCell ref="S87:V87"/>
     <mergeCell ref="N15:R15"/>
-    <mergeCell ref="S87:V87"/>
     <mergeCell ref="D51:H51"/>
     <mergeCell ref="C15:C16"/>
+    <mergeCell ref="N27:R27"/>
+    <mergeCell ref="S15:V15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25989,9 +26675,22 @@
       <c r="D2" s="70" t="n"/>
       <c r="E2" s="70" t="n"/>
       <c r="F2" s="70" t="n"/>
-      <c r="G2" s="71" t="n"/>
-      <c r="J2" s="5" t="n"/>
-      <c r="K2" s="5" t="n"/>
+      <c r="G2" s="70" t="n"/>
+      <c r="H2" s="70" t="n"/>
+      <c r="I2" s="70" t="n"/>
+      <c r="J2" s="70" t="n"/>
+      <c r="K2" s="70" t="n"/>
+      <c r="L2" s="70" t="n"/>
+      <c r="M2" s="70" t="n"/>
+      <c r="N2" s="70" t="n"/>
+      <c r="O2" s="70" t="n"/>
+      <c r="P2" s="70" t="n"/>
+      <c r="Q2" s="70" t="n"/>
+      <c r="R2" s="70" t="n"/>
+      <c r="S2" s="70" t="n"/>
+      <c r="T2" s="70" t="n"/>
+      <c r="U2" s="70" t="n"/>
+      <c r="V2" s="71" t="n"/>
     </row>
     <row r="3" ht="14.3" customHeight="1" s="33">
       <c r="B3" s="6" t="n"/>
@@ -26423,9 +27122,22 @@
       <c r="D14" s="70" t="n"/>
       <c r="E14" s="70" t="n"/>
       <c r="F14" s="70" t="n"/>
-      <c r="G14" s="71" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="n"/>
+      <c r="G14" s="70" t="n"/>
+      <c r="H14" s="70" t="n"/>
+      <c r="I14" s="70" t="n"/>
+      <c r="J14" s="70" t="n"/>
+      <c r="K14" s="70" t="n"/>
+      <c r="L14" s="70" t="n"/>
+      <c r="M14" s="70" t="n"/>
+      <c r="N14" s="70" t="n"/>
+      <c r="O14" s="70" t="n"/>
+      <c r="P14" s="70" t="n"/>
+      <c r="Q14" s="70" t="n"/>
+      <c r="R14" s="70" t="n"/>
+      <c r="S14" s="70" t="n"/>
+      <c r="T14" s="70" t="n"/>
+      <c r="U14" s="70" t="n"/>
+      <c r="V14" s="71" t="n"/>
     </row>
     <row r="15" ht="14.3" customHeight="1" s="33">
       <c r="B15" s="6" t="n"/>
@@ -26857,9 +27569,22 @@
       <c r="D26" s="70" t="n"/>
       <c r="E26" s="70" t="n"/>
       <c r="F26" s="70" t="n"/>
-      <c r="G26" s="71" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="n"/>
+      <c r="G26" s="70" t="n"/>
+      <c r="H26" s="70" t="n"/>
+      <c r="I26" s="70" t="n"/>
+      <c r="J26" s="70" t="n"/>
+      <c r="K26" s="70" t="n"/>
+      <c r="L26" s="70" t="n"/>
+      <c r="M26" s="70" t="n"/>
+      <c r="N26" s="70" t="n"/>
+      <c r="O26" s="70" t="n"/>
+      <c r="P26" s="70" t="n"/>
+      <c r="Q26" s="70" t="n"/>
+      <c r="R26" s="70" t="n"/>
+      <c r="S26" s="70" t="n"/>
+      <c r="T26" s="70" t="n"/>
+      <c r="U26" s="70" t="n"/>
+      <c r="V26" s="71" t="n"/>
     </row>
     <row r="27" ht="14.3" customHeight="1" s="33">
       <c r="B27" s="6" t="n"/>
@@ -27291,9 +28016,22 @@
       <c r="D38" s="70" t="n"/>
       <c r="E38" s="70" t="n"/>
       <c r="F38" s="70" t="n"/>
-      <c r="G38" s="71" t="n"/>
-      <c r="J38" s="5" t="n"/>
-      <c r="K38" s="5" t="n"/>
+      <c r="G38" s="70" t="n"/>
+      <c r="H38" s="70" t="n"/>
+      <c r="I38" s="70" t="n"/>
+      <c r="J38" s="70" t="n"/>
+      <c r="K38" s="70" t="n"/>
+      <c r="L38" s="70" t="n"/>
+      <c r="M38" s="70" t="n"/>
+      <c r="N38" s="70" t="n"/>
+      <c r="O38" s="70" t="n"/>
+      <c r="P38" s="70" t="n"/>
+      <c r="Q38" s="70" t="n"/>
+      <c r="R38" s="70" t="n"/>
+      <c r="S38" s="70" t="n"/>
+      <c r="T38" s="70" t="n"/>
+      <c r="U38" s="70" t="n"/>
+      <c r="V38" s="71" t="n"/>
     </row>
     <row r="39" ht="14.3" customHeight="1" s="33">
       <c r="B39" s="6" t="n"/>
@@ -27725,9 +28463,22 @@
       <c r="D50" s="70" t="n"/>
       <c r="E50" s="70" t="n"/>
       <c r="F50" s="70" t="n"/>
-      <c r="G50" s="71" t="n"/>
-      <c r="J50" s="5" t="n"/>
-      <c r="K50" s="5" t="n"/>
+      <c r="G50" s="70" t="n"/>
+      <c r="H50" s="70" t="n"/>
+      <c r="I50" s="70" t="n"/>
+      <c r="J50" s="70" t="n"/>
+      <c r="K50" s="70" t="n"/>
+      <c r="L50" s="70" t="n"/>
+      <c r="M50" s="70" t="n"/>
+      <c r="N50" s="70" t="n"/>
+      <c r="O50" s="70" t="n"/>
+      <c r="P50" s="70" t="n"/>
+      <c r="Q50" s="70" t="n"/>
+      <c r="R50" s="70" t="n"/>
+      <c r="S50" s="70" t="n"/>
+      <c r="T50" s="70" t="n"/>
+      <c r="U50" s="70" t="n"/>
+      <c r="V50" s="71" t="n"/>
     </row>
     <row r="51" ht="14.3" customHeight="1" s="33">
       <c r="B51" s="6" t="n"/>
@@ -28037,31 +28788,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B58" s="20" t="inlineStr">
+      <c r="B58" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C58" s="31" t="n"/>
-      <c r="D58" s="31" t="n"/>
-      <c r="E58" s="31" t="n"/>
-      <c r="F58" s="31" t="n"/>
-      <c r="G58" s="31" t="n"/>
-      <c r="H58" s="31" t="n"/>
-      <c r="I58" s="31" t="n"/>
-      <c r="J58" s="31" t="n"/>
-      <c r="K58" s="31" t="n"/>
-      <c r="L58" s="31" t="n"/>
-      <c r="M58" s="31" t="n"/>
-      <c r="N58" s="31" t="n"/>
-      <c r="O58" s="31" t="n"/>
-      <c r="P58" s="31" t="n"/>
-      <c r="Q58" s="31" t="n"/>
-      <c r="R58" s="31" t="n"/>
-      <c r="S58" s="31" t="n"/>
-      <c r="T58" s="31" t="n"/>
-      <c r="U58" s="31" t="n"/>
-      <c r="V58" s="31" t="n"/>
+      <c r="C58" s="80" t="n"/>
+      <c r="D58" s="80" t="n"/>
+      <c r="E58" s="80" t="n"/>
+      <c r="F58" s="80" t="n"/>
+      <c r="G58" s="80" t="n"/>
+      <c r="H58" s="80" t="n"/>
+      <c r="I58" s="80" t="n"/>
+      <c r="J58" s="80" t="n"/>
+      <c r="K58" s="80" t="n"/>
+      <c r="L58" s="80" t="n"/>
+      <c r="M58" s="80" t="n"/>
+      <c r="N58" s="80" t="n"/>
+      <c r="O58" s="80" t="n"/>
+      <c r="P58" s="80" t="n"/>
+      <c r="Q58" s="80" t="n"/>
+      <c r="R58" s="80" t="n"/>
+      <c r="S58" s="80" t="n"/>
+      <c r="T58" s="80" t="n"/>
+      <c r="U58" s="80" t="n"/>
+      <c r="V58" s="80" t="n"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -28159,9 +28910,22 @@
       <c r="D62" s="70" t="n"/>
       <c r="E62" s="70" t="n"/>
       <c r="F62" s="70" t="n"/>
-      <c r="G62" s="71" t="n"/>
-      <c r="J62" s="5" t="n"/>
-      <c r="K62" s="5" t="n"/>
+      <c r="G62" s="70" t="n"/>
+      <c r="H62" s="70" t="n"/>
+      <c r="I62" s="70" t="n"/>
+      <c r="J62" s="70" t="n"/>
+      <c r="K62" s="70" t="n"/>
+      <c r="L62" s="70" t="n"/>
+      <c r="M62" s="70" t="n"/>
+      <c r="N62" s="70" t="n"/>
+      <c r="O62" s="70" t="n"/>
+      <c r="P62" s="70" t="n"/>
+      <c r="Q62" s="70" t="n"/>
+      <c r="R62" s="70" t="n"/>
+      <c r="S62" s="70" t="n"/>
+      <c r="T62" s="70" t="n"/>
+      <c r="U62" s="70" t="n"/>
+      <c r="V62" s="71" t="n"/>
     </row>
     <row r="63" ht="14.3" customHeight="1" s="33">
       <c r="B63" s="6" t="n"/>
@@ -28471,31 +29235,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B70" s="20" t="inlineStr">
+      <c r="B70" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C70" s="21" t="n"/>
-      <c r="D70" s="21" t="n"/>
-      <c r="E70" s="21" t="n"/>
-      <c r="F70" s="21" t="n"/>
-      <c r="G70" s="21" t="n"/>
-      <c r="H70" s="21" t="n"/>
-      <c r="I70" s="21" t="n"/>
-      <c r="J70" s="21" t="n"/>
-      <c r="K70" s="21" t="n"/>
-      <c r="L70" s="21" t="n"/>
-      <c r="M70" s="21" t="n"/>
-      <c r="N70" s="21" t="n"/>
-      <c r="O70" s="21" t="n"/>
-      <c r="P70" s="21" t="n"/>
-      <c r="Q70" s="21" t="n"/>
-      <c r="R70" s="21" t="n"/>
-      <c r="S70" s="21" t="n"/>
-      <c r="T70" s="21" t="n"/>
-      <c r="U70" s="21" t="n"/>
-      <c r="V70" s="21" t="n"/>
+      <c r="C70" s="82" t="n"/>
+      <c r="D70" s="82" t="n"/>
+      <c r="E70" s="82" t="n"/>
+      <c r="F70" s="82" t="n"/>
+      <c r="G70" s="82" t="n"/>
+      <c r="H70" s="82" t="n"/>
+      <c r="I70" s="82" t="n"/>
+      <c r="J70" s="82" t="n"/>
+      <c r="K70" s="82" t="n"/>
+      <c r="L70" s="82" t="n"/>
+      <c r="M70" s="82" t="n"/>
+      <c r="N70" s="82" t="n"/>
+      <c r="O70" s="82" t="n"/>
+      <c r="P70" s="82" t="n"/>
+      <c r="Q70" s="82" t="n"/>
+      <c r="R70" s="82" t="n"/>
+      <c r="S70" s="82" t="n"/>
+      <c r="T70" s="82" t="n"/>
+      <c r="U70" s="82" t="n"/>
+      <c r="V70" s="82" t="n"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -28593,9 +29357,22 @@
       <c r="D74" s="70" t="n"/>
       <c r="E74" s="70" t="n"/>
       <c r="F74" s="70" t="n"/>
-      <c r="G74" s="71" t="n"/>
-      <c r="J74" s="5" t="n"/>
-      <c r="K74" s="5" t="n"/>
+      <c r="G74" s="70" t="n"/>
+      <c r="H74" s="70" t="n"/>
+      <c r="I74" s="70" t="n"/>
+      <c r="J74" s="70" t="n"/>
+      <c r="K74" s="70" t="n"/>
+      <c r="L74" s="70" t="n"/>
+      <c r="M74" s="70" t="n"/>
+      <c r="N74" s="70" t="n"/>
+      <c r="O74" s="70" t="n"/>
+      <c r="P74" s="70" t="n"/>
+      <c r="Q74" s="70" t="n"/>
+      <c r="R74" s="70" t="n"/>
+      <c r="S74" s="70" t="n"/>
+      <c r="T74" s="70" t="n"/>
+      <c r="U74" s="70" t="n"/>
+      <c r="V74" s="71" t="n"/>
     </row>
     <row r="75" ht="14.3" customHeight="1" s="33">
       <c r="B75" s="6" t="n"/>
@@ -29027,9 +29804,22 @@
       <c r="D86" s="70" t="n"/>
       <c r="E86" s="70" t="n"/>
       <c r="F86" s="70" t="n"/>
-      <c r="G86" s="71" t="n"/>
-      <c r="J86" s="5" t="n"/>
-      <c r="K86" s="5" t="n"/>
+      <c r="G86" s="70" t="n"/>
+      <c r="H86" s="70" t="n"/>
+      <c r="I86" s="70" t="n"/>
+      <c r="J86" s="70" t="n"/>
+      <c r="K86" s="70" t="n"/>
+      <c r="L86" s="70" t="n"/>
+      <c r="M86" s="70" t="n"/>
+      <c r="N86" s="70" t="n"/>
+      <c r="O86" s="70" t="n"/>
+      <c r="P86" s="70" t="n"/>
+      <c r="Q86" s="70" t="n"/>
+      <c r="R86" s="70" t="n"/>
+      <c r="S86" s="70" t="n"/>
+      <c r="T86" s="70" t="n"/>
+      <c r="U86" s="70" t="n"/>
+      <c r="V86" s="71" t="n"/>
     </row>
     <row r="87" ht="14.3" customHeight="1" s="33">
       <c r="B87" s="6" t="n"/>
@@ -29453,62 +30243,62 @@
     </row>
   </sheetData>
   <mergeCells count="56">
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="B86:V86"/>
+    <mergeCell ref="B2:V2"/>
+    <mergeCell ref="I15:M15"/>
+    <mergeCell ref="B3:B4"/>
     <mergeCell ref="N63:R63"/>
+    <mergeCell ref="D63:H63"/>
     <mergeCell ref="C63:C64"/>
     <mergeCell ref="I27:M27"/>
+    <mergeCell ref="B14:V14"/>
     <mergeCell ref="N51:R51"/>
-    <mergeCell ref="B38:G38"/>
-    <mergeCell ref="S51:V51"/>
-    <mergeCell ref="B74:G74"/>
-    <mergeCell ref="I75:M75"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="I87:M87"/>
-    <mergeCell ref="D75:H75"/>
-    <mergeCell ref="I3:M3"/>
-    <mergeCell ref="S3:V3"/>
-    <mergeCell ref="D87:H87"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="B26:G26"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="I39:M39"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="D39:H39"/>
-    <mergeCell ref="B75:B76"/>
-    <mergeCell ref="I63:M63"/>
-    <mergeCell ref="B86:G86"/>
-    <mergeCell ref="N27:R27"/>
-    <mergeCell ref="S15:V15"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="I15:M15"/>
-    <mergeCell ref="B14:G14"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="D63:H63"/>
     <mergeCell ref="N75:R75"/>
     <mergeCell ref="S63:V63"/>
     <mergeCell ref="B39:B40"/>
     <mergeCell ref="C75:C76"/>
+    <mergeCell ref="B38:V38"/>
+    <mergeCell ref="S51:V51"/>
     <mergeCell ref="N3:R3"/>
     <mergeCell ref="S75:V75"/>
     <mergeCell ref="D27:H27"/>
+    <mergeCell ref="I75:M75"/>
+    <mergeCell ref="B15:B16"/>
     <mergeCell ref="N39:R39"/>
+    <mergeCell ref="I87:M87"/>
+    <mergeCell ref="D75:H75"/>
+    <mergeCell ref="B74:V74"/>
     <mergeCell ref="S27:V27"/>
     <mergeCell ref="B87:B88"/>
+    <mergeCell ref="I3:M3"/>
     <mergeCell ref="C51:C52"/>
+    <mergeCell ref="S3:V3"/>
+    <mergeCell ref="D87:H87"/>
     <mergeCell ref="S39:V39"/>
-    <mergeCell ref="B50:G50"/>
-    <mergeCell ref="B62:G62"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="B50:V50"/>
+    <mergeCell ref="I39:M39"/>
+    <mergeCell ref="B26:V26"/>
     <mergeCell ref="D3:H3"/>
+    <mergeCell ref="B63:B64"/>
     <mergeCell ref="N87:R87"/>
+    <mergeCell ref="D39:H39"/>
     <mergeCell ref="B51:B52"/>
     <mergeCell ref="C87:C88"/>
+    <mergeCell ref="B75:B76"/>
+    <mergeCell ref="B62:V62"/>
     <mergeCell ref="I51:M51"/>
+    <mergeCell ref="C3:C4"/>
     <mergeCell ref="D15:H15"/>
-    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="I63:M63"/>
+    <mergeCell ref="S87:V87"/>
     <mergeCell ref="N15:R15"/>
-    <mergeCell ref="S87:V87"/>
     <mergeCell ref="D51:H51"/>
     <mergeCell ref="C15:C16"/>
+    <mergeCell ref="N27:R27"/>
+    <mergeCell ref="S15:V15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -29557,7 +30347,22 @@
       <c r="D2" s="70" t="n"/>
       <c r="E2" s="70" t="n"/>
       <c r="F2" s="70" t="n"/>
-      <c r="G2" s="71" t="n"/>
+      <c r="G2" s="70" t="n"/>
+      <c r="H2" s="70" t="n"/>
+      <c r="I2" s="70" t="n"/>
+      <c r="J2" s="70" t="n"/>
+      <c r="K2" s="70" t="n"/>
+      <c r="L2" s="70" t="n"/>
+      <c r="M2" s="70" t="n"/>
+      <c r="N2" s="70" t="n"/>
+      <c r="O2" s="70" t="n"/>
+      <c r="P2" s="70" t="n"/>
+      <c r="Q2" s="70" t="n"/>
+      <c r="R2" s="70" t="n"/>
+      <c r="S2" s="70" t="n"/>
+      <c r="T2" s="70" t="n"/>
+      <c r="U2" s="70" t="n"/>
+      <c r="V2" s="71" t="n"/>
     </row>
     <row r="3">
       <c r="B3" s="6" t="n"/>
@@ -29707,31 +30512,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="79" t="inlineStr">
         <is>
           <t>Nov_2015</t>
         </is>
       </c>
-      <c r="C5" s="21" t="n"/>
-      <c r="D5" s="21" t="n"/>
-      <c r="E5" s="21" t="n"/>
-      <c r="F5" s="21" t="n"/>
-      <c r="G5" s="21" t="n"/>
-      <c r="H5" s="21" t="n"/>
-      <c r="I5" s="21" t="n"/>
-      <c r="J5" s="21" t="n"/>
-      <c r="K5" s="21" t="n"/>
-      <c r="L5" s="21" t="n"/>
-      <c r="M5" s="21" t="n"/>
-      <c r="N5" s="21" t="n"/>
-      <c r="O5" s="21" t="n"/>
-      <c r="P5" s="21" t="n"/>
-      <c r="Q5" s="21" t="n"/>
-      <c r="R5" s="21" t="n"/>
-      <c r="S5" s="21" t="n"/>
-      <c r="T5" s="21" t="n"/>
-      <c r="U5" s="21" t="n"/>
-      <c r="V5" s="21" t="n"/>
+      <c r="C5" s="82" t="n"/>
+      <c r="D5" s="82" t="n"/>
+      <c r="E5" s="82" t="n"/>
+      <c r="F5" s="82" t="n"/>
+      <c r="G5" s="82" t="n"/>
+      <c r="H5" s="82" t="n"/>
+      <c r="I5" s="82" t="n"/>
+      <c r="J5" s="82" t="n"/>
+      <c r="K5" s="82" t="n"/>
+      <c r="L5" s="82" t="n"/>
+      <c r="M5" s="82" t="n"/>
+      <c r="N5" s="82" t="n"/>
+      <c r="O5" s="82" t="n"/>
+      <c r="P5" s="82" t="n"/>
+      <c r="Q5" s="82" t="n"/>
+      <c r="R5" s="82" t="n"/>
+      <c r="S5" s="82" t="n"/>
+      <c r="T5" s="82" t="n"/>
+      <c r="U5" s="82" t="n"/>
+      <c r="V5" s="82" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -29739,31 +30544,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="83" t="inlineStr">
         <is>
           <t>Nov_2016</t>
         </is>
       </c>
-      <c r="C6" s="21" t="n"/>
-      <c r="D6" s="21" t="n"/>
-      <c r="E6" s="21" t="n"/>
-      <c r="F6" s="21" t="n"/>
-      <c r="G6" s="21" t="n"/>
-      <c r="H6" s="21" t="n"/>
-      <c r="I6" s="21" t="n"/>
-      <c r="J6" s="21" t="n"/>
-      <c r="K6" s="21" t="n"/>
-      <c r="L6" s="21" t="n"/>
-      <c r="M6" s="21" t="n"/>
-      <c r="N6" s="21" t="n"/>
-      <c r="O6" s="21" t="n"/>
-      <c r="P6" s="21" t="n"/>
-      <c r="Q6" s="21" t="n"/>
-      <c r="R6" s="21" t="n"/>
-      <c r="S6" s="21" t="n"/>
-      <c r="T6" s="21" t="n"/>
-      <c r="U6" s="21" t="n"/>
-      <c r="V6" s="21" t="n"/>
+      <c r="C6" s="82" t="n"/>
+      <c r="D6" s="82" t="n"/>
+      <c r="E6" s="82" t="n"/>
+      <c r="F6" s="82" t="n"/>
+      <c r="G6" s="82" t="n"/>
+      <c r="H6" s="82" t="n"/>
+      <c r="I6" s="82" t="n"/>
+      <c r="J6" s="82" t="n"/>
+      <c r="K6" s="82" t="n"/>
+      <c r="L6" s="82" t="n"/>
+      <c r="M6" s="82" t="n"/>
+      <c r="N6" s="82" t="n"/>
+      <c r="O6" s="82" t="n"/>
+      <c r="P6" s="82" t="n"/>
+      <c r="Q6" s="82" t="n"/>
+      <c r="R6" s="82" t="n"/>
+      <c r="S6" s="82" t="n"/>
+      <c r="T6" s="82" t="n"/>
+      <c r="U6" s="82" t="n"/>
+      <c r="V6" s="82" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -29771,31 +30576,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="79" t="inlineStr">
         <is>
           <t>Nov_2017</t>
         </is>
       </c>
-      <c r="C7" s="21" t="n"/>
-      <c r="D7" s="21" t="n"/>
-      <c r="E7" s="21" t="n"/>
-      <c r="F7" s="21" t="n"/>
-      <c r="G7" s="21" t="n"/>
-      <c r="H7" s="21" t="n"/>
-      <c r="I7" s="21" t="n"/>
-      <c r="J7" s="21" t="n"/>
-      <c r="K7" s="21" t="n"/>
-      <c r="L7" s="21" t="n"/>
-      <c r="M7" s="21" t="n"/>
-      <c r="N7" s="21" t="n"/>
-      <c r="O7" s="21" t="n"/>
-      <c r="P7" s="21" t="n"/>
-      <c r="Q7" s="21" t="n"/>
-      <c r="R7" s="21" t="n"/>
-      <c r="S7" s="21" t="n"/>
-      <c r="T7" s="21" t="n"/>
-      <c r="U7" s="21" t="n"/>
-      <c r="V7" s="21" t="n"/>
+      <c r="C7" s="82" t="n"/>
+      <c r="D7" s="82" t="n"/>
+      <c r="E7" s="82" t="n"/>
+      <c r="F7" s="82" t="n"/>
+      <c r="G7" s="82" t="n"/>
+      <c r="H7" s="82" t="n"/>
+      <c r="I7" s="82" t="n"/>
+      <c r="J7" s="82" t="n"/>
+      <c r="K7" s="82" t="n"/>
+      <c r="L7" s="82" t="n"/>
+      <c r="M7" s="82" t="n"/>
+      <c r="N7" s="82" t="n"/>
+      <c r="O7" s="82" t="n"/>
+      <c r="P7" s="82" t="n"/>
+      <c r="Q7" s="82" t="n"/>
+      <c r="R7" s="82" t="n"/>
+      <c r="S7" s="82" t="n"/>
+      <c r="T7" s="82" t="n"/>
+      <c r="U7" s="82" t="n"/>
+      <c r="V7" s="82" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -29803,31 +30608,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="79" t="inlineStr">
         <is>
           <t>Nov_2018</t>
         </is>
       </c>
-      <c r="C8" s="21" t="n"/>
-      <c r="D8" s="21" t="n"/>
-      <c r="E8" s="21" t="n"/>
-      <c r="F8" s="21" t="n"/>
-      <c r="G8" s="21" t="n"/>
-      <c r="H8" s="21" t="n"/>
-      <c r="I8" s="21" t="n"/>
-      <c r="J8" s="21" t="n"/>
-      <c r="K8" s="21" t="n"/>
-      <c r="L8" s="21" t="n"/>
-      <c r="M8" s="21" t="n"/>
-      <c r="N8" s="21" t="n"/>
-      <c r="O8" s="21" t="n"/>
-      <c r="P8" s="21" t="n"/>
-      <c r="Q8" s="21" t="n"/>
-      <c r="R8" s="21" t="n"/>
-      <c r="S8" s="21" t="n"/>
-      <c r="T8" s="21" t="n"/>
-      <c r="U8" s="21" t="n"/>
-      <c r="V8" s="21" t="n"/>
+      <c r="C8" s="82" t="n"/>
+      <c r="D8" s="82" t="n"/>
+      <c r="E8" s="82" t="n"/>
+      <c r="F8" s="82" t="n"/>
+      <c r="G8" s="82" t="n"/>
+      <c r="H8" s="82" t="n"/>
+      <c r="I8" s="82" t="n"/>
+      <c r="J8" s="82" t="n"/>
+      <c r="K8" s="82" t="n"/>
+      <c r="L8" s="82" t="n"/>
+      <c r="M8" s="82" t="n"/>
+      <c r="N8" s="82" t="n"/>
+      <c r="O8" s="82" t="n"/>
+      <c r="P8" s="82" t="n"/>
+      <c r="Q8" s="82" t="n"/>
+      <c r="R8" s="82" t="n"/>
+      <c r="S8" s="82" t="n"/>
+      <c r="T8" s="82" t="n"/>
+      <c r="U8" s="82" t="n"/>
+      <c r="V8" s="82" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -29835,31 +30640,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="79" t="inlineStr">
         <is>
           <t>Nov_2019</t>
         </is>
       </c>
-      <c r="C9" s="21" t="n"/>
-      <c r="D9" s="21" t="n"/>
-      <c r="E9" s="21" t="n"/>
-      <c r="F9" s="21" t="n"/>
-      <c r="G9" s="21" t="n"/>
-      <c r="H9" s="21" t="n"/>
-      <c r="I9" s="21" t="n"/>
-      <c r="J9" s="21" t="n"/>
-      <c r="K9" s="21" t="n"/>
-      <c r="L9" s="21" t="n"/>
-      <c r="M9" s="21" t="n"/>
-      <c r="N9" s="21" t="n"/>
-      <c r="O9" s="21" t="n"/>
-      <c r="P9" s="21" t="n"/>
-      <c r="Q9" s="21" t="n"/>
-      <c r="R9" s="21" t="n"/>
-      <c r="S9" s="21" t="n"/>
-      <c r="T9" s="21" t="n"/>
-      <c r="U9" s="21" t="n"/>
-      <c r="V9" s="21" t="n"/>
+      <c r="C9" s="82" t="n"/>
+      <c r="D9" s="82" t="n"/>
+      <c r="E9" s="82" t="n"/>
+      <c r="F9" s="82" t="n"/>
+      <c r="G9" s="82" t="n"/>
+      <c r="H9" s="82" t="n"/>
+      <c r="I9" s="82" t="n"/>
+      <c r="J9" s="82" t="n"/>
+      <c r="K9" s="82" t="n"/>
+      <c r="L9" s="82" t="n"/>
+      <c r="M9" s="82" t="n"/>
+      <c r="N9" s="82" t="n"/>
+      <c r="O9" s="82" t="n"/>
+      <c r="P9" s="82" t="n"/>
+      <c r="Q9" s="82" t="n"/>
+      <c r="R9" s="82" t="n"/>
+      <c r="S9" s="82" t="n"/>
+      <c r="T9" s="82" t="n"/>
+      <c r="U9" s="82" t="n"/>
+      <c r="V9" s="82" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -29867,31 +30672,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="79" t="inlineStr">
         <is>
           <t>Nov_2020</t>
         </is>
       </c>
-      <c r="C10" s="21" t="n"/>
-      <c r="D10" s="21" t="n"/>
-      <c r="E10" s="21" t="n"/>
-      <c r="F10" s="21" t="n"/>
-      <c r="G10" s="21" t="n"/>
-      <c r="H10" s="21" t="n"/>
-      <c r="I10" s="21" t="n"/>
-      <c r="J10" s="21" t="n"/>
-      <c r="K10" s="21" t="n"/>
-      <c r="L10" s="21" t="n"/>
-      <c r="M10" s="21" t="n"/>
-      <c r="N10" s="21" t="n"/>
-      <c r="O10" s="21" t="n"/>
-      <c r="P10" s="21" t="n"/>
-      <c r="Q10" s="21" t="n"/>
-      <c r="R10" s="21" t="n"/>
-      <c r="S10" s="21" t="n"/>
-      <c r="T10" s="21" t="n"/>
-      <c r="U10" s="21" t="n"/>
-      <c r="V10" s="21" t="n"/>
+      <c r="C10" s="82" t="n"/>
+      <c r="D10" s="82" t="n"/>
+      <c r="E10" s="82" t="n"/>
+      <c r="F10" s="82" t="n"/>
+      <c r="G10" s="82" t="n"/>
+      <c r="H10" s="82" t="n"/>
+      <c r="I10" s="82" t="n"/>
+      <c r="J10" s="82" t="n"/>
+      <c r="K10" s="82" t="n"/>
+      <c r="L10" s="82" t="n"/>
+      <c r="M10" s="82" t="n"/>
+      <c r="N10" s="82" t="n"/>
+      <c r="O10" s="82" t="n"/>
+      <c r="P10" s="82" t="n"/>
+      <c r="Q10" s="82" t="n"/>
+      <c r="R10" s="82" t="n"/>
+      <c r="S10" s="82" t="n"/>
+      <c r="T10" s="82" t="n"/>
+      <c r="U10" s="82" t="n"/>
+      <c r="V10" s="82" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -29899,31 +30704,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="79" t="inlineStr">
         <is>
           <t>Nov_2021</t>
         </is>
       </c>
-      <c r="C11" s="21" t="n"/>
-      <c r="D11" s="21" t="n"/>
-      <c r="E11" s="21" t="n"/>
-      <c r="F11" s="21" t="n"/>
-      <c r="G11" s="21" t="n"/>
-      <c r="H11" s="21" t="n"/>
-      <c r="I11" s="21" t="n"/>
-      <c r="J11" s="21" t="n"/>
-      <c r="K11" s="21" t="n"/>
-      <c r="L11" s="21" t="n"/>
-      <c r="M11" s="21" t="n"/>
-      <c r="N11" s="21" t="n"/>
-      <c r="O11" s="21" t="n"/>
-      <c r="P11" s="21" t="n"/>
-      <c r="Q11" s="21" t="n"/>
-      <c r="R11" s="21" t="n"/>
-      <c r="S11" s="21" t="n"/>
-      <c r="T11" s="21" t="n"/>
-      <c r="U11" s="21" t="n"/>
-      <c r="V11" s="21" t="n"/>
+      <c r="C11" s="82" t="n"/>
+      <c r="D11" s="82" t="n"/>
+      <c r="E11" s="82" t="n"/>
+      <c r="F11" s="82" t="n"/>
+      <c r="G11" s="82" t="n"/>
+      <c r="H11" s="82" t="n"/>
+      <c r="I11" s="82" t="n"/>
+      <c r="J11" s="82" t="n"/>
+      <c r="K11" s="82" t="n"/>
+      <c r="L11" s="82" t="n"/>
+      <c r="M11" s="82" t="n"/>
+      <c r="N11" s="82" t="n"/>
+      <c r="O11" s="82" t="n"/>
+      <c r="P11" s="82" t="n"/>
+      <c r="Q11" s="82" t="n"/>
+      <c r="R11" s="82" t="n"/>
+      <c r="S11" s="82" t="n"/>
+      <c r="T11" s="82" t="n"/>
+      <c r="U11" s="82" t="n"/>
+      <c r="V11" s="82" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1" s="33">
       <c r="A12" t="inlineStr">
@@ -29931,31 +30736,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B12" s="28" t="inlineStr">
+      <c r="B12" s="81" t="inlineStr">
         <is>
           <t>Nov_2022</t>
         </is>
       </c>
-      <c r="C12" s="21" t="n"/>
-      <c r="D12" s="21" t="n"/>
-      <c r="E12" s="21" t="n"/>
-      <c r="F12" s="21" t="n"/>
-      <c r="G12" s="21" t="n"/>
-      <c r="H12" s="21" t="n"/>
-      <c r="I12" s="21" t="n"/>
-      <c r="J12" s="21" t="n"/>
-      <c r="K12" s="21" t="n"/>
-      <c r="L12" s="21" t="n"/>
-      <c r="M12" s="21" t="n"/>
-      <c r="N12" s="21" t="n"/>
-      <c r="O12" s="21" t="n"/>
-      <c r="P12" s="21" t="n"/>
-      <c r="Q12" s="21" t="n"/>
-      <c r="R12" s="21" t="n"/>
-      <c r="S12" s="21" t="n"/>
-      <c r="T12" s="21" t="n"/>
-      <c r="U12" s="21" t="n"/>
-      <c r="V12" s="21" t="n"/>
+      <c r="C12" s="82" t="n"/>
+      <c r="D12" s="82" t="n"/>
+      <c r="E12" s="82" t="n"/>
+      <c r="F12" s="82" t="n"/>
+      <c r="G12" s="82" t="n"/>
+      <c r="H12" s="82" t="n"/>
+      <c r="I12" s="82" t="n"/>
+      <c r="J12" s="82" t="n"/>
+      <c r="K12" s="82" t="n"/>
+      <c r="L12" s="82" t="n"/>
+      <c r="M12" s="82" t="n"/>
+      <c r="N12" s="82" t="n"/>
+      <c r="O12" s="82" t="n"/>
+      <c r="P12" s="82" t="n"/>
+      <c r="Q12" s="82" t="n"/>
+      <c r="R12" s="82" t="n"/>
+      <c r="S12" s="82" t="n"/>
+      <c r="T12" s="82" t="n"/>
+      <c r="U12" s="82" t="n"/>
+      <c r="V12" s="82" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1" s="33">
       <c r="C13" s="21" t="n"/>
@@ -29989,7 +30794,22 @@
       <c r="D14" s="70" t="n"/>
       <c r="E14" s="70" t="n"/>
       <c r="F14" s="70" t="n"/>
-      <c r="G14" s="71" t="n"/>
+      <c r="G14" s="70" t="n"/>
+      <c r="H14" s="70" t="n"/>
+      <c r="I14" s="70" t="n"/>
+      <c r="J14" s="70" t="n"/>
+      <c r="K14" s="70" t="n"/>
+      <c r="L14" s="70" t="n"/>
+      <c r="M14" s="70" t="n"/>
+      <c r="N14" s="70" t="n"/>
+      <c r="O14" s="70" t="n"/>
+      <c r="P14" s="70" t="n"/>
+      <c r="Q14" s="70" t="n"/>
+      <c r="R14" s="70" t="n"/>
+      <c r="S14" s="70" t="n"/>
+      <c r="T14" s="70" t="n"/>
+      <c r="U14" s="70" t="n"/>
+      <c r="V14" s="71" t="n"/>
     </row>
     <row r="15" ht="14.3" customHeight="1" s="33">
       <c r="B15" s="6" t="n"/>
@@ -30139,31 +30959,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B17" s="20" t="inlineStr">
+      <c r="B17" s="79" t="inlineStr">
         <is>
           <t>Nov_2015</t>
         </is>
       </c>
-      <c r="C17" s="21" t="n"/>
-      <c r="D17" s="21" t="n"/>
-      <c r="E17" s="21" t="n"/>
-      <c r="F17" s="21" t="n"/>
-      <c r="G17" s="21" t="n"/>
-      <c r="H17" s="21" t="n"/>
-      <c r="I17" s="21" t="n"/>
-      <c r="J17" s="21" t="n"/>
-      <c r="K17" s="21" t="n"/>
-      <c r="L17" s="21" t="n"/>
-      <c r="M17" s="21" t="n"/>
-      <c r="N17" s="21" t="n"/>
-      <c r="O17" s="21" t="n"/>
-      <c r="P17" s="21" t="n"/>
-      <c r="Q17" s="21" t="n"/>
-      <c r="R17" s="21" t="n"/>
-      <c r="S17" s="21" t="n"/>
-      <c r="T17" s="21" t="n"/>
-      <c r="U17" s="21" t="n"/>
-      <c r="V17" s="21" t="n"/>
+      <c r="C17" s="82" t="n"/>
+      <c r="D17" s="82" t="n"/>
+      <c r="E17" s="82" t="n"/>
+      <c r="F17" s="82" t="n"/>
+      <c r="G17" s="82" t="n"/>
+      <c r="H17" s="82" t="n"/>
+      <c r="I17" s="82" t="n"/>
+      <c r="J17" s="82" t="n"/>
+      <c r="K17" s="82" t="n"/>
+      <c r="L17" s="82" t="n"/>
+      <c r="M17" s="82" t="n"/>
+      <c r="N17" s="82" t="n"/>
+      <c r="O17" s="82" t="n"/>
+      <c r="P17" s="82" t="n"/>
+      <c r="Q17" s="82" t="n"/>
+      <c r="R17" s="82" t="n"/>
+      <c r="S17" s="82" t="n"/>
+      <c r="T17" s="82" t="n"/>
+      <c r="U17" s="82" t="n"/>
+      <c r="V17" s="82" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -30171,31 +30991,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="83" t="inlineStr">
         <is>
           <t>Nov_2016</t>
         </is>
       </c>
-      <c r="C18" s="21" t="n"/>
-      <c r="D18" s="21" t="n"/>
-      <c r="E18" s="21" t="n"/>
-      <c r="F18" s="21" t="n"/>
-      <c r="G18" s="21" t="n"/>
-      <c r="H18" s="21" t="n"/>
-      <c r="I18" s="21" t="n"/>
-      <c r="J18" s="21" t="n"/>
-      <c r="K18" s="21" t="n"/>
-      <c r="L18" s="21" t="n"/>
-      <c r="M18" s="21" t="n"/>
-      <c r="N18" s="21" t="n"/>
-      <c r="O18" s="21" t="n"/>
-      <c r="P18" s="21" t="n"/>
-      <c r="Q18" s="21" t="n"/>
-      <c r="R18" s="21" t="n"/>
-      <c r="S18" s="21" t="n"/>
-      <c r="T18" s="21" t="n"/>
-      <c r="U18" s="21" t="n"/>
-      <c r="V18" s="21" t="n"/>
+      <c r="C18" s="82" t="n"/>
+      <c r="D18" s="82" t="n"/>
+      <c r="E18" s="82" t="n"/>
+      <c r="F18" s="82" t="n"/>
+      <c r="G18" s="82" t="n"/>
+      <c r="H18" s="82" t="n"/>
+      <c r="I18" s="82" t="n"/>
+      <c r="J18" s="82" t="n"/>
+      <c r="K18" s="82" t="n"/>
+      <c r="L18" s="82" t="n"/>
+      <c r="M18" s="82" t="n"/>
+      <c r="N18" s="82" t="n"/>
+      <c r="O18" s="82" t="n"/>
+      <c r="P18" s="82" t="n"/>
+      <c r="Q18" s="82" t="n"/>
+      <c r="R18" s="82" t="n"/>
+      <c r="S18" s="82" t="n"/>
+      <c r="T18" s="82" t="n"/>
+      <c r="U18" s="82" t="n"/>
+      <c r="V18" s="82" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -30203,31 +31023,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B19" s="20" t="inlineStr">
+      <c r="B19" s="79" t="inlineStr">
         <is>
           <t>Nov_2017</t>
         </is>
       </c>
-      <c r="C19" s="21" t="n"/>
-      <c r="D19" s="21" t="n"/>
-      <c r="E19" s="21" t="n"/>
-      <c r="F19" s="21" t="n"/>
-      <c r="G19" s="21" t="n"/>
-      <c r="H19" s="21" t="n"/>
-      <c r="I19" s="21" t="n"/>
-      <c r="J19" s="21" t="n"/>
-      <c r="K19" s="21" t="n"/>
-      <c r="L19" s="21" t="n"/>
-      <c r="M19" s="21" t="n"/>
-      <c r="N19" s="21" t="n"/>
-      <c r="O19" s="21" t="n"/>
-      <c r="P19" s="21" t="n"/>
-      <c r="Q19" s="21" t="n"/>
-      <c r="R19" s="21" t="n"/>
-      <c r="S19" s="21" t="n"/>
-      <c r="T19" s="21" t="n"/>
-      <c r="U19" s="21" t="n"/>
-      <c r="V19" s="21" t="n"/>
+      <c r="C19" s="82" t="n"/>
+      <c r="D19" s="82" t="n"/>
+      <c r="E19" s="82" t="n"/>
+      <c r="F19" s="82" t="n"/>
+      <c r="G19" s="82" t="n"/>
+      <c r="H19" s="82" t="n"/>
+      <c r="I19" s="82" t="n"/>
+      <c r="J19" s="82" t="n"/>
+      <c r="K19" s="82" t="n"/>
+      <c r="L19" s="82" t="n"/>
+      <c r="M19" s="82" t="n"/>
+      <c r="N19" s="82" t="n"/>
+      <c r="O19" s="82" t="n"/>
+      <c r="P19" s="82" t="n"/>
+      <c r="Q19" s="82" t="n"/>
+      <c r="R19" s="82" t="n"/>
+      <c r="S19" s="82" t="n"/>
+      <c r="T19" s="82" t="n"/>
+      <c r="U19" s="82" t="n"/>
+      <c r="V19" s="82" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -30235,31 +31055,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B20" s="20" t="inlineStr">
+      <c r="B20" s="79" t="inlineStr">
         <is>
           <t>Nov_2018</t>
         </is>
       </c>
-      <c r="C20" s="21" t="n"/>
-      <c r="D20" s="21" t="n"/>
-      <c r="E20" s="21" t="n"/>
-      <c r="F20" s="21" t="n"/>
-      <c r="G20" s="21" t="n"/>
-      <c r="H20" s="21" t="n"/>
-      <c r="I20" s="21" t="n"/>
-      <c r="J20" s="21" t="n"/>
-      <c r="K20" s="21" t="n"/>
-      <c r="L20" s="21" t="n"/>
-      <c r="M20" s="21" t="n"/>
-      <c r="N20" s="21" t="n"/>
-      <c r="O20" s="21" t="n"/>
-      <c r="P20" s="21" t="n"/>
-      <c r="Q20" s="21" t="n"/>
-      <c r="R20" s="21" t="n"/>
-      <c r="S20" s="21" t="n"/>
-      <c r="T20" s="21" t="n"/>
-      <c r="U20" s="21" t="n"/>
-      <c r="V20" s="21" t="n"/>
+      <c r="C20" s="82" t="n"/>
+      <c r="D20" s="82" t="n"/>
+      <c r="E20" s="82" t="n"/>
+      <c r="F20" s="82" t="n"/>
+      <c r="G20" s="82" t="n"/>
+      <c r="H20" s="82" t="n"/>
+      <c r="I20" s="82" t="n"/>
+      <c r="J20" s="82" t="n"/>
+      <c r="K20" s="82" t="n"/>
+      <c r="L20" s="82" t="n"/>
+      <c r="M20" s="82" t="n"/>
+      <c r="N20" s="82" t="n"/>
+      <c r="O20" s="82" t="n"/>
+      <c r="P20" s="82" t="n"/>
+      <c r="Q20" s="82" t="n"/>
+      <c r="R20" s="82" t="n"/>
+      <c r="S20" s="82" t="n"/>
+      <c r="T20" s="82" t="n"/>
+      <c r="U20" s="82" t="n"/>
+      <c r="V20" s="82" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -30267,31 +31087,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B21" s="20" t="inlineStr">
+      <c r="B21" s="79" t="inlineStr">
         <is>
           <t>Nov_2019</t>
         </is>
       </c>
-      <c r="C21" s="21" t="n"/>
-      <c r="D21" s="21" t="n"/>
-      <c r="E21" s="21" t="n"/>
-      <c r="F21" s="21" t="n"/>
-      <c r="G21" s="21" t="n"/>
-      <c r="H21" s="21" t="n"/>
-      <c r="I21" s="21" t="n"/>
-      <c r="J21" s="21" t="n"/>
-      <c r="K21" s="21" t="n"/>
-      <c r="L21" s="21" t="n"/>
-      <c r="M21" s="21" t="n"/>
-      <c r="N21" s="21" t="n"/>
-      <c r="O21" s="21" t="n"/>
-      <c r="P21" s="21" t="n"/>
-      <c r="Q21" s="21" t="n"/>
-      <c r="R21" s="21" t="n"/>
-      <c r="S21" s="21" t="n"/>
-      <c r="T21" s="21" t="n"/>
-      <c r="U21" s="21" t="n"/>
-      <c r="V21" s="21" t="n"/>
+      <c r="C21" s="82" t="n"/>
+      <c r="D21" s="82" t="n"/>
+      <c r="E21" s="82" t="n"/>
+      <c r="F21" s="82" t="n"/>
+      <c r="G21" s="82" t="n"/>
+      <c r="H21" s="82" t="n"/>
+      <c r="I21" s="82" t="n"/>
+      <c r="J21" s="82" t="n"/>
+      <c r="K21" s="82" t="n"/>
+      <c r="L21" s="82" t="n"/>
+      <c r="M21" s="82" t="n"/>
+      <c r="N21" s="82" t="n"/>
+      <c r="O21" s="82" t="n"/>
+      <c r="P21" s="82" t="n"/>
+      <c r="Q21" s="82" t="n"/>
+      <c r="R21" s="82" t="n"/>
+      <c r="S21" s="82" t="n"/>
+      <c r="T21" s="82" t="n"/>
+      <c r="U21" s="82" t="n"/>
+      <c r="V21" s="82" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -30299,31 +31119,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B22" s="20" t="inlineStr">
+      <c r="B22" s="79" t="inlineStr">
         <is>
           <t>Nov_2020</t>
         </is>
       </c>
-      <c r="C22" s="21" t="n"/>
-      <c r="D22" s="21" t="n"/>
-      <c r="E22" s="21" t="n"/>
-      <c r="F22" s="21" t="n"/>
-      <c r="G22" s="21" t="n"/>
-      <c r="H22" s="21" t="n"/>
-      <c r="I22" s="21" t="n"/>
-      <c r="J22" s="21" t="n"/>
-      <c r="K22" s="21" t="n"/>
-      <c r="L22" s="21" t="n"/>
-      <c r="M22" s="21" t="n"/>
-      <c r="N22" s="21" t="n"/>
-      <c r="O22" s="21" t="n"/>
-      <c r="P22" s="21" t="n"/>
-      <c r="Q22" s="21" t="n"/>
-      <c r="R22" s="21" t="n"/>
-      <c r="S22" s="21" t="n"/>
-      <c r="T22" s="21" t="n"/>
-      <c r="U22" s="21" t="n"/>
-      <c r="V22" s="21" t="n"/>
+      <c r="C22" s="82" t="n"/>
+      <c r="D22" s="82" t="n"/>
+      <c r="E22" s="82" t="n"/>
+      <c r="F22" s="82" t="n"/>
+      <c r="G22" s="82" t="n"/>
+      <c r="H22" s="82" t="n"/>
+      <c r="I22" s="82" t="n"/>
+      <c r="J22" s="82" t="n"/>
+      <c r="K22" s="82" t="n"/>
+      <c r="L22" s="82" t="n"/>
+      <c r="M22" s="82" t="n"/>
+      <c r="N22" s="82" t="n"/>
+      <c r="O22" s="82" t="n"/>
+      <c r="P22" s="82" t="n"/>
+      <c r="Q22" s="82" t="n"/>
+      <c r="R22" s="82" t="n"/>
+      <c r="S22" s="82" t="n"/>
+      <c r="T22" s="82" t="n"/>
+      <c r="U22" s="82" t="n"/>
+      <c r="V22" s="82" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -30331,31 +31151,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B23" s="20" t="inlineStr">
+      <c r="B23" s="79" t="inlineStr">
         <is>
           <t>Nov_2021</t>
         </is>
       </c>
-      <c r="C23" s="21" t="n"/>
-      <c r="D23" s="21" t="n"/>
-      <c r="E23" s="21" t="n"/>
-      <c r="F23" s="21" t="n"/>
-      <c r="G23" s="21" t="n"/>
-      <c r="H23" s="21" t="n"/>
-      <c r="I23" s="21" t="n"/>
-      <c r="J23" s="21" t="n"/>
-      <c r="K23" s="21" t="n"/>
-      <c r="L23" s="21" t="n"/>
-      <c r="M23" s="21" t="n"/>
-      <c r="N23" s="21" t="n"/>
-      <c r="O23" s="21" t="n"/>
-      <c r="P23" s="21" t="n"/>
-      <c r="Q23" s="21" t="n"/>
-      <c r="R23" s="21" t="n"/>
-      <c r="S23" s="21" t="n"/>
-      <c r="T23" s="21" t="n"/>
-      <c r="U23" s="21" t="n"/>
-      <c r="V23" s="21" t="n"/>
+      <c r="C23" s="82" t="n"/>
+      <c r="D23" s="82" t="n"/>
+      <c r="E23" s="82" t="n"/>
+      <c r="F23" s="82" t="n"/>
+      <c r="G23" s="82" t="n"/>
+      <c r="H23" s="82" t="n"/>
+      <c r="I23" s="82" t="n"/>
+      <c r="J23" s="82" t="n"/>
+      <c r="K23" s="82" t="n"/>
+      <c r="L23" s="82" t="n"/>
+      <c r="M23" s="82" t="n"/>
+      <c r="N23" s="82" t="n"/>
+      <c r="O23" s="82" t="n"/>
+      <c r="P23" s="82" t="n"/>
+      <c r="Q23" s="82" t="n"/>
+      <c r="R23" s="82" t="n"/>
+      <c r="S23" s="82" t="n"/>
+      <c r="T23" s="82" t="n"/>
+      <c r="U23" s="82" t="n"/>
+      <c r="V23" s="82" t="n"/>
     </row>
     <row r="24" ht="15" customHeight="1" s="33">
       <c r="A24" t="inlineStr">
@@ -30363,46 +31183,46 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B24" s="28" t="inlineStr">
+      <c r="B24" s="81" t="inlineStr">
         <is>
           <t>Nov_2022</t>
         </is>
       </c>
-      <c r="C24" s="21" t="n"/>
-      <c r="D24" s="21" t="n"/>
-      <c r="E24" s="21" t="n"/>
-      <c r="F24" s="21" t="n"/>
-      <c r="G24" s="21" t="n"/>
-      <c r="H24" s="21" t="n"/>
-      <c r="I24" s="21" t="n"/>
-      <c r="J24" s="21" t="n"/>
-      <c r="K24" s="21" t="n"/>
-      <c r="L24" s="21" t="n"/>
-      <c r="M24" s="21" t="n"/>
-      <c r="N24" s="21" t="n"/>
-      <c r="O24" s="21" t="n"/>
-      <c r="P24" s="21" t="n"/>
-      <c r="Q24" s="21" t="n"/>
-      <c r="R24" s="21" t="n"/>
-      <c r="S24" s="21" t="n"/>
-      <c r="T24" s="21" t="n"/>
-      <c r="U24" s="21" t="n"/>
-      <c r="V24" s="21" t="n"/>
+      <c r="C24" s="82" t="n"/>
+      <c r="D24" s="82" t="n"/>
+      <c r="E24" s="82" t="n"/>
+      <c r="F24" s="82" t="n"/>
+      <c r="G24" s="82" t="n"/>
+      <c r="H24" s="82" t="n"/>
+      <c r="I24" s="82" t="n"/>
+      <c r="J24" s="82" t="n"/>
+      <c r="K24" s="82" t="n"/>
+      <c r="L24" s="82" t="n"/>
+      <c r="M24" s="82" t="n"/>
+      <c r="N24" s="82" t="n"/>
+      <c r="O24" s="82" t="n"/>
+      <c r="P24" s="82" t="n"/>
+      <c r="Q24" s="82" t="n"/>
+      <c r="R24" s="82" t="n"/>
+      <c r="S24" s="82" t="n"/>
+      <c r="T24" s="82" t="n"/>
+      <c r="U24" s="82" t="n"/>
+      <c r="V24" s="82" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B2:G2"/>
     <mergeCell ref="I3:M3"/>
+    <mergeCell ref="D15:H15"/>
     <mergeCell ref="S3:V3"/>
+    <mergeCell ref="N3:R3"/>
     <mergeCell ref="I15:M15"/>
-    <mergeCell ref="B14:G14"/>
+    <mergeCell ref="B2:V2"/>
+    <mergeCell ref="C3:C4"/>
     <mergeCell ref="B3:B4"/>
-    <mergeCell ref="D3:H3"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="N3:R3"/>
-    <mergeCell ref="C3:C4"/>
     <mergeCell ref="N15:R15"/>
     <mergeCell ref="C15:C16"/>
+    <mergeCell ref="B14:V14"/>
+    <mergeCell ref="D3:H3"/>
     <mergeCell ref="B15:B16"/>
     <mergeCell ref="S15:V15"/>
   </mergeCells>
@@ -30453,9 +31273,22 @@
       <c r="D2" s="70" t="n"/>
       <c r="E2" s="70" t="n"/>
       <c r="F2" s="70" t="n"/>
-      <c r="G2" s="71" t="n"/>
-      <c r="J2" s="5" t="n"/>
-      <c r="K2" s="5" t="n"/>
+      <c r="G2" s="70" t="n"/>
+      <c r="H2" s="70" t="n"/>
+      <c r="I2" s="70" t="n"/>
+      <c r="J2" s="70" t="n"/>
+      <c r="K2" s="70" t="n"/>
+      <c r="L2" s="70" t="n"/>
+      <c r="M2" s="70" t="n"/>
+      <c r="N2" s="70" t="n"/>
+      <c r="O2" s="70" t="n"/>
+      <c r="P2" s="70" t="n"/>
+      <c r="Q2" s="70" t="n"/>
+      <c r="R2" s="70" t="n"/>
+      <c r="S2" s="70" t="n"/>
+      <c r="T2" s="70" t="n"/>
+      <c r="U2" s="70" t="n"/>
+      <c r="V2" s="71" t="n"/>
     </row>
     <row r="3" ht="14.3" customHeight="1" s="33">
       <c r="B3" s="6" t="n"/>
@@ -30887,9 +31720,22 @@
       <c r="D14" s="70" t="n"/>
       <c r="E14" s="70" t="n"/>
       <c r="F14" s="70" t="n"/>
-      <c r="G14" s="71" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="n"/>
+      <c r="G14" s="70" t="n"/>
+      <c r="H14" s="70" t="n"/>
+      <c r="I14" s="70" t="n"/>
+      <c r="J14" s="70" t="n"/>
+      <c r="K14" s="70" t="n"/>
+      <c r="L14" s="70" t="n"/>
+      <c r="M14" s="70" t="n"/>
+      <c r="N14" s="70" t="n"/>
+      <c r="O14" s="70" t="n"/>
+      <c r="P14" s="70" t="n"/>
+      <c r="Q14" s="70" t="n"/>
+      <c r="R14" s="70" t="n"/>
+      <c r="S14" s="70" t="n"/>
+      <c r="T14" s="70" t="n"/>
+      <c r="U14" s="70" t="n"/>
+      <c r="V14" s="71" t="n"/>
     </row>
     <row r="15" ht="14.3" customHeight="1" s="33">
       <c r="B15" s="6" t="n"/>
@@ -31321,9 +32167,22 @@
       <c r="D26" s="70" t="n"/>
       <c r="E26" s="70" t="n"/>
       <c r="F26" s="70" t="n"/>
-      <c r="G26" s="71" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="n"/>
+      <c r="G26" s="70" t="n"/>
+      <c r="H26" s="70" t="n"/>
+      <c r="I26" s="70" t="n"/>
+      <c r="J26" s="70" t="n"/>
+      <c r="K26" s="70" t="n"/>
+      <c r="L26" s="70" t="n"/>
+      <c r="M26" s="70" t="n"/>
+      <c r="N26" s="70" t="n"/>
+      <c r="O26" s="70" t="n"/>
+      <c r="P26" s="70" t="n"/>
+      <c r="Q26" s="70" t="n"/>
+      <c r="R26" s="70" t="n"/>
+      <c r="S26" s="70" t="n"/>
+      <c r="T26" s="70" t="n"/>
+      <c r="U26" s="70" t="n"/>
+      <c r="V26" s="71" t="n"/>
     </row>
     <row r="27" ht="14.3" customHeight="1" s="33">
       <c r="B27" s="6" t="n"/>
@@ -31755,9 +32614,22 @@
       <c r="D38" s="70" t="n"/>
       <c r="E38" s="70" t="n"/>
       <c r="F38" s="70" t="n"/>
-      <c r="G38" s="71" t="n"/>
-      <c r="J38" s="5" t="n"/>
-      <c r="K38" s="5" t="n"/>
+      <c r="G38" s="70" t="n"/>
+      <c r="H38" s="70" t="n"/>
+      <c r="I38" s="70" t="n"/>
+      <c r="J38" s="70" t="n"/>
+      <c r="K38" s="70" t="n"/>
+      <c r="L38" s="70" t="n"/>
+      <c r="M38" s="70" t="n"/>
+      <c r="N38" s="70" t="n"/>
+      <c r="O38" s="70" t="n"/>
+      <c r="P38" s="70" t="n"/>
+      <c r="Q38" s="70" t="n"/>
+      <c r="R38" s="70" t="n"/>
+      <c r="S38" s="70" t="n"/>
+      <c r="T38" s="70" t="n"/>
+      <c r="U38" s="70" t="n"/>
+      <c r="V38" s="71" t="n"/>
     </row>
     <row r="39" ht="14.3" customHeight="1" s="33">
       <c r="B39" s="6" t="n"/>
@@ -32189,9 +33061,22 @@
       <c r="D50" s="70" t="n"/>
       <c r="E50" s="70" t="n"/>
       <c r="F50" s="70" t="n"/>
-      <c r="G50" s="71" t="n"/>
-      <c r="J50" s="5" t="n"/>
-      <c r="K50" s="5" t="n"/>
+      <c r="G50" s="70" t="n"/>
+      <c r="H50" s="70" t="n"/>
+      <c r="I50" s="70" t="n"/>
+      <c r="J50" s="70" t="n"/>
+      <c r="K50" s="70" t="n"/>
+      <c r="L50" s="70" t="n"/>
+      <c r="M50" s="70" t="n"/>
+      <c r="N50" s="70" t="n"/>
+      <c r="O50" s="70" t="n"/>
+      <c r="P50" s="70" t="n"/>
+      <c r="Q50" s="70" t="n"/>
+      <c r="R50" s="70" t="n"/>
+      <c r="S50" s="70" t="n"/>
+      <c r="T50" s="70" t="n"/>
+      <c r="U50" s="70" t="n"/>
+      <c r="V50" s="71" t="n"/>
     </row>
     <row r="51" ht="14.3" customHeight="1" s="33">
       <c r="B51" s="6" t="n"/>
@@ -32501,31 +33386,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B58" s="20" t="inlineStr">
+      <c r="B58" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C58" s="31" t="n"/>
-      <c r="D58" s="31" t="n"/>
-      <c r="E58" s="31" t="n"/>
-      <c r="F58" s="31" t="n"/>
-      <c r="G58" s="31" t="n"/>
-      <c r="H58" s="31" t="n"/>
-      <c r="I58" s="31" t="n"/>
-      <c r="J58" s="31" t="n"/>
-      <c r="K58" s="31" t="n"/>
-      <c r="L58" s="31" t="n"/>
-      <c r="M58" s="31" t="n"/>
-      <c r="N58" s="31" t="n"/>
-      <c r="O58" s="31" t="n"/>
-      <c r="P58" s="31" t="n"/>
-      <c r="Q58" s="31" t="n"/>
-      <c r="R58" s="31" t="n"/>
-      <c r="S58" s="31" t="n"/>
-      <c r="T58" s="31" t="n"/>
-      <c r="U58" s="31" t="n"/>
-      <c r="V58" s="31" t="n"/>
+      <c r="C58" s="80" t="n"/>
+      <c r="D58" s="80" t="n"/>
+      <c r="E58" s="80" t="n"/>
+      <c r="F58" s="80" t="n"/>
+      <c r="G58" s="80" t="n"/>
+      <c r="H58" s="80" t="n"/>
+      <c r="I58" s="80" t="n"/>
+      <c r="J58" s="80" t="n"/>
+      <c r="K58" s="80" t="n"/>
+      <c r="L58" s="80" t="n"/>
+      <c r="M58" s="80" t="n"/>
+      <c r="N58" s="80" t="n"/>
+      <c r="O58" s="80" t="n"/>
+      <c r="P58" s="80" t="n"/>
+      <c r="Q58" s="80" t="n"/>
+      <c r="R58" s="80" t="n"/>
+      <c r="S58" s="80" t="n"/>
+      <c r="T58" s="80" t="n"/>
+      <c r="U58" s="80" t="n"/>
+      <c r="V58" s="80" t="n"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -32623,9 +33508,22 @@
       <c r="D62" s="70" t="n"/>
       <c r="E62" s="70" t="n"/>
       <c r="F62" s="70" t="n"/>
-      <c r="G62" s="71" t="n"/>
-      <c r="J62" s="5" t="n"/>
-      <c r="K62" s="5" t="n"/>
+      <c r="G62" s="70" t="n"/>
+      <c r="H62" s="70" t="n"/>
+      <c r="I62" s="70" t="n"/>
+      <c r="J62" s="70" t="n"/>
+      <c r="K62" s="70" t="n"/>
+      <c r="L62" s="70" t="n"/>
+      <c r="M62" s="70" t="n"/>
+      <c r="N62" s="70" t="n"/>
+      <c r="O62" s="70" t="n"/>
+      <c r="P62" s="70" t="n"/>
+      <c r="Q62" s="70" t="n"/>
+      <c r="R62" s="70" t="n"/>
+      <c r="S62" s="70" t="n"/>
+      <c r="T62" s="70" t="n"/>
+      <c r="U62" s="70" t="n"/>
+      <c r="V62" s="71" t="n"/>
     </row>
     <row r="63" ht="14.3" customHeight="1" s="33">
       <c r="B63" s="6" t="n"/>
@@ -32935,31 +33833,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B70" s="20" t="inlineStr">
+      <c r="B70" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C70" s="21" t="n"/>
-      <c r="D70" s="21" t="n"/>
-      <c r="E70" s="21" t="n"/>
-      <c r="F70" s="21" t="n"/>
-      <c r="G70" s="21" t="n"/>
-      <c r="H70" s="21" t="n"/>
-      <c r="I70" s="21" t="n"/>
-      <c r="J70" s="21" t="n"/>
-      <c r="K70" s="21" t="n"/>
-      <c r="L70" s="21" t="n"/>
-      <c r="M70" s="21" t="n"/>
-      <c r="N70" s="21" t="n"/>
-      <c r="O70" s="21" t="n"/>
-      <c r="P70" s="21" t="n"/>
-      <c r="Q70" s="21" t="n"/>
-      <c r="R70" s="21" t="n"/>
-      <c r="S70" s="21" t="n"/>
-      <c r="T70" s="21" t="n"/>
-      <c r="U70" s="21" t="n"/>
-      <c r="V70" s="21" t="n"/>
+      <c r="C70" s="82" t="n"/>
+      <c r="D70" s="82" t="n"/>
+      <c r="E70" s="82" t="n"/>
+      <c r="F70" s="82" t="n"/>
+      <c r="G70" s="82" t="n"/>
+      <c r="H70" s="82" t="n"/>
+      <c r="I70" s="82" t="n"/>
+      <c r="J70" s="82" t="n"/>
+      <c r="K70" s="82" t="n"/>
+      <c r="L70" s="82" t="n"/>
+      <c r="M70" s="82" t="n"/>
+      <c r="N70" s="82" t="n"/>
+      <c r="O70" s="82" t="n"/>
+      <c r="P70" s="82" t="n"/>
+      <c r="Q70" s="82" t="n"/>
+      <c r="R70" s="82" t="n"/>
+      <c r="S70" s="82" t="n"/>
+      <c r="T70" s="82" t="n"/>
+      <c r="U70" s="82" t="n"/>
+      <c r="V70" s="82" t="n"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -33057,9 +33955,22 @@
       <c r="D74" s="70" t="n"/>
       <c r="E74" s="70" t="n"/>
       <c r="F74" s="70" t="n"/>
-      <c r="G74" s="71" t="n"/>
-      <c r="J74" s="5" t="n"/>
-      <c r="K74" s="5" t="n"/>
+      <c r="G74" s="70" t="n"/>
+      <c r="H74" s="70" t="n"/>
+      <c r="I74" s="70" t="n"/>
+      <c r="J74" s="70" t="n"/>
+      <c r="K74" s="70" t="n"/>
+      <c r="L74" s="70" t="n"/>
+      <c r="M74" s="70" t="n"/>
+      <c r="N74" s="70" t="n"/>
+      <c r="O74" s="70" t="n"/>
+      <c r="P74" s="70" t="n"/>
+      <c r="Q74" s="70" t="n"/>
+      <c r="R74" s="70" t="n"/>
+      <c r="S74" s="70" t="n"/>
+      <c r="T74" s="70" t="n"/>
+      <c r="U74" s="70" t="n"/>
+      <c r="V74" s="71" t="n"/>
     </row>
     <row r="75" ht="14.3" customHeight="1" s="33">
       <c r="B75" s="6" t="n"/>
@@ -33491,9 +34402,22 @@
       <c r="D86" s="70" t="n"/>
       <c r="E86" s="70" t="n"/>
       <c r="F86" s="70" t="n"/>
-      <c r="G86" s="71" t="n"/>
-      <c r="J86" s="5" t="n"/>
-      <c r="K86" s="5" t="n"/>
+      <c r="G86" s="70" t="n"/>
+      <c r="H86" s="70" t="n"/>
+      <c r="I86" s="70" t="n"/>
+      <c r="J86" s="70" t="n"/>
+      <c r="K86" s="70" t="n"/>
+      <c r="L86" s="70" t="n"/>
+      <c r="M86" s="70" t="n"/>
+      <c r="N86" s="70" t="n"/>
+      <c r="O86" s="70" t="n"/>
+      <c r="P86" s="70" t="n"/>
+      <c r="Q86" s="70" t="n"/>
+      <c r="R86" s="70" t="n"/>
+      <c r="S86" s="70" t="n"/>
+      <c r="T86" s="70" t="n"/>
+      <c r="U86" s="70" t="n"/>
+      <c r="V86" s="71" t="n"/>
     </row>
     <row r="87" ht="14.3" customHeight="1" s="33">
       <c r="B87" s="6" t="n"/>
@@ -33939,62 +34863,62 @@
     </row>
   </sheetData>
   <mergeCells count="56">
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="B86:V86"/>
+    <mergeCell ref="B2:V2"/>
+    <mergeCell ref="I15:M15"/>
+    <mergeCell ref="B3:B4"/>
     <mergeCell ref="N63:R63"/>
+    <mergeCell ref="D63:H63"/>
     <mergeCell ref="C63:C64"/>
     <mergeCell ref="I27:M27"/>
+    <mergeCell ref="B14:V14"/>
     <mergeCell ref="N51:R51"/>
-    <mergeCell ref="B38:G38"/>
-    <mergeCell ref="S51:V51"/>
-    <mergeCell ref="B74:G74"/>
-    <mergeCell ref="I75:M75"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="I87:M87"/>
-    <mergeCell ref="D75:H75"/>
-    <mergeCell ref="I3:M3"/>
-    <mergeCell ref="S3:V3"/>
-    <mergeCell ref="D87:H87"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="B26:G26"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="I39:M39"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="D39:H39"/>
-    <mergeCell ref="B75:B76"/>
-    <mergeCell ref="I63:M63"/>
-    <mergeCell ref="B86:G86"/>
-    <mergeCell ref="N27:R27"/>
-    <mergeCell ref="S15:V15"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="I15:M15"/>
-    <mergeCell ref="B14:G14"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="D63:H63"/>
     <mergeCell ref="N75:R75"/>
     <mergeCell ref="S63:V63"/>
     <mergeCell ref="B39:B40"/>
     <mergeCell ref="C75:C76"/>
+    <mergeCell ref="B38:V38"/>
+    <mergeCell ref="S51:V51"/>
     <mergeCell ref="N3:R3"/>
     <mergeCell ref="S75:V75"/>
     <mergeCell ref="D27:H27"/>
+    <mergeCell ref="I75:M75"/>
+    <mergeCell ref="B15:B16"/>
     <mergeCell ref="N39:R39"/>
+    <mergeCell ref="I87:M87"/>
+    <mergeCell ref="D75:H75"/>
+    <mergeCell ref="B74:V74"/>
     <mergeCell ref="S27:V27"/>
     <mergeCell ref="B87:B88"/>
+    <mergeCell ref="I3:M3"/>
     <mergeCell ref="C51:C52"/>
+    <mergeCell ref="S3:V3"/>
+    <mergeCell ref="D87:H87"/>
     <mergeCell ref="S39:V39"/>
-    <mergeCell ref="B50:G50"/>
-    <mergeCell ref="B62:G62"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="B50:V50"/>
+    <mergeCell ref="I39:M39"/>
+    <mergeCell ref="B26:V26"/>
     <mergeCell ref="D3:H3"/>
+    <mergeCell ref="B63:B64"/>
     <mergeCell ref="N87:R87"/>
+    <mergeCell ref="D39:H39"/>
     <mergeCell ref="B51:B52"/>
     <mergeCell ref="C87:C88"/>
+    <mergeCell ref="B75:B76"/>
+    <mergeCell ref="B62:V62"/>
     <mergeCell ref="I51:M51"/>
+    <mergeCell ref="C3:C4"/>
     <mergeCell ref="D15:H15"/>
-    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="I63:M63"/>
+    <mergeCell ref="S87:V87"/>
     <mergeCell ref="N15:R15"/>
-    <mergeCell ref="S87:V87"/>
     <mergeCell ref="D51:H51"/>
     <mergeCell ref="C15:C16"/>
+    <mergeCell ref="N27:R27"/>
+    <mergeCell ref="S15:V15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -34043,9 +34967,22 @@
       <c r="D2" s="70" t="n"/>
       <c r="E2" s="70" t="n"/>
       <c r="F2" s="70" t="n"/>
-      <c r="G2" s="71" t="n"/>
-      <c r="J2" s="5" t="n"/>
-      <c r="K2" s="5" t="n"/>
+      <c r="G2" s="70" t="n"/>
+      <c r="H2" s="70" t="n"/>
+      <c r="I2" s="70" t="n"/>
+      <c r="J2" s="70" t="n"/>
+      <c r="K2" s="70" t="n"/>
+      <c r="L2" s="70" t="n"/>
+      <c r="M2" s="70" t="n"/>
+      <c r="N2" s="70" t="n"/>
+      <c r="O2" s="70" t="n"/>
+      <c r="P2" s="70" t="n"/>
+      <c r="Q2" s="70" t="n"/>
+      <c r="R2" s="70" t="n"/>
+      <c r="S2" s="70" t="n"/>
+      <c r="T2" s="70" t="n"/>
+      <c r="U2" s="70" t="n"/>
+      <c r="V2" s="71" t="n"/>
     </row>
     <row r="3" ht="14.3" customHeight="1" s="33">
       <c r="B3" s="6" t="n"/>
@@ -34477,9 +35414,22 @@
       <c r="D14" s="70" t="n"/>
       <c r="E14" s="70" t="n"/>
       <c r="F14" s="70" t="n"/>
-      <c r="G14" s="71" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="n"/>
+      <c r="G14" s="70" t="n"/>
+      <c r="H14" s="70" t="n"/>
+      <c r="I14" s="70" t="n"/>
+      <c r="J14" s="70" t="n"/>
+      <c r="K14" s="70" t="n"/>
+      <c r="L14" s="70" t="n"/>
+      <c r="M14" s="70" t="n"/>
+      <c r="N14" s="70" t="n"/>
+      <c r="O14" s="70" t="n"/>
+      <c r="P14" s="70" t="n"/>
+      <c r="Q14" s="70" t="n"/>
+      <c r="R14" s="70" t="n"/>
+      <c r="S14" s="70" t="n"/>
+      <c r="T14" s="70" t="n"/>
+      <c r="U14" s="70" t="n"/>
+      <c r="V14" s="71" t="n"/>
     </row>
     <row r="15" ht="14.3" customHeight="1" s="33">
       <c r="B15" s="6" t="n"/>
@@ -34911,9 +35861,22 @@
       <c r="D26" s="70" t="n"/>
       <c r="E26" s="70" t="n"/>
       <c r="F26" s="70" t="n"/>
-      <c r="G26" s="71" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="n"/>
+      <c r="G26" s="70" t="n"/>
+      <c r="H26" s="70" t="n"/>
+      <c r="I26" s="70" t="n"/>
+      <c r="J26" s="70" t="n"/>
+      <c r="K26" s="70" t="n"/>
+      <c r="L26" s="70" t="n"/>
+      <c r="M26" s="70" t="n"/>
+      <c r="N26" s="70" t="n"/>
+      <c r="O26" s="70" t="n"/>
+      <c r="P26" s="70" t="n"/>
+      <c r="Q26" s="70" t="n"/>
+      <c r="R26" s="70" t="n"/>
+      <c r="S26" s="70" t="n"/>
+      <c r="T26" s="70" t="n"/>
+      <c r="U26" s="70" t="n"/>
+      <c r="V26" s="71" t="n"/>
     </row>
     <row r="27" ht="14.3" customHeight="1" s="33">
       <c r="B27" s="6" t="n"/>
@@ -35345,9 +36308,22 @@
       <c r="D38" s="70" t="n"/>
       <c r="E38" s="70" t="n"/>
       <c r="F38" s="70" t="n"/>
-      <c r="G38" s="71" t="n"/>
-      <c r="J38" s="5" t="n"/>
-      <c r="K38" s="5" t="n"/>
+      <c r="G38" s="70" t="n"/>
+      <c r="H38" s="70" t="n"/>
+      <c r="I38" s="70" t="n"/>
+      <c r="J38" s="70" t="n"/>
+      <c r="K38" s="70" t="n"/>
+      <c r="L38" s="70" t="n"/>
+      <c r="M38" s="70" t="n"/>
+      <c r="N38" s="70" t="n"/>
+      <c r="O38" s="70" t="n"/>
+      <c r="P38" s="70" t="n"/>
+      <c r="Q38" s="70" t="n"/>
+      <c r="R38" s="70" t="n"/>
+      <c r="S38" s="70" t="n"/>
+      <c r="T38" s="70" t="n"/>
+      <c r="U38" s="70" t="n"/>
+      <c r="V38" s="71" t="n"/>
     </row>
     <row r="39" ht="14.3" customHeight="1" s="33">
       <c r="B39" s="6" t="n"/>
@@ -35779,9 +36755,22 @@
       <c r="D50" s="70" t="n"/>
       <c r="E50" s="70" t="n"/>
       <c r="F50" s="70" t="n"/>
-      <c r="G50" s="71" t="n"/>
-      <c r="J50" s="5" t="n"/>
-      <c r="K50" s="5" t="n"/>
+      <c r="G50" s="70" t="n"/>
+      <c r="H50" s="70" t="n"/>
+      <c r="I50" s="70" t="n"/>
+      <c r="J50" s="70" t="n"/>
+      <c r="K50" s="70" t="n"/>
+      <c r="L50" s="70" t="n"/>
+      <c r="M50" s="70" t="n"/>
+      <c r="N50" s="70" t="n"/>
+      <c r="O50" s="70" t="n"/>
+      <c r="P50" s="70" t="n"/>
+      <c r="Q50" s="70" t="n"/>
+      <c r="R50" s="70" t="n"/>
+      <c r="S50" s="70" t="n"/>
+      <c r="T50" s="70" t="n"/>
+      <c r="U50" s="70" t="n"/>
+      <c r="V50" s="71" t="n"/>
     </row>
     <row r="51" ht="14.3" customHeight="1" s="33">
       <c r="B51" s="6" t="n"/>
@@ -36091,31 +37080,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B58" s="20" t="inlineStr">
+      <c r="B58" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C58" s="31" t="n"/>
-      <c r="D58" s="31" t="n"/>
-      <c r="E58" s="31" t="n"/>
-      <c r="F58" s="31" t="n"/>
-      <c r="G58" s="31" t="n"/>
-      <c r="H58" s="31" t="n"/>
-      <c r="I58" s="31" t="n"/>
-      <c r="J58" s="31" t="n"/>
-      <c r="K58" s="31" t="n"/>
-      <c r="L58" s="31" t="n"/>
-      <c r="M58" s="31" t="n"/>
-      <c r="N58" s="31" t="n"/>
-      <c r="O58" s="31" t="n"/>
-      <c r="P58" s="31" t="n"/>
-      <c r="Q58" s="31" t="n"/>
-      <c r="R58" s="31" t="n"/>
-      <c r="S58" s="31" t="n"/>
-      <c r="T58" s="31" t="n"/>
-      <c r="U58" s="31" t="n"/>
-      <c r="V58" s="31" t="n"/>
+      <c r="C58" s="80" t="n"/>
+      <c r="D58" s="80" t="n"/>
+      <c r="E58" s="80" t="n"/>
+      <c r="F58" s="80" t="n"/>
+      <c r="G58" s="80" t="n"/>
+      <c r="H58" s="80" t="n"/>
+      <c r="I58" s="80" t="n"/>
+      <c r="J58" s="80" t="n"/>
+      <c r="K58" s="80" t="n"/>
+      <c r="L58" s="80" t="n"/>
+      <c r="M58" s="80" t="n"/>
+      <c r="N58" s="80" t="n"/>
+      <c r="O58" s="80" t="n"/>
+      <c r="P58" s="80" t="n"/>
+      <c r="Q58" s="80" t="n"/>
+      <c r="R58" s="80" t="n"/>
+      <c r="S58" s="80" t="n"/>
+      <c r="T58" s="80" t="n"/>
+      <c r="U58" s="80" t="n"/>
+      <c r="V58" s="80" t="n"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -36213,9 +37202,22 @@
       <c r="D62" s="70" t="n"/>
       <c r="E62" s="70" t="n"/>
       <c r="F62" s="70" t="n"/>
-      <c r="G62" s="71" t="n"/>
-      <c r="J62" s="5" t="n"/>
-      <c r="K62" s="5" t="n"/>
+      <c r="G62" s="70" t="n"/>
+      <c r="H62" s="70" t="n"/>
+      <c r="I62" s="70" t="n"/>
+      <c r="J62" s="70" t="n"/>
+      <c r="K62" s="70" t="n"/>
+      <c r="L62" s="70" t="n"/>
+      <c r="M62" s="70" t="n"/>
+      <c r="N62" s="70" t="n"/>
+      <c r="O62" s="70" t="n"/>
+      <c r="P62" s="70" t="n"/>
+      <c r="Q62" s="70" t="n"/>
+      <c r="R62" s="70" t="n"/>
+      <c r="S62" s="70" t="n"/>
+      <c r="T62" s="70" t="n"/>
+      <c r="U62" s="70" t="n"/>
+      <c r="V62" s="71" t="n"/>
     </row>
     <row r="63" ht="14.3" customHeight="1" s="33">
       <c r="B63" s="6" t="n"/>
@@ -36525,31 +37527,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B70" s="20" t="inlineStr">
+      <c r="B70" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C70" s="21" t="n"/>
-      <c r="D70" s="21" t="n"/>
-      <c r="E70" s="21" t="n"/>
-      <c r="F70" s="21" t="n"/>
-      <c r="G70" s="21" t="n"/>
-      <c r="H70" s="21" t="n"/>
-      <c r="I70" s="21" t="n"/>
-      <c r="J70" s="21" t="n"/>
-      <c r="K70" s="21" t="n"/>
-      <c r="L70" s="21" t="n"/>
-      <c r="M70" s="21" t="n"/>
-      <c r="N70" s="21" t="n"/>
-      <c r="O70" s="21" t="n"/>
-      <c r="P70" s="21" t="n"/>
-      <c r="Q70" s="21" t="n"/>
-      <c r="R70" s="21" t="n"/>
-      <c r="S70" s="21" t="n"/>
-      <c r="T70" s="21" t="n"/>
-      <c r="U70" s="21" t="n"/>
-      <c r="V70" s="21" t="n"/>
+      <c r="C70" s="82" t="n"/>
+      <c r="D70" s="82" t="n"/>
+      <c r="E70" s="82" t="n"/>
+      <c r="F70" s="82" t="n"/>
+      <c r="G70" s="82" t="n"/>
+      <c r="H70" s="82" t="n"/>
+      <c r="I70" s="82" t="n"/>
+      <c r="J70" s="82" t="n"/>
+      <c r="K70" s="82" t="n"/>
+      <c r="L70" s="82" t="n"/>
+      <c r="M70" s="82" t="n"/>
+      <c r="N70" s="82" t="n"/>
+      <c r="O70" s="82" t="n"/>
+      <c r="P70" s="82" t="n"/>
+      <c r="Q70" s="82" t="n"/>
+      <c r="R70" s="82" t="n"/>
+      <c r="S70" s="82" t="n"/>
+      <c r="T70" s="82" t="n"/>
+      <c r="U70" s="82" t="n"/>
+      <c r="V70" s="82" t="n"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -36647,9 +37649,22 @@
       <c r="D74" s="70" t="n"/>
       <c r="E74" s="70" t="n"/>
       <c r="F74" s="70" t="n"/>
-      <c r="G74" s="71" t="n"/>
-      <c r="J74" s="5" t="n"/>
-      <c r="K74" s="5" t="n"/>
+      <c r="G74" s="70" t="n"/>
+      <c r="H74" s="70" t="n"/>
+      <c r="I74" s="70" t="n"/>
+      <c r="J74" s="70" t="n"/>
+      <c r="K74" s="70" t="n"/>
+      <c r="L74" s="70" t="n"/>
+      <c r="M74" s="70" t="n"/>
+      <c r="N74" s="70" t="n"/>
+      <c r="O74" s="70" t="n"/>
+      <c r="P74" s="70" t="n"/>
+      <c r="Q74" s="70" t="n"/>
+      <c r="R74" s="70" t="n"/>
+      <c r="S74" s="70" t="n"/>
+      <c r="T74" s="70" t="n"/>
+      <c r="U74" s="70" t="n"/>
+      <c r="V74" s="71" t="n"/>
     </row>
     <row r="75" ht="14.3" customHeight="1" s="33">
       <c r="B75" s="6" t="n"/>
@@ -37081,9 +38096,22 @@
       <c r="D86" s="70" t="n"/>
       <c r="E86" s="70" t="n"/>
       <c r="F86" s="70" t="n"/>
-      <c r="G86" s="71" t="n"/>
-      <c r="J86" s="5" t="n"/>
-      <c r="K86" s="5" t="n"/>
+      <c r="G86" s="70" t="n"/>
+      <c r="H86" s="70" t="n"/>
+      <c r="I86" s="70" t="n"/>
+      <c r="J86" s="70" t="n"/>
+      <c r="K86" s="70" t="n"/>
+      <c r="L86" s="70" t="n"/>
+      <c r="M86" s="70" t="n"/>
+      <c r="N86" s="70" t="n"/>
+      <c r="O86" s="70" t="n"/>
+      <c r="P86" s="70" t="n"/>
+      <c r="Q86" s="70" t="n"/>
+      <c r="R86" s="70" t="n"/>
+      <c r="S86" s="70" t="n"/>
+      <c r="T86" s="70" t="n"/>
+      <c r="U86" s="70" t="n"/>
+      <c r="V86" s="71" t="n"/>
     </row>
     <row r="87" ht="14.3" customHeight="1" s="33">
       <c r="B87" s="6" t="n"/>
@@ -37507,62 +38535,62 @@
     </row>
   </sheetData>
   <mergeCells count="56">
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="B86:V86"/>
+    <mergeCell ref="B2:V2"/>
+    <mergeCell ref="I15:M15"/>
+    <mergeCell ref="B3:B4"/>
     <mergeCell ref="N63:R63"/>
+    <mergeCell ref="D63:H63"/>
     <mergeCell ref="C63:C64"/>
     <mergeCell ref="I27:M27"/>
+    <mergeCell ref="B14:V14"/>
     <mergeCell ref="N51:R51"/>
-    <mergeCell ref="B38:G38"/>
-    <mergeCell ref="S51:V51"/>
-    <mergeCell ref="B74:G74"/>
-    <mergeCell ref="I75:M75"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="I87:M87"/>
-    <mergeCell ref="D75:H75"/>
-    <mergeCell ref="I3:M3"/>
-    <mergeCell ref="S3:V3"/>
-    <mergeCell ref="D87:H87"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="B26:G26"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="I39:M39"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="D39:H39"/>
-    <mergeCell ref="B75:B76"/>
-    <mergeCell ref="I63:M63"/>
-    <mergeCell ref="B86:G86"/>
-    <mergeCell ref="N27:R27"/>
-    <mergeCell ref="S15:V15"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="I15:M15"/>
-    <mergeCell ref="B14:G14"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="D63:H63"/>
     <mergeCell ref="N75:R75"/>
     <mergeCell ref="S63:V63"/>
     <mergeCell ref="B39:B40"/>
     <mergeCell ref="C75:C76"/>
+    <mergeCell ref="B38:V38"/>
+    <mergeCell ref="S51:V51"/>
     <mergeCell ref="N3:R3"/>
     <mergeCell ref="S75:V75"/>
     <mergeCell ref="D27:H27"/>
+    <mergeCell ref="I75:M75"/>
+    <mergeCell ref="B15:B16"/>
     <mergeCell ref="N39:R39"/>
+    <mergeCell ref="I87:M87"/>
+    <mergeCell ref="D75:H75"/>
+    <mergeCell ref="B74:V74"/>
     <mergeCell ref="S27:V27"/>
     <mergeCell ref="B87:B88"/>
+    <mergeCell ref="I3:M3"/>
     <mergeCell ref="C51:C52"/>
+    <mergeCell ref="S3:V3"/>
+    <mergeCell ref="D87:H87"/>
     <mergeCell ref="S39:V39"/>
-    <mergeCell ref="B50:G50"/>
-    <mergeCell ref="B62:G62"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="B50:V50"/>
+    <mergeCell ref="I39:M39"/>
+    <mergeCell ref="B26:V26"/>
     <mergeCell ref="D3:H3"/>
+    <mergeCell ref="B63:B64"/>
     <mergeCell ref="N87:R87"/>
+    <mergeCell ref="D39:H39"/>
     <mergeCell ref="B51:B52"/>
     <mergeCell ref="C87:C88"/>
+    <mergeCell ref="B75:B76"/>
+    <mergeCell ref="B62:V62"/>
     <mergeCell ref="I51:M51"/>
+    <mergeCell ref="C3:C4"/>
     <mergeCell ref="D15:H15"/>
-    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="I63:M63"/>
+    <mergeCell ref="S87:V87"/>
     <mergeCell ref="N15:R15"/>
-    <mergeCell ref="S87:V87"/>
     <mergeCell ref="D51:H51"/>
     <mergeCell ref="C15:C16"/>
+    <mergeCell ref="N27:R27"/>
+    <mergeCell ref="S15:V15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -37611,9 +38639,22 @@
       <c r="D2" s="70" t="n"/>
       <c r="E2" s="70" t="n"/>
       <c r="F2" s="70" t="n"/>
-      <c r="G2" s="71" t="n"/>
-      <c r="J2" s="5" t="n"/>
-      <c r="K2" s="5" t="n"/>
+      <c r="G2" s="70" t="n"/>
+      <c r="H2" s="70" t="n"/>
+      <c r="I2" s="70" t="n"/>
+      <c r="J2" s="70" t="n"/>
+      <c r="K2" s="70" t="n"/>
+      <c r="L2" s="70" t="n"/>
+      <c r="M2" s="70" t="n"/>
+      <c r="N2" s="70" t="n"/>
+      <c r="O2" s="70" t="n"/>
+      <c r="P2" s="70" t="n"/>
+      <c r="Q2" s="70" t="n"/>
+      <c r="R2" s="70" t="n"/>
+      <c r="S2" s="70" t="n"/>
+      <c r="T2" s="70" t="n"/>
+      <c r="U2" s="70" t="n"/>
+      <c r="V2" s="71" t="n"/>
     </row>
     <row r="3" ht="14.3" customHeight="1" s="33">
       <c r="B3" s="6" t="n"/>
@@ -38045,9 +39086,22 @@
       <c r="D14" s="70" t="n"/>
       <c r="E14" s="70" t="n"/>
       <c r="F14" s="70" t="n"/>
-      <c r="G14" s="71" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="n"/>
+      <c r="G14" s="70" t="n"/>
+      <c r="H14" s="70" t="n"/>
+      <c r="I14" s="70" t="n"/>
+      <c r="J14" s="70" t="n"/>
+      <c r="K14" s="70" t="n"/>
+      <c r="L14" s="70" t="n"/>
+      <c r="M14" s="70" t="n"/>
+      <c r="N14" s="70" t="n"/>
+      <c r="O14" s="70" t="n"/>
+      <c r="P14" s="70" t="n"/>
+      <c r="Q14" s="70" t="n"/>
+      <c r="R14" s="70" t="n"/>
+      <c r="S14" s="70" t="n"/>
+      <c r="T14" s="70" t="n"/>
+      <c r="U14" s="70" t="n"/>
+      <c r="V14" s="71" t="n"/>
     </row>
     <row r="15" ht="14.3" customHeight="1" s="33">
       <c r="B15" s="6" t="n"/>
@@ -38479,9 +39533,22 @@
       <c r="D26" s="70" t="n"/>
       <c r="E26" s="70" t="n"/>
       <c r="F26" s="70" t="n"/>
-      <c r="G26" s="71" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="n"/>
+      <c r="G26" s="70" t="n"/>
+      <c r="H26" s="70" t="n"/>
+      <c r="I26" s="70" t="n"/>
+      <c r="J26" s="70" t="n"/>
+      <c r="K26" s="70" t="n"/>
+      <c r="L26" s="70" t="n"/>
+      <c r="M26" s="70" t="n"/>
+      <c r="N26" s="70" t="n"/>
+      <c r="O26" s="70" t="n"/>
+      <c r="P26" s="70" t="n"/>
+      <c r="Q26" s="70" t="n"/>
+      <c r="R26" s="70" t="n"/>
+      <c r="S26" s="70" t="n"/>
+      <c r="T26" s="70" t="n"/>
+      <c r="U26" s="70" t="n"/>
+      <c r="V26" s="71" t="n"/>
     </row>
     <row r="27" ht="14.3" customHeight="1" s="33">
       <c r="B27" s="6" t="n"/>
@@ -38913,9 +39980,22 @@
       <c r="D38" s="70" t="n"/>
       <c r="E38" s="70" t="n"/>
       <c r="F38" s="70" t="n"/>
-      <c r="G38" s="71" t="n"/>
-      <c r="J38" s="5" t="n"/>
-      <c r="K38" s="5" t="n"/>
+      <c r="G38" s="70" t="n"/>
+      <c r="H38" s="70" t="n"/>
+      <c r="I38" s="70" t="n"/>
+      <c r="J38" s="70" t="n"/>
+      <c r="K38" s="70" t="n"/>
+      <c r="L38" s="70" t="n"/>
+      <c r="M38" s="70" t="n"/>
+      <c r="N38" s="70" t="n"/>
+      <c r="O38" s="70" t="n"/>
+      <c r="P38" s="70" t="n"/>
+      <c r="Q38" s="70" t="n"/>
+      <c r="R38" s="70" t="n"/>
+      <c r="S38" s="70" t="n"/>
+      <c r="T38" s="70" t="n"/>
+      <c r="U38" s="70" t="n"/>
+      <c r="V38" s="71" t="n"/>
     </row>
     <row r="39" ht="14.3" customHeight="1" s="33">
       <c r="B39" s="6" t="n"/>
@@ -39347,9 +40427,22 @@
       <c r="D50" s="70" t="n"/>
       <c r="E50" s="70" t="n"/>
       <c r="F50" s="70" t="n"/>
-      <c r="G50" s="71" t="n"/>
-      <c r="J50" s="5" t="n"/>
-      <c r="K50" s="5" t="n"/>
+      <c r="G50" s="70" t="n"/>
+      <c r="H50" s="70" t="n"/>
+      <c r="I50" s="70" t="n"/>
+      <c r="J50" s="70" t="n"/>
+      <c r="K50" s="70" t="n"/>
+      <c r="L50" s="70" t="n"/>
+      <c r="M50" s="70" t="n"/>
+      <c r="N50" s="70" t="n"/>
+      <c r="O50" s="70" t="n"/>
+      <c r="P50" s="70" t="n"/>
+      <c r="Q50" s="70" t="n"/>
+      <c r="R50" s="70" t="n"/>
+      <c r="S50" s="70" t="n"/>
+      <c r="T50" s="70" t="n"/>
+      <c r="U50" s="70" t="n"/>
+      <c r="V50" s="71" t="n"/>
     </row>
     <row r="51" ht="14.3" customHeight="1" s="33">
       <c r="B51" s="6" t="n"/>
@@ -39659,31 +40752,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B58" s="20" t="inlineStr">
+      <c r="B58" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C58" s="31" t="n"/>
-      <c r="D58" s="31" t="n"/>
-      <c r="E58" s="31" t="n"/>
-      <c r="F58" s="31" t="n"/>
-      <c r="G58" s="31" t="n"/>
-      <c r="H58" s="31" t="n"/>
-      <c r="I58" s="31" t="n"/>
-      <c r="J58" s="31" t="n"/>
-      <c r="K58" s="31" t="n"/>
-      <c r="L58" s="31" t="n"/>
-      <c r="M58" s="31" t="n"/>
-      <c r="N58" s="31" t="n"/>
-      <c r="O58" s="31" t="n"/>
-      <c r="P58" s="31" t="n"/>
-      <c r="Q58" s="31" t="n"/>
-      <c r="R58" s="31" t="n"/>
-      <c r="S58" s="31" t="n"/>
-      <c r="T58" s="31" t="n"/>
-      <c r="U58" s="31" t="n"/>
-      <c r="V58" s="31" t="n"/>
+      <c r="C58" s="80" t="n"/>
+      <c r="D58" s="80" t="n"/>
+      <c r="E58" s="80" t="n"/>
+      <c r="F58" s="80" t="n"/>
+      <c r="G58" s="80" t="n"/>
+      <c r="H58" s="80" t="n"/>
+      <c r="I58" s="80" t="n"/>
+      <c r="J58" s="80" t="n"/>
+      <c r="K58" s="80" t="n"/>
+      <c r="L58" s="80" t="n"/>
+      <c r="M58" s="80" t="n"/>
+      <c r="N58" s="80" t="n"/>
+      <c r="O58" s="80" t="n"/>
+      <c r="P58" s="80" t="n"/>
+      <c r="Q58" s="80" t="n"/>
+      <c r="R58" s="80" t="n"/>
+      <c r="S58" s="80" t="n"/>
+      <c r="T58" s="80" t="n"/>
+      <c r="U58" s="80" t="n"/>
+      <c r="V58" s="80" t="n"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -39781,9 +40874,22 @@
       <c r="D62" s="70" t="n"/>
       <c r="E62" s="70" t="n"/>
       <c r="F62" s="70" t="n"/>
-      <c r="G62" s="71" t="n"/>
-      <c r="J62" s="5" t="n"/>
-      <c r="K62" s="5" t="n"/>
+      <c r="G62" s="70" t="n"/>
+      <c r="H62" s="70" t="n"/>
+      <c r="I62" s="70" t="n"/>
+      <c r="J62" s="70" t="n"/>
+      <c r="K62" s="70" t="n"/>
+      <c r="L62" s="70" t="n"/>
+      <c r="M62" s="70" t="n"/>
+      <c r="N62" s="70" t="n"/>
+      <c r="O62" s="70" t="n"/>
+      <c r="P62" s="70" t="n"/>
+      <c r="Q62" s="70" t="n"/>
+      <c r="R62" s="70" t="n"/>
+      <c r="S62" s="70" t="n"/>
+      <c r="T62" s="70" t="n"/>
+      <c r="U62" s="70" t="n"/>
+      <c r="V62" s="71" t="n"/>
     </row>
     <row r="63" ht="14.3" customHeight="1" s="33">
       <c r="B63" s="6" t="n"/>
@@ -40093,31 +41199,31 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B70" s="20" t="inlineStr">
+      <c r="B70" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C70" s="21" t="n"/>
-      <c r="D70" s="21" t="n"/>
-      <c r="E70" s="21" t="n"/>
-      <c r="F70" s="21" t="n"/>
-      <c r="G70" s="21" t="n"/>
-      <c r="H70" s="21" t="n"/>
-      <c r="I70" s="21" t="n"/>
-      <c r="J70" s="21" t="n"/>
-      <c r="K70" s="21" t="n"/>
-      <c r="L70" s="21" t="n"/>
-      <c r="M70" s="21" t="n"/>
-      <c r="N70" s="21" t="n"/>
-      <c r="O70" s="21" t="n"/>
-      <c r="P70" s="21" t="n"/>
-      <c r="Q70" s="21" t="n"/>
-      <c r="R70" s="21" t="n"/>
-      <c r="S70" s="21" t="n"/>
-      <c r="T70" s="21" t="n"/>
-      <c r="U70" s="21" t="n"/>
-      <c r="V70" s="21" t="n"/>
+      <c r="C70" s="82" t="n"/>
+      <c r="D70" s="82" t="n"/>
+      <c r="E70" s="82" t="n"/>
+      <c r="F70" s="82" t="n"/>
+      <c r="G70" s="82" t="n"/>
+      <c r="H70" s="82" t="n"/>
+      <c r="I70" s="82" t="n"/>
+      <c r="J70" s="82" t="n"/>
+      <c r="K70" s="82" t="n"/>
+      <c r="L70" s="82" t="n"/>
+      <c r="M70" s="82" t="n"/>
+      <c r="N70" s="82" t="n"/>
+      <c r="O70" s="82" t="n"/>
+      <c r="P70" s="82" t="n"/>
+      <c r="Q70" s="82" t="n"/>
+      <c r="R70" s="82" t="n"/>
+      <c r="S70" s="82" t="n"/>
+      <c r="T70" s="82" t="n"/>
+      <c r="U70" s="82" t="n"/>
+      <c r="V70" s="82" t="n"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -40215,9 +41321,22 @@
       <c r="D74" s="70" t="n"/>
       <c r="E74" s="70" t="n"/>
       <c r="F74" s="70" t="n"/>
-      <c r="G74" s="71" t="n"/>
-      <c r="J74" s="5" t="n"/>
-      <c r="K74" s="5" t="n"/>
+      <c r="G74" s="70" t="n"/>
+      <c r="H74" s="70" t="n"/>
+      <c r="I74" s="70" t="n"/>
+      <c r="J74" s="70" t="n"/>
+      <c r="K74" s="70" t="n"/>
+      <c r="L74" s="70" t="n"/>
+      <c r="M74" s="70" t="n"/>
+      <c r="N74" s="70" t="n"/>
+      <c r="O74" s="70" t="n"/>
+      <c r="P74" s="70" t="n"/>
+      <c r="Q74" s="70" t="n"/>
+      <c r="R74" s="70" t="n"/>
+      <c r="S74" s="70" t="n"/>
+      <c r="T74" s="70" t="n"/>
+      <c r="U74" s="70" t="n"/>
+      <c r="V74" s="71" t="n"/>
     </row>
     <row r="75" ht="14.3" customHeight="1" s="33">
       <c r="B75" s="6" t="n"/>
@@ -40649,9 +41768,22 @@
       <c r="D86" s="70" t="n"/>
       <c r="E86" s="70" t="n"/>
       <c r="F86" s="70" t="n"/>
-      <c r="G86" s="71" t="n"/>
-      <c r="J86" s="5" t="n"/>
-      <c r="K86" s="5" t="n"/>
+      <c r="G86" s="70" t="n"/>
+      <c r="H86" s="70" t="n"/>
+      <c r="I86" s="70" t="n"/>
+      <c r="J86" s="70" t="n"/>
+      <c r="K86" s="70" t="n"/>
+      <c r="L86" s="70" t="n"/>
+      <c r="M86" s="70" t="n"/>
+      <c r="N86" s="70" t="n"/>
+      <c r="O86" s="70" t="n"/>
+      <c r="P86" s="70" t="n"/>
+      <c r="Q86" s="70" t="n"/>
+      <c r="R86" s="70" t="n"/>
+      <c r="S86" s="70" t="n"/>
+      <c r="T86" s="70" t="n"/>
+      <c r="U86" s="70" t="n"/>
+      <c r="V86" s="71" t="n"/>
     </row>
     <row r="87" ht="14.3" customHeight="1" s="33">
       <c r="B87" s="6" t="n"/>
@@ -41097,62 +42229,62 @@
     </row>
   </sheetData>
   <mergeCells count="56">
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="B86:V86"/>
+    <mergeCell ref="B2:V2"/>
+    <mergeCell ref="I15:M15"/>
+    <mergeCell ref="B3:B4"/>
     <mergeCell ref="N63:R63"/>
+    <mergeCell ref="D63:H63"/>
     <mergeCell ref="C63:C64"/>
     <mergeCell ref="I27:M27"/>
+    <mergeCell ref="B14:V14"/>
     <mergeCell ref="N51:R51"/>
-    <mergeCell ref="B38:G38"/>
-    <mergeCell ref="S51:V51"/>
-    <mergeCell ref="B74:G74"/>
-    <mergeCell ref="I75:M75"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="I87:M87"/>
-    <mergeCell ref="D75:H75"/>
-    <mergeCell ref="I3:M3"/>
-    <mergeCell ref="S3:V3"/>
-    <mergeCell ref="D87:H87"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="B26:G26"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="I39:M39"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="D39:H39"/>
-    <mergeCell ref="B75:B76"/>
-    <mergeCell ref="I63:M63"/>
-    <mergeCell ref="B86:G86"/>
-    <mergeCell ref="N27:R27"/>
-    <mergeCell ref="S15:V15"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="I15:M15"/>
-    <mergeCell ref="B14:G14"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="D63:H63"/>
     <mergeCell ref="N75:R75"/>
     <mergeCell ref="S63:V63"/>
     <mergeCell ref="B39:B40"/>
     <mergeCell ref="C75:C76"/>
+    <mergeCell ref="B38:V38"/>
+    <mergeCell ref="S51:V51"/>
     <mergeCell ref="N3:R3"/>
     <mergeCell ref="S75:V75"/>
     <mergeCell ref="D27:H27"/>
+    <mergeCell ref="I75:M75"/>
+    <mergeCell ref="B15:B16"/>
     <mergeCell ref="N39:R39"/>
+    <mergeCell ref="I87:M87"/>
+    <mergeCell ref="D75:H75"/>
+    <mergeCell ref="B74:V74"/>
     <mergeCell ref="S27:V27"/>
     <mergeCell ref="B87:B88"/>
+    <mergeCell ref="I3:M3"/>
     <mergeCell ref="C51:C52"/>
+    <mergeCell ref="S3:V3"/>
+    <mergeCell ref="D87:H87"/>
     <mergeCell ref="S39:V39"/>
-    <mergeCell ref="B50:G50"/>
-    <mergeCell ref="B62:G62"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="B50:V50"/>
+    <mergeCell ref="I39:M39"/>
+    <mergeCell ref="B26:V26"/>
     <mergeCell ref="D3:H3"/>
+    <mergeCell ref="B63:B64"/>
     <mergeCell ref="N87:R87"/>
+    <mergeCell ref="D39:H39"/>
     <mergeCell ref="B51:B52"/>
     <mergeCell ref="C87:C88"/>
+    <mergeCell ref="B75:B76"/>
+    <mergeCell ref="B62:V62"/>
     <mergeCell ref="I51:M51"/>
+    <mergeCell ref="C3:C4"/>
     <mergeCell ref="D15:H15"/>
-    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="I63:M63"/>
+    <mergeCell ref="S87:V87"/>
     <mergeCell ref="N15:R15"/>
-    <mergeCell ref="S87:V87"/>
     <mergeCell ref="D51:H51"/>
     <mergeCell ref="C15:C16"/>
+    <mergeCell ref="N27:R27"/>
+    <mergeCell ref="S15:V15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
